--- a/pattern_report.xlsx
+++ b/pattern_report.xlsx
@@ -474,7 +474,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>v10.0</t>
+          <t>v11.0</t>
         </is>
       </c>
     </row>
@@ -485,7 +485,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>46225.0157182254</v>
+        <v>46225.33961270287</v>
       </c>
     </row>
     <row r="4">
@@ -579,7 +579,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>25562</v>
+        <v>25542</v>
       </c>
     </row>
     <row r="13">
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>25526</v>
+        <v>25506</v>
       </c>
     </row>
     <row r="14">
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>28978</v>
+        <v>28948</v>
       </c>
     </row>
     <row r="18">
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="B18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>28978</v>
+        <v>18757</v>
       </c>
     </row>
     <row r="20">
@@ -902,10 +902,10 @@
         <v>31.0259555014865</v>
       </c>
       <c r="J2" t="n">
-        <v>4255</v>
+        <v>4258</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>0.545475910693302</v>
+        <v>0.5453264443400657</v>
       </c>
       <c r="L2" t="n">
         <v>60</v>
@@ -926,10 +926,10 @@
         <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>4253</v>
+        <v>4256</v>
       </c>
       <c r="S2" s="4" t="n">
-        <v>0.6484834234657888</v>
+        <v>0.6487312030075187</v>
       </c>
       <c r="T2" t="n">
         <v>60</v>
@@ -987,16 +987,16 @@
         <v>31.0259555014865</v>
       </c>
       <c r="J3" t="n">
-        <v>6041</v>
+        <v>6039</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>0.54262539314683</v>
+        <v>0.5423083291935751</v>
       </c>
       <c r="L3" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M3" s="4" t="n">
-        <v>0.5632183908045977</v>
+        <v>0.5568181818181818</v>
       </c>
       <c r="N3" t="n">
         <v>147</v>
@@ -1011,16 +1011,16 @@
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>6035</v>
+        <v>6033</v>
       </c>
       <c r="S3" s="4" t="n">
-        <v>0.6533554266777133</v>
+        <v>0.6530747555113542</v>
       </c>
       <c r="T3" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="U3" s="4" t="n">
-        <v>0.6896551724137931</v>
+        <v>0.6931818181818182</v>
       </c>
       <c r="V3" t="n">
         <v>144</v>
@@ -1072,10 +1072,10 @@
         <v>-10.98901052835441</v>
       </c>
       <c r="J4" t="n">
-        <v>4647</v>
+        <v>4637</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>0.5881213686249193</v>
+        <v>0.5906836316583999</v>
       </c>
       <c r="L4" t="n">
         <v>7</v>
@@ -1096,10 +1096,10 @@
         <v>0.75</v>
       </c>
       <c r="R4" t="n">
-        <v>4627</v>
+        <v>4617</v>
       </c>
       <c r="S4" s="4" t="n">
-        <v>0.6848930192349254</v>
+        <v>0.6881091617933723</v>
       </c>
       <c r="T4" t="n">
         <v>7</v>
@@ -1157,10 +1157,10 @@
         <v>-3.083700440528636</v>
       </c>
       <c r="J5" t="n">
-        <v>4255</v>
+        <v>4258</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>0.545475910693302</v>
+        <v>0.5453264443400657</v>
       </c>
       <c r="L5" t="n">
         <v>69</v>
@@ -1181,10 +1181,10 @@
         <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>4253</v>
+        <v>4256</v>
       </c>
       <c r="S5" s="4" t="n">
-        <v>0.6484834234657888</v>
+        <v>0.6487312030075187</v>
       </c>
       <c r="T5" t="n">
         <v>69</v>
@@ -1242,10 +1242,10 @@
         <v>-1.021508226671353</v>
       </c>
       <c r="J6" t="n">
-        <v>4647</v>
+        <v>4637</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.5881213686249193</v>
+        <v>0.5906836316583999</v>
       </c>
       <c r="L6" t="n">
         <v>70</v>
@@ -1266,10 +1266,10 @@
         <v>0.5</v>
       </c>
       <c r="R6" t="n">
-        <v>4627</v>
+        <v>4617</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>0.6848930192349254</v>
+        <v>0.6881091617933723</v>
       </c>
       <c r="T6" t="n">
         <v>70</v>
@@ -1327,10 +1327,10 @@
         <v>-0.7510697115483023</v>
       </c>
       <c r="J7" t="n">
-        <v>4255</v>
+        <v>4258</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.545475910693302</v>
+        <v>0.5453264443400657</v>
       </c>
       <c r="L7" t="n">
         <v>57</v>
@@ -1349,10 +1349,10 @@
       </c>
       <c r="Q7" s="4" t="inlineStr"/>
       <c r="R7" t="n">
-        <v>4253</v>
+        <v>4256</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>0.6484834234657888</v>
+        <v>0.6487312030075187</v>
       </c>
       <c r="T7" t="n">
         <v>57</v>
@@ -1408,10 +1408,10 @@
         <v>-10.0328947368421</v>
       </c>
       <c r="J8" t="n">
-        <v>3005</v>
+        <v>3002</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.6472545757071547</v>
+        <v>0.6462358427714857</v>
       </c>
       <c r="L8" t="n">
         <v>36</v>
@@ -1432,10 +1432,10 @@
         <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>3004</v>
+        <v>3001</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>0.7420106524633822</v>
+        <v>0.7410863045651449</v>
       </c>
       <c r="T8" t="n">
         <v>36</v>
@@ -1493,10 +1493,10 @@
         <v>3.456786664007372</v>
       </c>
       <c r="J9" t="n">
-        <v>4647</v>
+        <v>4637</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.5881213686249193</v>
+        <v>0.5906836316583999</v>
       </c>
       <c r="L9" t="n">
         <v>66</v>
@@ -1517,10 +1517,10 @@
         <v>1</v>
       </c>
       <c r="R9" t="n">
-        <v>4627</v>
+        <v>4617</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>0.6848930192349254</v>
+        <v>0.6881091617933723</v>
       </c>
       <c r="T9" t="n">
         <v>66</v>
@@ -1578,10 +1578,10 @@
         <v>-1.796407185628746</v>
       </c>
       <c r="J10" t="n">
-        <v>3005</v>
+        <v>3002</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.6472545757071547</v>
+        <v>0.6462358427714857</v>
       </c>
       <c r="L10" t="n">
         <v>28</v>
@@ -1600,10 +1600,10 @@
       </c>
       <c r="Q10" s="4" t="inlineStr"/>
       <c r="R10" t="n">
-        <v>3004</v>
+        <v>3001</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>0.7420106524633822</v>
+        <v>0.7410863045651449</v>
       </c>
       <c r="T10" t="n">
         <v>28</v>
@@ -1659,10 +1659,10 @@
         <v>0.9630809405433149</v>
       </c>
       <c r="J11" t="n">
-        <v>6041</v>
+        <v>6039</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.54262539314683</v>
+        <v>0.5423083291935751</v>
       </c>
       <c r="L11" t="n">
         <v>107</v>
@@ -1683,10 +1683,10 @@
         <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>6035</v>
+        <v>6033</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>0.6533554266777133</v>
+        <v>0.6530747555113542</v>
       </c>
       <c r="T11" t="n">
         <v>107</v>
@@ -2060,10 +2060,10 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>0.6231404958677685</v>
+        <v>0.6221122112211221</v>
       </c>
       <c r="K4" t="n">
         <v>7</v>
@@ -2082,10 +2082,10 @@
       </c>
       <c r="P4" s="4" t="inlineStr"/>
       <c r="Q4" t="n">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="R4" s="4" t="n">
-        <v>0.6892561983471074</v>
+        <v>0.6897689768976898</v>
       </c>
       <c r="S4" t="n">
         <v>7</v>
@@ -2602,10 +2602,10 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.6618705035971223</v>
+        <v>0.6642857142857143</v>
       </c>
       <c r="K11" t="n">
         <v>1</v>
@@ -2624,10 +2624,10 @@
       </c>
       <c r="P11" s="4" t="inlineStr"/>
       <c r="Q11" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>0.7553956834532374</v>
+        <v>0.7571428571428571</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -2680,10 +2680,10 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.6473684210526316</v>
+        <v>0.6465968586387435</v>
       </c>
       <c r="K12" t="n">
         <v>5</v>
@@ -2702,10 +2702,10 @@
       </c>
       <c r="P12" s="4" t="inlineStr"/>
       <c r="Q12" t="n">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>0.7263157894736842</v>
+        <v>0.725130890052356</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2914,10 +2914,10 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.6217008797653959</v>
+        <v>0.6228070175438597</v>
       </c>
       <c r="K15" t="n">
         <v>6</v>
@@ -2936,10 +2936,10 @@
       </c>
       <c r="P15" s="4" t="inlineStr"/>
       <c r="Q15" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>0.7096774193548387</v>
+        <v>0.7105263157894737</v>
       </c>
       <c r="S15" t="n">
         <v>6</v>
@@ -2992,10 +2992,10 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.6232558139534884</v>
+        <v>0.625</v>
       </c>
       <c r="K16" t="n">
         <v>8</v>
@@ -3014,10 +3014,10 @@
       </c>
       <c r="P16" s="4" t="inlineStr"/>
       <c r="Q16" t="n">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>0.7093023255813954</v>
+        <v>0.7106481481481481</v>
       </c>
       <c r="S16" t="n">
         <v>8</v>
@@ -3280,10 +3280,10 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1205</v>
+        <v>1199</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.5294605809128631</v>
+        <v>0.5312760633861552</v>
       </c>
       <c r="K20" t="n">
         <v>2</v>
@@ -3302,10 +3302,10 @@
       </c>
       <c r="P20" s="4" t="inlineStr"/>
       <c r="Q20" t="n">
-        <v>1195</v>
+        <v>1189</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>0.6535564853556486</v>
+        <v>0.6593776282590412</v>
       </c>
       <c r="S20" t="n">
         <v>2</v>
@@ -3358,10 +3358,10 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1830</v>
+        <v>1817</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.5442622950819672</v>
+        <v>0.5465052283984591</v>
       </c>
       <c r="K21" t="n">
         <v>2</v>
@@ -3382,10 +3382,10 @@
         <v>0.5</v>
       </c>
       <c r="Q21" t="n">
-        <v>1817</v>
+        <v>1804</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>0.6604292790313704</v>
+        <v>0.6657427937915743</v>
       </c>
       <c r="S21" t="n">
         <v>2</v>
@@ -3440,10 +3440,10 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2058</v>
+        <v>2046</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.5510204081632653</v>
+        <v>0.552297165200391</v>
       </c>
       <c r="K22" t="n">
         <v>2</v>
@@ -3464,10 +3464,10 @@
         <v>0.5</v>
       </c>
       <c r="Q22" t="n">
-        <v>2044</v>
+        <v>2032</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>0.6648727984344422</v>
+        <v>0.6692913385826772</v>
       </c>
       <c r="S22" t="n">
         <v>2</v>
@@ -3522,10 +3522,10 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.7333333333333333</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -3542,10 +3542,10 @@
       </c>
       <c r="P23" s="4" t="inlineStr"/>
       <c r="Q23" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>0.7333333333333333</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -3596,10 +3596,10 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.7826086956521739</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -3616,10 +3616,10 @@
       </c>
       <c r="P24" s="4" t="inlineStr"/>
       <c r="Q24" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.7826086956521739</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -3670,10 +3670,10 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.6956521739130435</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -3690,10 +3690,10 @@
       </c>
       <c r="P25" s="4" t="inlineStr"/>
       <c r="Q25" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.6956521739130435</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -3744,10 +3744,10 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>0.6818181818181818</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -3762,10 +3762,10 @@
       </c>
       <c r="P26" s="4" t="inlineStr"/>
       <c r="Q26" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>0.6818181818181818</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -3913,7 +3913,7 @@
         <v>104</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>0.7788461538461539</v>
+        <v>0.7884615384615384</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3966,10 +3966,10 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>0.4966887417218543</v>
+        <v>0.4962192816635161</v>
       </c>
       <c r="K29" t="n">
         <v>16</v>
@@ -3988,10 +3988,10 @@
       </c>
       <c r="P29" s="4" t="inlineStr"/>
       <c r="Q29" t="n">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>0.5950804162724692</v>
+        <v>0.5954631379962193</v>
       </c>
       <c r="S29" t="n">
         <v>16</v>
@@ -4044,10 +4044,10 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1924</v>
+        <v>1925</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>0.5046777546777547</v>
+        <v>0.5044155844155844</v>
       </c>
       <c r="K30" t="n">
         <v>31</v>
@@ -4066,10 +4066,10 @@
       </c>
       <c r="P30" s="4" t="inlineStr"/>
       <c r="Q30" t="n">
-        <v>1923</v>
+        <v>1924</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>0.6183047321892876</v>
+        <v>0.6185031185031185</v>
       </c>
       <c r="S30" t="n">
         <v>31</v>
@@ -4122,10 +4122,10 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2501</v>
+        <v>2503</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>0.521391443422631</v>
+        <v>0.5213743507790651</v>
       </c>
       <c r="K31" t="n">
         <v>41</v>
@@ -4144,10 +4144,10 @@
       </c>
       <c r="P31" s="4" t="inlineStr"/>
       <c r="Q31" t="n">
-        <v>2499</v>
+        <v>2501</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>0.6294517807122849</v>
+        <v>0.6297481007596961</v>
       </c>
       <c r="S31" t="n">
         <v>41</v>
@@ -4200,10 +4200,10 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>0.5016251354279523</v>
+        <v>0.5010822510822511</v>
       </c>
       <c r="K32" t="n">
         <v>10</v>
@@ -4222,10 +4222,10 @@
       </c>
       <c r="P32" s="4" t="inlineStr"/>
       <c r="Q32" t="n">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>0.6258134490238612</v>
+        <v>0.6262188515709642</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4278,10 +4278,10 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1578</v>
+        <v>1579</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>0.4955640050697085</v>
+        <v>0.4952501583280557</v>
       </c>
       <c r="K33" t="n">
         <v>15</v>
@@ -4300,10 +4300,10 @@
       </c>
       <c r="P33" s="4" t="inlineStr"/>
       <c r="Q33" t="n">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>0.6150919467343057</v>
+        <v>0.6153358681875792</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4668,10 +4668,10 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1205</v>
+        <v>1199</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>0.5294605809128631</v>
+        <v>0.5312760633861552</v>
       </c>
       <c r="K38" t="n">
         <v>25</v>
@@ -4690,10 +4690,10 @@
       </c>
       <c r="P38" s="4" t="inlineStr"/>
       <c r="Q38" t="n">
-        <v>1195</v>
+        <v>1189</v>
       </c>
       <c r="R38" s="4" t="n">
-        <v>0.6535564853556486</v>
+        <v>0.6593776282590412</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4746,10 +4746,10 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1830</v>
+        <v>1817</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>0.5442622950819672</v>
+        <v>0.5465052283984591</v>
       </c>
       <c r="K39" t="n">
         <v>32</v>
@@ -4768,10 +4768,10 @@
       </c>
       <c r="P39" s="4" t="inlineStr"/>
       <c r="Q39" t="n">
-        <v>1817</v>
+        <v>1804</v>
       </c>
       <c r="R39" s="4" t="n">
-        <v>0.6604292790313704</v>
+        <v>0.6657427937915743</v>
       </c>
       <c r="S39" t="n">
         <v>32</v>
@@ -4824,10 +4824,10 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2058</v>
+        <v>2046</v>
       </c>
       <c r="J40" s="4" t="n">
-        <v>0.5510204081632653</v>
+        <v>0.552297165200391</v>
       </c>
       <c r="K40" t="n">
         <v>36</v>
@@ -4846,10 +4846,10 @@
       </c>
       <c r="P40" s="4" t="inlineStr"/>
       <c r="Q40" t="n">
-        <v>2044</v>
+        <v>2032</v>
       </c>
       <c r="R40" s="4" t="n">
-        <v>0.6648727984344422</v>
+        <v>0.6692913385826772</v>
       </c>
       <c r="S40" t="n">
         <v>36</v>
@@ -4902,10 +4902,10 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1042</v>
+        <v>1049</v>
       </c>
       <c r="J41" s="4" t="n">
-        <v>0.54510556621881</v>
+        <v>0.553860819828408</v>
       </c>
       <c r="K41" t="n">
         <v>18</v>
@@ -4926,10 +4926,10 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>1035</v>
+        <v>1042</v>
       </c>
       <c r="R41" s="4" t="n">
-        <v>0.6473429951690821</v>
+        <v>0.6525911708253359</v>
       </c>
       <c r="S41" t="n">
         <v>18</v>
@@ -4984,10 +4984,10 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1918</v>
+        <v>1916</v>
       </c>
       <c r="J42" s="4" t="n">
-        <v>0.5375391032325338</v>
+        <v>0.5443632567849687</v>
       </c>
       <c r="K42" t="n">
         <v>32</v>
@@ -5008,10 +5008,10 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>1904</v>
+        <v>1902</v>
       </c>
       <c r="R42" s="4" t="n">
-        <v>0.6486344537815126</v>
+        <v>0.655099894847529</v>
       </c>
       <c r="S42" t="n">
         <v>32</v>
@@ -5066,10 +5066,10 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2517</v>
+        <v>2521</v>
       </c>
       <c r="J43" s="4" t="n">
-        <v>0.5399284862932062</v>
+        <v>0.5450218167393891</v>
       </c>
       <c r="K43" t="n">
         <v>39</v>
@@ -5090,10 +5090,10 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>2500</v>
+        <v>2504</v>
       </c>
       <c r="R43" s="4" t="n">
-        <v>0.6536</v>
+        <v>0.6601437699680511</v>
       </c>
       <c r="S43" t="n">
         <v>39</v>
@@ -5148,10 +5148,10 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="J44" s="4" t="n">
-        <v>0.5817174515235457</v>
+        <v>0.5810055865921788</v>
       </c>
       <c r="K44" t="n">
         <v>6</v>
@@ -5170,10 +5170,10 @@
       </c>
       <c r="P44" s="4" t="inlineStr"/>
       <c r="Q44" t="n">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="R44" s="4" t="n">
-        <v>0.6648199445983379</v>
+        <v>0.6620111731843575</v>
       </c>
       <c r="S44" t="n">
         <v>6</v>
@@ -5226,10 +5226,10 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="J45" s="4" t="n">
-        <v>0.5922165820642978</v>
+        <v>0.5932203389830508</v>
       </c>
       <c r="K45" t="n">
         <v>11</v>
@@ -5248,10 +5248,10 @@
       </c>
       <c r="P45" s="4" t="inlineStr"/>
       <c r="Q45" t="n">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="R45" s="4" t="n">
-        <v>0.6700507614213198</v>
+        <v>0.6711864406779661</v>
       </c>
       <c r="S45" t="n">
         <v>11</v>
@@ -5304,10 +5304,10 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="J46" s="4" t="n">
-        <v>0.6044880785413744</v>
+        <v>0.6064425770308123</v>
       </c>
       <c r="K46" t="n">
         <v>15</v>
@@ -5326,10 +5326,10 @@
       </c>
       <c r="P46" s="4" t="inlineStr"/>
       <c r="Q46" t="n">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="R46" s="4" t="n">
-        <v>0.6816269284712483</v>
+        <v>0.6834733893557423</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5382,10 +5382,10 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="J47" s="4" t="n">
-        <v>0.4966887417218543</v>
+        <v>0.4962192816635161</v>
       </c>
       <c r="K47" t="n">
         <v>12</v>
@@ -5404,10 +5404,10 @@
       </c>
       <c r="P47" s="4" t="inlineStr"/>
       <c r="Q47" t="n">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="R47" s="4" t="n">
-        <v>0.5950804162724692</v>
+        <v>0.5954631379962193</v>
       </c>
       <c r="S47" t="n">
         <v>12</v>
@@ -5460,10 +5460,10 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1924</v>
+        <v>1925</v>
       </c>
       <c r="J48" s="4" t="n">
-        <v>0.5046777546777547</v>
+        <v>0.5044155844155844</v>
       </c>
       <c r="K48" t="n">
         <v>21</v>
@@ -5482,10 +5482,10 @@
       </c>
       <c r="P48" s="4" t="inlineStr"/>
       <c r="Q48" t="n">
-        <v>1923</v>
+        <v>1924</v>
       </c>
       <c r="R48" s="4" t="n">
-        <v>0.6183047321892876</v>
+        <v>0.6185031185031185</v>
       </c>
       <c r="S48" t="n">
         <v>21</v>
@@ -5538,10 +5538,10 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2501</v>
+        <v>2503</v>
       </c>
       <c r="J49" s="4" t="n">
-        <v>0.521391443422631</v>
+        <v>0.5213743507790651</v>
       </c>
       <c r="K49" t="n">
         <v>27</v>
@@ -5560,10 +5560,10 @@
       </c>
       <c r="P49" s="4" t="inlineStr"/>
       <c r="Q49" t="n">
-        <v>2499</v>
+        <v>2501</v>
       </c>
       <c r="R49" s="4" t="n">
-        <v>0.6294517807122849</v>
+        <v>0.6297481007596961</v>
       </c>
       <c r="S49" t="n">
         <v>27</v>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="J56" s="4" t="n">
-        <v>0.5669700910273082</v>
+        <v>0.5626631853785901</v>
       </c>
       <c r="K56" t="n">
         <v>6</v>
@@ -6106,10 +6106,10 @@
       </c>
       <c r="P56" s="4" t="inlineStr"/>
       <c r="Q56" t="n">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="R56" s="4" t="n">
-        <v>0.6853055916775033</v>
+        <v>0.6814621409921671</v>
       </c>
       <c r="S56" t="n">
         <v>6</v>
@@ -6162,10 +6162,10 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1426</v>
+        <v>1423</v>
       </c>
       <c r="J57" s="4" t="n">
-        <v>0.6093969144460029</v>
+        <v>0.607167955024596</v>
       </c>
       <c r="K57" t="n">
         <v>14</v>
@@ -6184,10 +6184,10 @@
       </c>
       <c r="P57" s="4" t="inlineStr"/>
       <c r="Q57" t="n">
-        <v>1426</v>
+        <v>1423</v>
       </c>
       <c r="R57" s="4" t="n">
-        <v>0.7145862552594671</v>
+        <v>0.7118763176387913</v>
       </c>
       <c r="S57" t="n">
         <v>14</v>
@@ -6240,10 +6240,10 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1830</v>
+        <v>1828</v>
       </c>
       <c r="J58" s="4" t="n">
-        <v>0.6311475409836066</v>
+        <v>0.6280087527352297</v>
       </c>
       <c r="K58" t="n">
         <v>21</v>
@@ -6262,10 +6262,10 @@
       </c>
       <c r="P58" s="4" t="inlineStr"/>
       <c r="Q58" t="n">
-        <v>1830</v>
+        <v>1828</v>
       </c>
       <c r="R58" s="4" t="n">
-        <v>0.7316939890710382</v>
+        <v>0.7286652078774617</v>
       </c>
       <c r="S58" t="n">
         <v>21</v>
@@ -6318,10 +6318,10 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="J59" s="4" t="n">
-        <v>0.6819672131147541</v>
+        <v>0.6831683168316832</v>
       </c>
       <c r="K59" t="n">
         <v>6</v>
@@ -6340,10 +6340,10 @@
       </c>
       <c r="P59" s="4" t="inlineStr"/>
       <c r="Q59" t="n">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="R59" s="4" t="n">
-        <v>0.7664473684210527</v>
+        <v>0.7682119205298014</v>
       </c>
       <c r="S59" t="n">
         <v>6</v>
@@ -6396,10 +6396,10 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="J60" s="4" t="n">
-        <v>0.6682027649769585</v>
+        <v>0.6685912240184757</v>
       </c>
       <c r="K60" t="n">
         <v>12</v>
@@ -6420,10 +6420,10 @@
         <v>1</v>
       </c>
       <c r="Q60" t="n">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="R60" s="4" t="n">
-        <v>0.7566320645905421</v>
+        <v>0.7572254335260116</v>
       </c>
       <c r="S60" t="n">
         <v>12</v>
@@ -6478,10 +6478,10 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="J61" s="4" t="n">
-        <v>0.7371134020618557</v>
+        <v>0.7366609294320138</v>
       </c>
       <c r="K61" t="n">
         <v>10</v>
@@ -6500,10 +6500,10 @@
       </c>
       <c r="P61" s="4" t="inlineStr"/>
       <c r="Q61" t="n">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="R61" s="4" t="n">
-        <v>0.8072289156626506</v>
+        <v>0.8068965517241379</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6638,10 +6638,10 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="J63" s="4" t="n">
-        <v>0.7477272727272727</v>
+        <v>0.744874715261959</v>
       </c>
       <c r="K63" t="n">
         <v>9</v>
@@ -6662,10 +6662,10 @@
         <v>1</v>
       </c>
       <c r="Q63" t="n">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="R63" s="4" t="n">
-        <v>0.8314350797266514</v>
+        <v>0.8310502283105022</v>
       </c>
       <c r="S63" t="n">
         <v>9</v>
@@ -6723,7 +6723,7 @@
         <v>777</v>
       </c>
       <c r="J64" s="4" t="n">
-        <v>0.6808236808236808</v>
+        <v>0.6782496782496783</v>
       </c>
       <c r="K64" t="n">
         <v>15</v>
@@ -6747,7 +6747,7 @@
         <v>776</v>
       </c>
       <c r="R64" s="4" t="n">
-        <v>0.7835051546391752</v>
+        <v>0.7822164948453608</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -6802,10 +6802,10 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1222</v>
+        <v>1219</v>
       </c>
       <c r="J65" s="4" t="n">
-        <v>0.5499181669394435</v>
+        <v>0.5520918785890074</v>
       </c>
       <c r="K65" t="n">
         <v>13</v>
@@ -6824,10 +6824,10 @@
       </c>
       <c r="P65" s="4" t="inlineStr"/>
       <c r="Q65" t="n">
-        <v>1218</v>
+        <v>1215</v>
       </c>
       <c r="R65" s="4" t="n">
-        <v>0.6436781609195402</v>
+        <v>0.6436213991769547</v>
       </c>
       <c r="S65" t="n">
         <v>13</v>
@@ -6880,10 +6880,10 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1946</v>
+        <v>1947</v>
       </c>
       <c r="J66" s="4" t="n">
-        <v>0.578622816032888</v>
+        <v>0.5824345146379045</v>
       </c>
       <c r="K66" t="n">
         <v>22</v>
@@ -6902,10 +6902,10 @@
       </c>
       <c r="P66" s="4" t="inlineStr"/>
       <c r="Q66" t="n">
-        <v>1940</v>
+        <v>1941</v>
       </c>
       <c r="R66" s="4" t="n">
-        <v>0.6721649484536083</v>
+        <v>0.6738794435857806</v>
       </c>
       <c r="S66" t="n">
         <v>22</v>
@@ -6958,10 +6958,10 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2183</v>
+        <v>2190</v>
       </c>
       <c r="J67" s="4" t="n">
-        <v>0.5945945945945946</v>
+        <v>0.5981735159817352</v>
       </c>
       <c r="K67" t="n">
         <v>30</v>
@@ -6982,10 +6982,10 @@
         <v>1</v>
       </c>
       <c r="Q67" t="n">
-        <v>2177</v>
+        <v>2184</v>
       </c>
       <c r="R67" s="4" t="n">
-        <v>0.6853468075333027</v>
+        <v>0.6872710622710623</v>
       </c>
       <c r="S67" t="n">
         <v>30</v>
@@ -7040,10 +7040,10 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1042</v>
+        <v>1049</v>
       </c>
       <c r="J68" s="4" t="n">
-        <v>0.54510556621881</v>
+        <v>0.553860819828408</v>
       </c>
       <c r="K68" t="n">
         <v>25</v>
@@ -7062,10 +7062,10 @@
       </c>
       <c r="P68" s="4" t="inlineStr"/>
       <c r="Q68" t="n">
-        <v>1035</v>
+        <v>1042</v>
       </c>
       <c r="R68" s="4" t="n">
-        <v>0.6473429951690821</v>
+        <v>0.6525911708253359</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7118,10 +7118,10 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1918</v>
+        <v>1916</v>
       </c>
       <c r="J69" s="4" t="n">
-        <v>0.5375391032325338</v>
+        <v>0.5443632567849687</v>
       </c>
       <c r="K69" t="n">
         <v>33</v>
@@ -7142,10 +7142,10 @@
         <v>1</v>
       </c>
       <c r="Q69" t="n">
-        <v>1904</v>
+        <v>1902</v>
       </c>
       <c r="R69" s="4" t="n">
-        <v>0.6486344537815126</v>
+        <v>0.655099894847529</v>
       </c>
       <c r="S69" t="n">
         <v>33</v>
@@ -7200,10 +7200,10 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2517</v>
+        <v>2521</v>
       </c>
       <c r="J70" s="4" t="n">
-        <v>0.5399284862932062</v>
+        <v>0.5450218167393891</v>
       </c>
       <c r="K70" t="n">
         <v>44</v>
@@ -7224,10 +7224,10 @@
         <v>1</v>
       </c>
       <c r="Q70" t="n">
-        <v>2500</v>
+        <v>2504</v>
       </c>
       <c r="R70" s="4" t="n">
-        <v>0.6536</v>
+        <v>0.6601437699680511</v>
       </c>
       <c r="S70" t="n">
         <v>44</v>
@@ -7282,10 +7282,10 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>660</v>
+        <v>644</v>
       </c>
       <c r="J71" s="4" t="n">
-        <v>0.5287878787878788</v>
+        <v>0.531055900621118</v>
       </c>
       <c r="K71" t="n">
         <v>5</v>
@@ -7304,10 +7304,10 @@
       </c>
       <c r="P71" s="4" t="inlineStr"/>
       <c r="Q71" t="n">
-        <v>657</v>
+        <v>641</v>
       </c>
       <c r="R71" s="4" t="n">
-        <v>0.6681887366818874</v>
+        <v>0.6708268330733229</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -7360,10 +7360,10 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1189</v>
+        <v>1186</v>
       </c>
       <c r="J72" s="4" t="n">
-        <v>0.5306980656013457</v>
+        <v>0.5354131534569984</v>
       </c>
       <c r="K72" t="n">
         <v>11</v>
@@ -7382,10 +7382,10 @@
       </c>
       <c r="P72" s="4" t="inlineStr"/>
       <c r="Q72" t="n">
-        <v>1184</v>
+        <v>1181</v>
       </c>
       <c r="R72" s="4" t="n">
-        <v>0.660472972972973</v>
+        <v>0.6663844199830652</v>
       </c>
       <c r="S72" t="n">
         <v>11</v>
@@ -7438,10 +7438,10 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1837</v>
+        <v>1832</v>
       </c>
       <c r="J73" s="4" t="n">
-        <v>0.5498094719651606</v>
+        <v>0.5567685589519651</v>
       </c>
       <c r="K73" t="n">
         <v>25</v>
@@ -7460,10 +7460,10 @@
       </c>
       <c r="P73" s="4" t="inlineStr"/>
       <c r="Q73" t="n">
-        <v>1828</v>
+        <v>1823</v>
       </c>
       <c r="R73" s="4" t="n">
-        <v>0.6717724288840262</v>
+        <v>0.6785518376302797</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -7516,10 +7516,10 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="J74" s="4" t="n">
-        <v>0.5786407766990291</v>
+        <v>0.580896686159844</v>
       </c>
       <c r="K74" t="n">
         <v>6</v>
@@ -7538,10 +7538,10 @@
       </c>
       <c r="P74" s="4" t="inlineStr"/>
       <c r="Q74" t="n">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="R74" s="4" t="n">
-        <v>0.6848249027237354</v>
+        <v>0.6875</v>
       </c>
       <c r="S74" t="n">
         <v>6</v>
@@ -7594,10 +7594,10 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="J75" s="4" t="n">
-        <v>0.5824817518248175</v>
+        <v>0.5847953216374269</v>
       </c>
       <c r="K75" t="n">
         <v>6</v>
@@ -7616,10 +7616,10 @@
       </c>
       <c r="P75" s="4" t="inlineStr"/>
       <c r="Q75" t="n">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="R75" s="4" t="n">
-        <v>0.6900584795321637</v>
+        <v>0.6925329428989752</v>
       </c>
       <c r="S75" t="n">
         <v>6</v>
@@ -7672,10 +7672,10 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="J76" s="4" t="n">
-        <v>0.5975935828877005</v>
+        <v>0.5997322623828648</v>
       </c>
       <c r="K76" t="n">
         <v>6</v>
@@ -7694,10 +7694,10 @@
       </c>
       <c r="P76" s="4" t="inlineStr"/>
       <c r="Q76" t="n">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="R76" s="4" t="n">
-        <v>0.6987951807228916</v>
+        <v>0.7010723860589813</v>
       </c>
       <c r="S76" t="n">
         <v>6</v>
@@ -7828,10 +7828,10 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="J78" s="4" t="n">
-        <v>0.6682027649769585</v>
+        <v>0.6685912240184757</v>
       </c>
       <c r="K78" t="n">
         <v>6</v>
@@ -7850,10 +7850,10 @@
       </c>
       <c r="P78" s="4" t="inlineStr"/>
       <c r="Q78" t="n">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="R78" s="4" t="n">
-        <v>0.7566320645905421</v>
+        <v>0.7572254335260116</v>
       </c>
       <c r="S78" t="n">
         <v>6</v>
@@ -7906,10 +7906,10 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1907</v>
+        <v>1905</v>
       </c>
       <c r="J79" s="4" t="n">
-        <v>0.6009438909281594</v>
+        <v>0.5994750656167979</v>
       </c>
       <c r="K79" t="n">
         <v>17</v>
@@ -7928,10 +7928,10 @@
       </c>
       <c r="P79" s="4" t="inlineStr"/>
       <c r="Q79" t="n">
-        <v>1907</v>
+        <v>1905</v>
       </c>
       <c r="R79" s="4" t="n">
-        <v>0.7094913476664919</v>
+        <v>0.7081364829396325</v>
       </c>
       <c r="S79" t="n">
         <v>17</v>
@@ -8062,10 +8062,10 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="J81" s="4" t="n">
-        <v>0.5665445665445665</v>
+        <v>0.5639464068209501</v>
       </c>
       <c r="K81" t="n">
         <v>4</v>
@@ -8084,10 +8084,10 @@
       </c>
       <c r="P81" s="4" t="inlineStr"/>
       <c r="Q81" t="n">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="R81" s="4" t="n">
-        <v>0.6727716727716728</v>
+        <v>0.6699147381242387</v>
       </c>
       <c r="S81" t="n">
         <v>4</v>
@@ -8140,10 +8140,10 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="J82" s="4" t="n">
-        <v>0.5826446280991735</v>
+        <v>0.5798180314309347</v>
       </c>
       <c r="K82" t="n">
         <v>8</v>
@@ -8162,10 +8162,10 @@
       </c>
       <c r="P82" s="4" t="inlineStr"/>
       <c r="Q82" t="n">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="R82" s="4" t="n">
-        <v>0.6834710743801653</v>
+        <v>0.6807278742762614</v>
       </c>
       <c r="S82" t="n">
         <v>8</v>
@@ -8218,10 +8218,10 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="J83" s="4" t="n">
-        <v>0.5260115606936416</v>
+        <v>0.5244956772334294</v>
       </c>
       <c r="K83" t="n">
         <v>5</v>
@@ -8242,10 +8242,10 @@
         <v>1</v>
       </c>
       <c r="Q83" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="R83" s="4" t="n">
-        <v>0.6231884057971014</v>
+        <v>0.6213872832369942</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -8327,7 +8327,7 @@
         <v>1195</v>
       </c>
       <c r="R84" s="4" t="n">
-        <v>0.6041841004184101</v>
+        <v>0.6033472803347281</v>
       </c>
       <c r="S84" t="n">
         <v>14</v>
@@ -8409,7 +8409,7 @@
         <v>1326</v>
       </c>
       <c r="R85" s="4" t="n">
-        <v>0.6070889894419306</v>
+        <v>0.6063348416289592</v>
       </c>
       <c r="S85" t="n">
         <v>19</v>
@@ -8647,7 +8647,7 @@
         <v>520</v>
       </c>
       <c r="R88" s="4" t="n">
-        <v>0.65</v>
+        <v>0.6480769230769231</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -8702,10 +8702,10 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="J89" s="4" t="n">
-        <v>0.4705882352941176</v>
+        <v>0.4706896551724138</v>
       </c>
       <c r="K89" t="n">
         <v>13</v>
@@ -8724,10 +8724,10 @@
       </c>
       <c r="P89" s="4" t="inlineStr"/>
       <c r="Q89" t="n">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="R89" s="4" t="n">
-        <v>0.5961871750433275</v>
+        <v>0.5941278065630398</v>
       </c>
       <c r="S89" t="n">
         <v>13</v>
@@ -8783,7 +8783,7 @@
         <v>1323</v>
       </c>
       <c r="J90" s="4" t="n">
-        <v>0.4829931972789115</v>
+        <v>0.4822373393801965</v>
       </c>
       <c r="K90" t="n">
         <v>28</v>
@@ -8807,7 +8807,7 @@
         <v>1322</v>
       </c>
       <c r="R90" s="4" t="n">
-        <v>0.602874432677761</v>
+        <v>0.6013615733736762</v>
       </c>
       <c r="S90" t="n">
         <v>28</v>
@@ -8862,10 +8862,10 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>2103</v>
+        <v>2108</v>
       </c>
       <c r="J91" s="4" t="n">
-        <v>0.4954826438421303</v>
+        <v>0.4943074003795067</v>
       </c>
       <c r="K91" t="n">
         <v>43</v>
@@ -8886,10 +8886,10 @@
         <v>1</v>
       </c>
       <c r="Q91" t="n">
-        <v>2101</v>
+        <v>2106</v>
       </c>
       <c r="R91" s="4" t="n">
-        <v>0.6178010471204188</v>
+        <v>0.6168091168091168</v>
       </c>
       <c r="S91" t="n">
         <v>43</v>

--- a/pattern_report.xlsx
+++ b/pattern_report.xlsx
@@ -13,8 +13,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'OZET'!$A$1:$B$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'BUGUN_SINYALLER'!$A$1:$Y$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'BUGUN_BENZER_HAREKET'!$A$1:$X$91</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'BUGUN_SINYALLER'!$A$1:$Y$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'BUGUN_BENZER_HAREKET'!$A$1:$X$73</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -485,7 +485,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>46225.33961270287</v>
+        <v>46225.44395755747</v>
       </c>
     </row>
     <row r="4">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
     </row>
     <row r="5">
@@ -505,7 +505,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>42480</v>
+        <v>42482</v>
       </c>
     </row>
     <row r="6">
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>46131</v>
+        <v>46133</v>
       </c>
     </row>
     <row r="7">
@@ -525,7 +525,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>46132</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="8">
@@ -535,7 +535,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
     </row>
     <row r="9">
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
@@ -579,7 +579,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>25542</v>
+        <v>25559</v>
       </c>
     </row>
     <row r="13">
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>25506</v>
+        <v>25530</v>
       </c>
     </row>
     <row r="14">
@@ -599,7 +599,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>796</v>
+        <v>737</v>
       </c>
     </row>
     <row r="15">
@@ -609,7 +609,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>786</v>
+        <v>727</v>
       </c>
     </row>
     <row r="16">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>222373</v>
+        <v>222473</v>
       </c>
     </row>
     <row r="17">
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>28948</v>
+        <v>28956</v>
       </c>
     </row>
     <row r="18">
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>18757</v>
+        <v>256</v>
       </c>
     </row>
     <row r="20">
@@ -708,7 +708,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y11"/>
+  <dimension ref="A1:Y9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -716,7 +716,7 @@
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
     <col width="23" customWidth="1" min="7" max="7"/>
     <col width="23" customWidth="1" min="8" max="8"/>
     <col width="24" customWidth="1" min="9" max="9"/>
@@ -867,11 +867,11 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AKSEN</t>
+          <t>AKBNK</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -886,38 +886,38 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>106</v>
+        <v>66.84999847412109</v>
       </c>
       <c r="G2" t="n">
-        <v>10.87866285760892</v>
+        <v>-2.551020464905951</v>
       </c>
       <c r="H2" t="n">
-        <v>15.09229289486322</v>
+        <v>-1.182561764543022</v>
       </c>
       <c r="I2" t="n">
-        <v>31.0259555014865</v>
+        <v>-9.047621123644767</v>
       </c>
       <c r="J2" t="n">
-        <v>4258</v>
+        <v>2380</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>0.5453264443400657</v>
+        <v>0.6600840336134454</v>
       </c>
       <c r="L2" t="n">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="M2" s="4" t="n">
-        <v>0.55</v>
+        <v>0.6551724137931034</v>
       </c>
       <c r="N2" t="n">
-        <v>97</v>
+        <v>63</v>
       </c>
       <c r="O2" s="4" t="n">
-        <v>0.6804123711340206</v>
+        <v>0.6349206349206349</v>
       </c>
       <c r="P2" t="n">
         <v>1</v>
@@ -926,22 +926,22 @@
         <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>4256</v>
+        <v>2380</v>
       </c>
       <c r="S2" s="4" t="n">
-        <v>0.6487312030075187</v>
+        <v>0.7546218487394958</v>
       </c>
       <c r="T2" t="n">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="U2" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.896551724137931</v>
       </c>
       <c r="V2" t="n">
-        <v>94</v>
+        <v>63</v>
       </c>
       <c r="W2" s="4" t="n">
-        <v>0.8191489361702128</v>
+        <v>0.6825396825396826</v>
       </c>
       <c r="X2" t="n">
         <v>1</v>
@@ -952,227 +952,223 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AKSEN</t>
+          <t>AKBNK</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SHOOTING_STAR</t>
+          <t>HAMMER</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Shooting Star</t>
+          <t>Hammer</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>106</v>
+        <v>66.84999847412109</v>
       </c>
       <c r="G3" t="n">
-        <v>10.87866285760892</v>
+        <v>-2.551020464905951</v>
       </c>
       <c r="H3" t="n">
-        <v>15.09229289486322</v>
+        <v>-1.182561764543022</v>
       </c>
       <c r="I3" t="n">
-        <v>31.0259555014865</v>
+        <v>-9.047621123644767</v>
       </c>
       <c r="J3" t="n">
-        <v>6039</v>
+        <v>3002</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>0.5423083291935751</v>
+        <v>0.6462358427714857</v>
       </c>
       <c r="L3" t="n">
-        <v>88</v>
+        <v>45</v>
       </c>
       <c r="M3" s="4" t="n">
-        <v>0.5568181818181818</v>
+        <v>0.7111111111111111</v>
       </c>
       <c r="N3" t="n">
-        <v>147</v>
+        <v>75</v>
       </c>
       <c r="O3" s="4" t="n">
-        <v>0.6802721088435374</v>
+        <v>0.6133333333333333</v>
       </c>
       <c r="P3" t="n">
         <v>1</v>
       </c>
       <c r="Q3" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>6033</v>
+        <v>3001</v>
       </c>
       <c r="S3" s="4" t="n">
-        <v>0.6530747555113542</v>
+        <v>0.7410863045651449</v>
       </c>
       <c r="T3" t="n">
-        <v>88</v>
+        <v>45</v>
       </c>
       <c r="U3" s="4" t="n">
-        <v>0.6931818181818182</v>
+        <v>0.8222222222222222</v>
       </c>
       <c r="V3" t="n">
-        <v>144</v>
+        <v>73</v>
       </c>
       <c r="W3" s="4" t="n">
-        <v>0.8125</v>
+        <v>0.6575342465753424</v>
       </c>
       <c r="X3" t="n">
         <v>1</v>
       </c>
       <c r="Y3" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BALSU</t>
+          <t>ASTOR</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>BEARISH_ENGULFING</t>
+          <t>HAMMER</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Bearish Engulfing</t>
+          <t>Hammer</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>16.20000076293945</v>
+        <v>300</v>
       </c>
       <c r="G4" t="n">
-        <v>0.309604616657766</v>
+        <v>-4.000000000000004</v>
       </c>
       <c r="H4" t="n">
-        <v>21.25749385661693</v>
+        <v>-5.660377358490565</v>
       </c>
       <c r="I4" t="n">
-        <v>-10.98901052835441</v>
+        <v>-5.511811023622048</v>
       </c>
       <c r="J4" t="n">
-        <v>4637</v>
+        <v>3002</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>0.5906836316583999</v>
+        <v>0.6462358427714857</v>
       </c>
       <c r="L4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.5</v>
       </c>
       <c r="N4" t="n">
-        <v>154</v>
+        <v>75</v>
       </c>
       <c r="O4" s="4" t="n">
-        <v>0.7402597402597403</v>
+        <v>0.6133333333333333</v>
       </c>
       <c r="P4" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q4" s="4" t="n">
-        <v>0.75</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q4" s="4" t="inlineStr"/>
       <c r="R4" t="n">
-        <v>4617</v>
+        <v>3001</v>
       </c>
       <c r="S4" s="4" t="n">
-        <v>0.6881091617933723</v>
+        <v>0.7410863045651449</v>
       </c>
       <c r="T4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U4" s="4" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.5</v>
       </c>
       <c r="V4" t="n">
-        <v>151</v>
+        <v>73</v>
       </c>
       <c r="W4" s="4" t="n">
-        <v>0.8211920529801324</v>
+        <v>0.6575342465753424</v>
       </c>
       <c r="X4" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y4" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Y4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BRSAN</t>
+          <t>GUBRF</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DOJI</t>
+          <t>MORNING_STAR</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Doji</t>
+          <t>Morning Star</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>550</v>
+        <v>427</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1.124925991711079</v>
       </c>
       <c r="H5" t="n">
-        <v>2.611940298507465</v>
+        <v>3.76670716889429</v>
       </c>
       <c r="I5" t="n">
-        <v>-3.083700440528636</v>
+        <v>-7.224334600760452</v>
       </c>
       <c r="J5" t="n">
-        <v>4258</v>
+        <v>938</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>0.5453264443400657</v>
+        <v>0.6567164179104478</v>
       </c>
       <c r="L5" t="n">
-        <v>69</v>
+        <v>12</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>0.5362318840579711</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="N5" t="n">
-        <v>97</v>
+        <v>33</v>
       </c>
       <c r="O5" s="4" t="n">
-        <v>0.6804123711340206</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="P5" t="n">
         <v>1</v>
@@ -1181,22 +1177,22 @@
         <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>4256</v>
+        <v>938</v>
       </c>
       <c r="S5" s="4" t="n">
-        <v>0.6487312030075187</v>
+        <v>0.7547974413646056</v>
       </c>
       <c r="T5" t="n">
-        <v>69</v>
+        <v>12</v>
       </c>
       <c r="U5" s="4" t="n">
-        <v>0.5797101449275363</v>
+        <v>1</v>
       </c>
       <c r="V5" t="n">
-        <v>94</v>
+        <v>33</v>
       </c>
       <c r="W5" s="4" t="n">
-        <v>0.8191489361702128</v>
+        <v>0.696969696969697</v>
       </c>
       <c r="X5" t="n">
         <v>1</v>
@@ -1207,21 +1203,21 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BSOKE</t>
+          <t>OBAMS</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>BEARISH_ENGULFING</t>
+          <t>DOJI</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Bearish Engulfing</t>
+          <t>Doji</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1230,154 +1226,154 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>36.81999969482422</v>
+        <v>5.190000057220459</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6010962564894085</v>
+        <v>-2.808990469686379</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7662801649736428</v>
+        <v>0.5813994320832405</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.021508226671353</v>
+        <v>-10.97769939727128</v>
       </c>
       <c r="J6" t="n">
-        <v>4637</v>
+        <v>4268</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.5906836316583999</v>
+        <v>0.545688847235239</v>
       </c>
       <c r="L6" t="n">
-        <v>70</v>
+        <v>6</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.5</v>
       </c>
       <c r="N6" t="n">
-        <v>154</v>
+        <v>81</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.7402597402597403</v>
+        <v>0.6172839506172839</v>
       </c>
       <c r="P6" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q6" s="4" t="n">
-        <v>0.5</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q6" s="4" t="inlineStr"/>
       <c r="R6" t="n">
-        <v>4617</v>
+        <v>4256</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>0.6881091617933723</v>
+        <v>0.6482612781954887</v>
       </c>
       <c r="T6" t="n">
-        <v>70</v>
+        <v>6</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>0.6857142857142857</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="V6" t="n">
-        <v>151</v>
+        <v>78</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>0.8211920529801324</v>
+        <v>0.7564102564102564</v>
       </c>
       <c r="X6" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y6" s="4" t="n">
-        <v>0.5</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Y6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DOAS</t>
+          <t>PGSUS</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DOJI</t>
+          <t>HAMMER</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Doji</t>
+          <t>Hammer</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>185</v>
+        <v>163.5</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5434782608695565</v>
+        <v>-2.504470497717692</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.5376344086021501</v>
+        <v>-1.148726702900293</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.7510697115483023</v>
+        <v>-6.4645325254439</v>
       </c>
       <c r="J7" t="n">
-        <v>4258</v>
+        <v>3002</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.5453264443400657</v>
+        <v>0.6462358427714857</v>
       </c>
       <c r="L7" t="n">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="N7" t="n">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.6804123711340206</v>
+        <v>0.6133333333333333</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Q7" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="R7" t="n">
-        <v>4256</v>
+        <v>3001</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>0.6487312030075187</v>
+        <v>0.7410863045651449</v>
       </c>
       <c r="T7" t="n">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>0.8245614035087719</v>
+        <v>0.8095238095238095</v>
       </c>
       <c r="V7" t="n">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>0.8191489361702128</v>
+        <v>0.6575342465753424</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Y7" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>GUBRF</t>
+          <t>THYAO</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1396,16 +1392,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>410.25</v>
+        <v>318.5</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.7259528130671544</v>
+        <v>-3.48484848484848</v>
       </c>
       <c r="H8" t="n">
-        <v>-6.228571428571428</v>
+        <v>-4.497751124437777</v>
       </c>
       <c r="I8" t="n">
-        <v>-10.0328947368421</v>
+        <v>-8.213256484149856</v>
       </c>
       <c r="J8" t="n">
         <v>3002</v>
@@ -1414,22 +1410,22 @@
         <v>0.6462358427714857</v>
       </c>
       <c r="L8" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.6944444444444444</v>
+        <v>0.6785714285714286</v>
       </c>
       <c r="N8" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.6164383561643836</v>
+        <v>0.6133333333333333</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>3001</v>
@@ -1438,31 +1434,29 @@
         <v>0.7410863045651449</v>
       </c>
       <c r="T8" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>0.8611111111111112</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="V8" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>0.6527777777777778</v>
+        <v>0.6575342465753424</v>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y8" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Y8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ODAS</t>
+          <t>TKFEN</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1481,234 +1475,68 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>8.380000114440918</v>
+        <v>144.3000030517578</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.758494996787363</v>
+        <v>0.9090930431872923</v>
       </c>
       <c r="H9" t="n">
-        <v>1.08564720147204</v>
+        <v>1.763046506485244</v>
       </c>
       <c r="I9" t="n">
-        <v>3.456786664007372</v>
+        <v>7.286247622124775</v>
       </c>
       <c r="J9" t="n">
-        <v>4637</v>
+        <v>4639</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.5906836316583999</v>
+        <v>0.5906445354602285</v>
       </c>
       <c r="L9" t="n">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.6818181818181818</v>
+        <v>0.7222222222222222</v>
       </c>
       <c r="N9" t="n">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.7402597402597403</v>
+        <v>0.7266187050359713</v>
       </c>
       <c r="P9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q9" s="4" t="n">
         <v>1</v>
       </c>
       <c r="R9" t="n">
-        <v>4617</v>
+        <v>4636</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>0.6881091617933723</v>
+        <v>0.6857204486626403</v>
       </c>
       <c r="T9" t="n">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="V9" t="n">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>0.8211920529801324</v>
+        <v>0.8161764705882353</v>
       </c>
       <c r="X9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y9" s="4" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="3" t="n">
-        <v>46223</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>THYAO</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>HAMMER</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Hammer</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>328</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0.6134969325153339</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-4.789550072568938</v>
-      </c>
-      <c r="I10" t="n">
-        <v>-1.796407185628746</v>
-      </c>
-      <c r="J10" t="n">
-        <v>3002</v>
-      </c>
-      <c r="K10" s="4" t="n">
-        <v>0.6462358427714857</v>
-      </c>
-      <c r="L10" t="n">
-        <v>28</v>
-      </c>
-      <c r="M10" s="4" t="n">
-        <v>0.6785714285714286</v>
-      </c>
-      <c r="N10" t="n">
-        <v>73</v>
-      </c>
-      <c r="O10" s="4" t="n">
-        <v>0.6164383561643836</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="4" t="inlineStr"/>
-      <c r="R10" t="n">
-        <v>3001</v>
-      </c>
-      <c r="S10" s="4" t="n">
-        <v>0.7410863045651449</v>
-      </c>
-      <c r="T10" t="n">
-        <v>28</v>
-      </c>
-      <c r="U10" s="4" t="n">
-        <v>0.7142857142857143</v>
-      </c>
-      <c r="V10" t="n">
-        <v>72</v>
-      </c>
-      <c r="W10" s="4" t="n">
-        <v>0.6527777777777778</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" s="4" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="n">
-        <v>46223</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>VESTL</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>SHOOTING_STAR</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Shooting Star</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>SHORT</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>25.15999984741211</v>
-      </c>
-      <c r="G11" t="n">
-        <v>-3.379420265651756</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-4.769115159891335</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0.9630809405433149</v>
-      </c>
-      <c r="J11" t="n">
-        <v>6039</v>
-      </c>
-      <c r="K11" s="4" t="n">
-        <v>0.5423083291935751</v>
-      </c>
-      <c r="L11" t="n">
-        <v>107</v>
-      </c>
-      <c r="M11" s="4" t="n">
-        <v>0.5700934579439252</v>
-      </c>
-      <c r="N11" t="n">
-        <v>147</v>
-      </c>
-      <c r="O11" s="4" t="n">
-        <v>0.6802721088435374</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>6033</v>
-      </c>
-      <c r="S11" s="4" t="n">
-        <v>0.6530747555113542</v>
-      </c>
-      <c r="T11" t="n">
-        <v>107</v>
-      </c>
-      <c r="U11" s="4" t="n">
-        <v>0.6728971962616822</v>
-      </c>
-      <c r="V11" t="n">
-        <v>144</v>
-      </c>
-      <c r="W11" s="4" t="n">
-        <v>0.8125</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y11" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:Y11"/>
+  <autoFilter ref="A1:Y9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1719,7 +1547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X91"/>
+  <dimension ref="A1:X73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -1872,11 +1700,11 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AKSEN</t>
+          <t>AKBNK</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1886,7 +1714,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -1896,52 +1724,52 @@
         <v>2</v>
       </c>
       <c r="G2" t="n">
-        <v>10.87866285760892</v>
+        <v>-2.551020464905951</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>[10,12)</t>
+          <t>[-4,-2)</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>104</v>
+        <v>535</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>0.6634615384615384</v>
+        <v>0.6841121495327103</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L2" s="4" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="M2" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="N2" s="4" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
       </c>
       <c r="P2" s="4" t="inlineStr"/>
       <c r="Q2" t="n">
-        <v>104</v>
+        <v>535</v>
       </c>
       <c r="R2" s="4" t="n">
-        <v>0.7211538461538461</v>
+        <v>0.7700934579439253</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="T2" s="4" t="n">
-        <v>0</v>
+        <v>0.875</v>
       </c>
       <c r="U2" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="V2" s="4" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.55</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
@@ -1950,11 +1778,11 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AKSEN</t>
+          <t>AKBNK</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1964,7 +1792,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -1974,52 +1802,52 @@
         <v>4</v>
       </c>
       <c r="G3" t="n">
-        <v>10.87866285760892</v>
+        <v>-2.551020464905951</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>[8,12)</t>
+          <t>[-4,0)</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>305</v>
+        <v>1167</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>0.6754098360655738</v>
+        <v>0.6306769494430163</v>
       </c>
       <c r="K3" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="M3" t="n">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="N3" s="4" t="n">
-        <v>0.4545454545454545</v>
+        <v>0.5897435897435898</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
       </c>
       <c r="P3" s="4" t="inlineStr"/>
       <c r="Q3" t="n">
-        <v>305</v>
+        <v>1167</v>
       </c>
       <c r="R3" s="4" t="n">
-        <v>0.7213114754098361</v>
+        <v>0.7369323050556984</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T3" s="4" t="n">
-        <v>0.6</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="U3" t="n">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="V3" s="4" t="n">
-        <v>0.4545454545454545</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
@@ -2028,11 +1856,11 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>AKSEN</t>
+          <t>AKBNK</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2042,7 +1870,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -2052,65 +1880,69 @@
         <v>6</v>
       </c>
       <c r="G4" t="n">
-        <v>10.87866285760892</v>
+        <v>-2.551020464905951</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>[6,12)</t>
+          <t>[-6,0)</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>606</v>
+        <v>1466</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>0.6221122112211221</v>
+        <v>0.6596180081855388</v>
       </c>
       <c r="K4" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.7058823529411765</v>
       </c>
       <c r="M4" t="n">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>0.5</v>
+        <v>0.5909090909090909</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="P4" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="Q4" t="n">
-        <v>606</v>
+        <v>1466</v>
       </c>
       <c r="R4" s="4" t="n">
-        <v>0.6897689768976898</v>
+        <v>0.7578444747612552</v>
       </c>
       <c r="S4" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="T4" s="4" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.8823529411764706</v>
       </c>
       <c r="U4" t="n">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="V4" s="4" t="n">
-        <v>0.5625</v>
+        <v>0.6590909090909091</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="X4" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AKSEN</t>
+          <t>AKBNK</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2120,7 +1952,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -2130,52 +1962,52 @@
         <v>2</v>
       </c>
       <c r="G5" t="n">
-        <v>15.09229289486322</v>
+        <v>-1.182561764543022</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>[14,16)</t>
+          <t>[-2,0)</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>88</v>
+        <v>445</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>0.6363636363636364</v>
+        <v>0.5573033707865168</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L5" s="4" t="n">
         <v>1</v>
       </c>
       <c r="M5" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="N5" s="4" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.7272727272727273</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" s="4" t="inlineStr"/>
       <c r="Q5" t="n">
-        <v>88</v>
+        <v>445</v>
       </c>
       <c r="R5" s="4" t="n">
-        <v>0.7159090909090909</v>
+        <v>0.6853932584269663</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T5" s="4" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="V5" s="4" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.7272727272727273</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
@@ -2184,11 +2016,11 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AKSEN</t>
+          <t>AKBNK</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2198,7 +2030,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -2208,52 +2040,52 @@
         <v>4</v>
       </c>
       <c r="G6" t="n">
-        <v>15.09229289486322</v>
+        <v>-1.182561764543022</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>[12,16)</t>
+          <t>[-4,0)</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>234</v>
+        <v>1045</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.594017094017094</v>
+        <v>0.5933014354066986</v>
       </c>
       <c r="K6" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="M6" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.6</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" s="4" t="inlineStr"/>
       <c r="Q6" t="n">
-        <v>234</v>
+        <v>1045</v>
       </c>
       <c r="R6" s="4" t="n">
+        <v>0.6976076555023923</v>
+      </c>
+      <c r="S6" t="n">
+        <v>14</v>
+      </c>
+      <c r="T6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>30</v>
+      </c>
+      <c r="V6" s="4" t="n">
         <v>0.6666666666666666</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3</v>
-      </c>
-      <c r="T6" s="4" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="U6" t="n">
-        <v>15</v>
-      </c>
-      <c r="V6" s="4" t="n">
-        <v>0.6</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
@@ -2262,11 +2094,11 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AKSEN</t>
+          <t>AKBNK</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2276,7 +2108,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -2286,52 +2118,52 @@
         <v>6</v>
       </c>
       <c r="G7" t="n">
-        <v>15.09229289486322</v>
+        <v>-1.182561764543022</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>[12,18)</t>
+          <t>[-6,0)</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>290</v>
+        <v>1470</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.6172413793103448</v>
+        <v>0.617687074829932</v>
       </c>
       <c r="K7" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.75</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="M7" t="n">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.6111111111111112</v>
+        <v>0.5869565217391305</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" s="4" t="inlineStr"/>
       <c r="Q7" t="n">
-        <v>290</v>
+        <v>1470</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>0.6931034482758621</v>
+        <v>0.7224489795918367</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6521739130434783</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
@@ -2340,11 +2172,11 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AKSEN</t>
+          <t>AKBNK</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2354,7 +2186,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -2364,48 +2196,52 @@
         <v>2</v>
       </c>
       <c r="G8" t="n">
-        <v>31.0259555014865</v>
+        <v>-9.047621123644767</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>[30,32)</t>
+          <t>[-10,-8)</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>14</v>
+        <v>188</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.7857142857142857</v>
+        <v>0.6968085106382979</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L8" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="M8" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>1</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" s="4" t="inlineStr"/>
       <c r="Q8" t="n">
-        <v>14</v>
+        <v>188</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>0.9285714285714286</v>
+        <v>0.7819148936170213</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="T8" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="U8" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>1</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
@@ -2414,11 +2250,11 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AKSEN</t>
+          <t>AKBNK</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2428,7 +2264,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -2438,52 +2274,52 @@
         <v>4</v>
       </c>
       <c r="G9" t="n">
-        <v>31.0259555014865</v>
+        <v>-9.047621123644767</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>[28,32)</t>
+          <t>[-12,-8)</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>40</v>
+        <v>340</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.75</v>
+        <v>0.7264705882352941</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>1</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
       <c r="P9" s="4" t="inlineStr"/>
       <c r="Q9" t="n">
-        <v>40</v>
+        <v>340</v>
       </c>
       <c r="R9" s="4" t="n">
         <v>0.8</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T9" s="4" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>1</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
@@ -2492,11 +2328,11 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AKSEN</t>
+          <t>AKBNK</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2506,7 +2342,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -2516,52 +2352,52 @@
         <v>6</v>
       </c>
       <c r="G10" t="n">
-        <v>31.0259555014865</v>
+        <v>-9.047621123644767</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>[30,36)</t>
+          <t>[-12,-6)</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>45</v>
+        <v>585</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.7333333333333333</v>
+        <v>0.6991452991452991</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>1</v>
+        <v>0.375</v>
       </c>
       <c r="M10" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>1</v>
+        <v>0.4761904761904762</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
       <c r="P10" s="4" t="inlineStr"/>
       <c r="Q10" t="n">
-        <v>45</v>
+        <v>585</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>0.8222222222222222</v>
+        <v>0.7948717948717948</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="U10" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>1</v>
+        <v>0.4761904761904762</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
@@ -2570,21 +2406,21 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AKSEN</t>
+          <t>AKBNK</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SHOOTING_STAR</t>
+          <t>HAMMER</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -2594,52 +2430,52 @@
         <v>2</v>
       </c>
       <c r="G11" t="n">
-        <v>10.87866285760892</v>
+        <v>-2.551020464905951</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>[10,12)</t>
+          <t>[-4,-2)</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>140</v>
+        <v>657</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.6642857142857143</v>
+        <v>0.6590563165905632</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>1</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="M11" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7222222222222222</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
       </c>
       <c r="P11" s="4" t="inlineStr"/>
       <c r="Q11" t="n">
-        <v>140</v>
+        <v>657</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>0.7571428571428571</v>
+        <v>0.7473363774733638</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>1</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="U11" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>1</v>
+        <v>0.7222222222222222</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
@@ -2648,21 +2484,21 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>AKSEN</t>
+          <t>AKBNK</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SHOOTING_STAR</t>
+          <t>HAMMER</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -2672,75 +2508,79 @@
         <v>4</v>
       </c>
       <c r="G12" t="n">
-        <v>10.87866285760892</v>
+        <v>-2.551020464905951</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>[8,12)</t>
+          <t>[-4,0)</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>382</v>
+        <v>1423</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.6465968586387435</v>
+        <v>0.607167955024596</v>
       </c>
       <c r="K12" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.4</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="M12" t="n">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.4545454545454545</v>
+        <v>0.6842105263157895</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="P12" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="Q12" t="n">
-        <v>382</v>
+        <v>1423</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>0.725130890052356</v>
+        <v>0.7118763176387913</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>0.4</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="U12" t="n">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.7027027027027027</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="X12" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>AKSEN</t>
+          <t>AKBNK</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SHOOTING_STAR</t>
+          <t>HAMMER</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -2750,75 +2590,79 @@
         <v>6</v>
       </c>
       <c r="G13" t="n">
-        <v>10.87866285760892</v>
+        <v>-2.551020464905951</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>[6,12)</t>
+          <t>[-6,0)</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>836</v>
+        <v>1828</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.631578947368421</v>
+        <v>0.6280087527352297</v>
       </c>
       <c r="K13" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.5</v>
+        <v>0.68</v>
       </c>
       <c r="M13" t="n">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.4761904761904762</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="P13" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="Q13" t="n">
-        <v>836</v>
+        <v>1828</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.7286652078774617</v>
       </c>
       <c r="S13" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="U13" t="n">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>0.6190476190476191</v>
+        <v>0.7045454545454546</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="X13" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>AKSEN</t>
+          <t>AKBNK</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>SHOOTING_STAR</t>
+          <t>HAMMER</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2828,52 +2672,52 @@
         <v>2</v>
       </c>
       <c r="G14" t="n">
-        <v>15.09229289486322</v>
+        <v>-1.182561764543022</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>[14,16)</t>
+          <t>[-2,0)</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>124</v>
+        <v>612</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.6451612903225806</v>
+        <v>0.5473856209150327</v>
       </c>
       <c r="K14" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8181818181818182</v>
       </c>
       <c r="M14" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>1</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
       </c>
       <c r="P14" s="4" t="inlineStr"/>
       <c r="Q14" t="n">
-        <v>124</v>
+        <v>612</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>0.75</v>
+        <v>0.6699346405228758</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8181818181818182</v>
       </c>
       <c r="U14" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>1</v>
+        <v>0.6363636363636364</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
@@ -2882,21 +2726,21 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>AKSEN</t>
+          <t>AKBNK</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SHOOTING_STAR</t>
+          <t>HAMMER</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2906,75 +2750,79 @@
         <v>4</v>
       </c>
       <c r="G15" t="n">
-        <v>15.09229289486322</v>
+        <v>-1.182561764543022</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>[12,16)</t>
+          <t>[-4,0)</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>342</v>
+        <v>1342</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.6228070175438597</v>
+        <v>0.5737704918032787</v>
       </c>
       <c r="K15" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.76</v>
       </c>
       <c r="M15" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.7333333333333333</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="P15" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="Q15" t="n">
-        <v>342</v>
+        <v>1342</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>0.7105263157894737</v>
+        <v>0.6900149031296572</v>
       </c>
       <c r="S15" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.88</v>
       </c>
       <c r="U15" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>0.8</v>
+        <v>0.6774193548387096</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="X15" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>AKSEN</t>
+          <t>AKBNK</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>SHOOTING_STAR</t>
+          <t>HAMMER</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2984,75 +2832,79 @@
         <v>6</v>
       </c>
       <c r="G16" t="n">
-        <v>15.09229289486322</v>
+        <v>-1.182561764543022</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>[12,18)</t>
+          <t>[-6,0)</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>432</v>
+        <v>1905</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.625</v>
+        <v>0.5994750656167979</v>
       </c>
       <c r="K16" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.625</v>
+        <v>0.78125</v>
       </c>
       <c r="M16" t="n">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.7647058823529411</v>
+        <v>0.6</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="P16" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="Q16" t="n">
-        <v>432</v>
+        <v>1905</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>0.7106481481481481</v>
+        <v>0.7081364829396325</v>
       </c>
       <c r="S16" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="U16" t="n">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>0.8235294117647058</v>
+        <v>0.673469387755102</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="X16" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>AKSEN</t>
+          <t>AKBNK</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SHOOTING_STAR</t>
+          <t>HAMMER</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -3062,45 +2914,53 @@
         <v>2</v>
       </c>
       <c r="G17" t="n">
-        <v>31.0259555014865</v>
+        <v>-9.047621123644767</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>[30,32)</t>
+          <t>[-10,-8)</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>35</v>
+        <v>251</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.6</v>
+        <v>0.7370517928286853</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" s="4" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="L17" s="4" t="n">
+        <v>0.75</v>
+      </c>
       <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" s="4" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="N17" s="4" t="n">
+        <v>0.5714285714285714</v>
+      </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" s="4" t="inlineStr"/>
       <c r="Q17" t="n">
-        <v>35</v>
+        <v>251</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>0.6857142857142857</v>
+        <v>0.8406374501992032</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" s="4" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="T17" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="4" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="V17" s="4" t="n">
+        <v>0.5714285714285714</v>
+      </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
@@ -3108,21 +2968,21 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>AKSEN</t>
+          <t>AKBNK</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>SHOOTING_STAR</t>
+          <t>HAMMER</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -3132,67 +2992,79 @@
         <v>4</v>
       </c>
       <c r="G18" t="n">
-        <v>31.0259555014865</v>
+        <v>-9.047621123644767</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>[28,32)</t>
+          <t>[-12,-8)</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>73</v>
+        <v>439</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.6438356164383562</v>
+        <v>0.744874715261959</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" s="4" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="L18" s="4" t="n">
+        <v>0.8333333333333334</v>
+      </c>
       <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" s="4" t="inlineStr"/>
+        <v>14</v>
+      </c>
+      <c r="N18" s="4" t="n">
+        <v>0.5714285714285714</v>
+      </c>
       <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="P18" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="Q18" t="n">
-        <v>73</v>
+        <v>438</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>0.7123287671232876</v>
+        <v>0.8310502283105022</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" s="4" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="T18" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" s="4" t="inlineStr"/>
+        <v>13</v>
+      </c>
+      <c r="V18" s="4" t="n">
+        <v>0.5384615384615384</v>
+      </c>
       <c r="W18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X18" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="X18" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>AKSEN</t>
+          <t>AKBNK</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SHOOTING_STAR</t>
+          <t>HAMMER</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -3202,67 +3074,79 @@
         <v>6</v>
       </c>
       <c r="G19" t="n">
-        <v>31.0259555014865</v>
+        <v>-9.047621123644767</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>[30,36)</t>
+          <t>[-12,-6)</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>63</v>
+        <v>777</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.6782496782496783</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" s="4" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="L19" s="4" t="n">
+        <v>0.7777777777777778</v>
+      </c>
       <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" s="4" t="inlineStr"/>
+        <v>22</v>
+      </c>
+      <c r="N19" s="4" t="n">
+        <v>0.5454545454545454</v>
+      </c>
       <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="P19" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="Q19" t="n">
-        <v>63</v>
+        <v>776</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>0.6825396825396826</v>
+        <v>0.7822164948453608</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" s="4" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="T19" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="4" t="inlineStr"/>
+        <v>21</v>
+      </c>
+      <c r="V19" s="4" t="n">
+        <v>0.5238095238095238</v>
+      </c>
       <c r="W19" t="n">
-        <v>0</v>
-      </c>
-      <c r="X19" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="X19" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BALSU</t>
+          <t>ASTOR</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>BEARISH_ENGULFING</t>
+          <t>HAMMER</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -3272,52 +3156,52 @@
         <v>2</v>
       </c>
       <c r="G20" t="n">
-        <v>0.309604616657766</v>
+        <v>-4.000000000000004</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>[0,2)</t>
+          <t>[-6,-4)</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1199</v>
+        <v>405</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.5312760633861552</v>
+        <v>0.7012345679012346</v>
       </c>
       <c r="K20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" t="n">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.7692307692307693</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
       </c>
       <c r="P20" s="4" t="inlineStr"/>
       <c r="Q20" t="n">
-        <v>1189</v>
+        <v>405</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>0.6593776282590412</v>
+        <v>0.7876543209876543</v>
       </c>
       <c r="S20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T20" s="4" t="n">
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>0.8157894736842105</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
@@ -3326,21 +3210,21 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BALSU</t>
+          <t>ASTOR</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>BEARISH_ENGULFING</t>
+          <t>HAMMER</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -3350,79 +3234,75 @@
         <v>4</v>
       </c>
       <c r="G21" t="n">
-        <v>0.309604616657766</v>
+        <v>-4.000000000000004</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>[0,4)</t>
+          <t>[-8,-4)</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1817</v>
+        <v>606</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.5465052283984591</v>
+        <v>0.7392739273927392</v>
       </c>
       <c r="K21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" t="n">
-        <v>58</v>
+        <v>12</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.7413793103448276</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="O21" t="n">
-        <v>2</v>
-      </c>
-      <c r="P21" s="4" t="n">
-        <v>0.5</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P21" s="4" t="inlineStr"/>
       <c r="Q21" t="n">
-        <v>1804</v>
+        <v>606</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>0.6657427937915743</v>
+        <v>0.8201320132013201</v>
       </c>
       <c r="S21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T21" s="4" t="n">
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>57</v>
+        <v>12</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>0.8070175438596491</v>
+        <v>0.75</v>
       </c>
       <c r="W21" t="n">
-        <v>2</v>
-      </c>
-      <c r="X21" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="X21" s="4" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BALSU</t>
+          <t>ASTOR</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>BEARISH_ENGULFING</t>
+          <t>HAMMER</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -3432,79 +3312,75 @@
         <v>6</v>
       </c>
       <c r="G22" t="n">
-        <v>0.309604616657766</v>
+        <v>-4.000000000000004</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>[0,6)</t>
+          <t>[-6,0)</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2046</v>
+        <v>1828</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.552297165200391</v>
+        <v>0.6280087527352297</v>
       </c>
       <c r="K22" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="M22" t="n">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.7352941176470589</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="O22" t="n">
-        <v>2</v>
-      </c>
-      <c r="P22" s="4" t="n">
-        <v>0.5</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P22" s="4" t="inlineStr"/>
       <c r="Q22" t="n">
-        <v>2032</v>
+        <v>1828</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>0.6692913385826772</v>
+        <v>0.7286652078774617</v>
       </c>
       <c r="S22" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="U22" t="n">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>0.7910447761194029</v>
+        <v>0.7045454545454546</v>
       </c>
       <c r="W22" t="n">
-        <v>2</v>
-      </c>
-      <c r="X22" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="X22" s="4" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BALSU</t>
+          <t>ASTOR</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>BEARISH_ENGULFING</t>
+          <t>HAMMER</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -3514,48 +3390,48 @@
         <v>2</v>
       </c>
       <c r="G23" t="n">
-        <v>21.25749385661693</v>
+        <v>-5.660377358490565</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>[20,22)</t>
+          <t>[-6,-4)</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>14</v>
+        <v>563</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.6607460035523979</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" s="4" t="inlineStr"/>
       <c r="M23" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0</v>
+        <v>0.5789473684210527</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
       </c>
       <c r="P23" s="4" t="inlineStr"/>
       <c r="Q23" t="n">
-        <v>14</v>
+        <v>563</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.7513321492007105</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
       </c>
       <c r="T23" s="4" t="inlineStr"/>
       <c r="U23" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
@@ -3564,21 +3440,21 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BALSU</t>
+          <t>ASTOR</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>BEARISH_ENGULFING</t>
+          <t>HAMMER</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -3588,48 +3464,52 @@
         <v>4</v>
       </c>
       <c r="G24" t="n">
-        <v>21.25749385661693</v>
+        <v>-5.660377358490565</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>[20,24)</t>
+          <t>[-8,-4)</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>23</v>
+        <v>866</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0.7826086956521739</v>
+        <v>0.6685912240184757</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L24" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="M24" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0</v>
+        <v>0.5882352941176471</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
       </c>
       <c r="P24" s="4" t="inlineStr"/>
       <c r="Q24" t="n">
-        <v>23</v>
+        <v>865</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>0.7826086956521739</v>
+        <v>0.7572254335260116</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="T24" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="U24" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>0</v>
+        <v>0.625</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
@@ -3638,21 +3518,21 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BALSU</t>
+          <t>ASTOR</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>BEARISH_ENGULFING</t>
+          <t>HAMMER</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -3662,48 +3542,52 @@
         <v>6</v>
       </c>
       <c r="G25" t="n">
-        <v>21.25749385661693</v>
+        <v>-5.660377358490565</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>[18,24)</t>
+          <t>[-6,0)</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>46</v>
+        <v>1905</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.6956521739130435</v>
+        <v>0.5994750656167979</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" s="4" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="L25" s="4" t="n">
+        <v>0.6</v>
+      </c>
       <c r="M25" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
       </c>
       <c r="P25" s="4" t="inlineStr"/>
       <c r="Q25" t="n">
-        <v>46</v>
+        <v>1905</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>0.6956521739130435</v>
+        <v>0.7081364829396325</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" s="4" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="T25" s="4" t="n">
+        <v>0.6</v>
+      </c>
       <c r="U25" t="n">
-        <v>2</v>
+        <v>49</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>0.5</v>
+        <v>0.673469387755102</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
@@ -3712,21 +3596,21 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>BALSU</t>
+          <t>ASTOR</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>BEARISH_ENGULFING</t>
+          <t>HAMMER</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -3736,45 +3620,53 @@
         <v>2</v>
       </c>
       <c r="G26" t="n">
-        <v>-10.98901052835441</v>
+        <v>-5.511811023622048</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>[-12,-10)</t>
+          <t>[-6,-4)</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>21</v>
+        <v>388</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6134020618556701</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L26" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" s="4" t="inlineStr"/>
+        <v>16</v>
+      </c>
+      <c r="N26" s="4" t="n">
+        <v>0.625</v>
+      </c>
       <c r="O26" t="n">
         <v>0</v>
       </c>
       <c r="P26" s="4" t="inlineStr"/>
       <c r="Q26" t="n">
-        <v>21</v>
+        <v>388</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7036082474226805</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="T26" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" s="4" t="inlineStr"/>
+        <v>16</v>
+      </c>
+      <c r="V26" s="4" t="n">
+        <v>0.6875</v>
+      </c>
       <c r="W26" t="n">
         <v>0</v>
       </c>
@@ -3782,21 +3674,21 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>BALSU</t>
+          <t>ASTOR</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>BEARISH_ENGULFING</t>
+          <t>HAMMER</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -3806,48 +3698,52 @@
         <v>4</v>
       </c>
       <c r="G27" t="n">
-        <v>-10.98901052835441</v>
+        <v>-5.511811023622048</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>[-12,-8)</t>
+          <t>[-8,-4)</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>44</v>
+        <v>726</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.6033057851239669</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L27" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="M27" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>1</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
       </c>
       <c r="P27" s="4" t="inlineStr"/>
       <c r="Q27" t="n">
-        <v>44</v>
+        <v>726</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>0.7727272727272727</v>
+        <v>0.7107438016528925</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="T27" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="U27" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>1</v>
+        <v>0.625</v>
       </c>
       <c r="W27" t="n">
         <v>0</v>
@@ -3856,21 +3752,21 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>BALSU</t>
+          <t>ASTOR</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>BEARISH_ENGULFING</t>
+          <t>HAMMER</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -3880,52 +3776,52 @@
         <v>6</v>
       </c>
       <c r="G28" t="n">
-        <v>-10.98901052835441</v>
+        <v>-5.511811023622048</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>[-12,-6)</t>
+          <t>[-6,0)</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>104</v>
+        <v>1209</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>0.7115384615384616</v>
+        <v>0.5798180314309347</v>
       </c>
       <c r="K28" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="M28" t="n">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.6176470588235294</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
       </c>
       <c r="P28" s="4" t="inlineStr"/>
       <c r="Q28" t="n">
-        <v>104</v>
+        <v>1209</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>0.7884615384615384</v>
+        <v>0.6807278742762614</v>
       </c>
       <c r="S28" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="U28" t="n">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="W28" t="n">
         <v>0</v>
@@ -3934,21 +3830,21 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>BRSAN</t>
+          <t>GUBRF</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>DOJI</t>
+          <t>MORNING_STAR</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -3958,7 +3854,7 @@
         <v>2</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>1.124925991711079</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -3966,44 +3862,44 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1058</v>
+        <v>382</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>0.4962192816635161</v>
+        <v>0.6308900523560209</v>
       </c>
       <c r="K29" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="L29" s="4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="M29" t="n">
+        <v>12</v>
+      </c>
+      <c r="N29" s="4" t="n">
         <v>0.5</v>
-      </c>
-      <c r="M29" t="n">
-        <v>19</v>
-      </c>
-      <c r="N29" s="4" t="n">
-        <v>0.5789473684210527</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
       </c>
       <c r="P29" s="4" t="inlineStr"/>
       <c r="Q29" t="n">
-        <v>1058</v>
+        <v>382</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>0.5954631379962193</v>
+        <v>0.756544502617801</v>
       </c>
       <c r="S29" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="W29" t="n">
         <v>0</v>
@@ -4012,21 +3908,21 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>BRSAN</t>
+          <t>GUBRF</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>DOJI</t>
+          <t>MORNING_STAR</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -4036,7 +3932,7 @@
         <v>4</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>1.124925991711079</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -4044,67 +3940,71 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1925</v>
+        <v>578</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>0.5044155844155844</v>
+        <v>0.6591695501730104</v>
       </c>
       <c r="K30" t="n">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>0.4838709677419355</v>
+        <v>0.875</v>
       </c>
       <c r="M30" t="n">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.631578947368421</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="P30" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="Q30" t="n">
-        <v>1924</v>
+        <v>578</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>0.6185031185031185</v>
+        <v>0.7612456747404844</v>
       </c>
       <c r="S30" t="n">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>0.5161290322580645</v>
+        <v>1</v>
       </c>
       <c r="U30" t="n">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>0.85</v>
+        <v>0.6842105263157895</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
-      </c>
-      <c r="X30" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="X30" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>BRSAN</t>
+          <t>GUBRF</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>DOJI</t>
+          <t>MORNING_STAR</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -4114,7 +4014,7 @@
         <v>6</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>1.124925991711079</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -4122,67 +4022,71 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2503</v>
+        <v>645</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>0.5213743507790651</v>
+        <v>0.6635658914728683</v>
       </c>
       <c r="K31" t="n">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.8</v>
       </c>
       <c r="M31" t="n">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>0.6785714285714286</v>
+        <v>0.6818181818181818</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="P31" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="Q31" t="n">
-        <v>2501</v>
+        <v>645</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>0.6297481007596961</v>
+        <v>0.7643410852713178</v>
       </c>
       <c r="S31" t="n">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>0.5853658536585366</v>
+        <v>1</v>
       </c>
       <c r="U31" t="n">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>0.8867924528301887</v>
+        <v>0.7272727272727273</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
-      </c>
-      <c r="X31" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="X31" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>BRSAN</t>
+          <t>GUBRF</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>DOJI</t>
+          <t>MORNING_STAR</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -4192,7 +4096,7 @@
         <v>2</v>
       </c>
       <c r="G32" t="n">
-        <v>2.611940298507465</v>
+        <v>3.76670716889429</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -4200,44 +4104,44 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>924</v>
+        <v>116</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>0.5010822510822511</v>
+        <v>0.7413793103448276</v>
       </c>
       <c r="K32" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="M32" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.75</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
       </c>
       <c r="P32" s="4" t="inlineStr"/>
       <c r="Q32" t="n">
-        <v>923</v>
+        <v>116</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>0.6262188515709642</v>
+        <v>0.8362068965517241</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="U32" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.75</v>
       </c>
       <c r="W32" t="n">
         <v>0</v>
@@ -4246,21 +4150,21 @@
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>BRSAN</t>
+          <t>GUBRF</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>DOJI</t>
+          <t>MORNING_STAR</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -4270,7 +4174,7 @@
         <v>4</v>
       </c>
       <c r="G33" t="n">
-        <v>2.611940298507465</v>
+        <v>3.76670716889429</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -4278,44 +4182,44 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1579</v>
+        <v>289</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>0.4952501583280557</v>
+        <v>0.671280276816609</v>
       </c>
       <c r="K33" t="n">
+        <v>4</v>
+      </c>
+      <c r="L33" s="4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="M33" t="n">
         <v>15</v>
       </c>
-      <c r="L33" s="4" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="M33" t="n">
-        <v>27</v>
-      </c>
       <c r="N33" s="4" t="n">
-        <v>0.7037037037037037</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
       </c>
       <c r="P33" s="4" t="inlineStr"/>
       <c r="Q33" t="n">
-        <v>1578</v>
+        <v>289</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>0.6153358681875792</v>
+        <v>0.7854671280276817</v>
       </c>
       <c r="S33" t="n">
+        <v>4</v>
+      </c>
+      <c r="T33" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
         <v>15</v>
       </c>
-      <c r="T33" s="4" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="U33" t="n">
-        <v>26</v>
-      </c>
       <c r="V33" s="4" t="n">
-        <v>0.8461538461538461</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="W33" t="n">
         <v>0</v>
@@ -4324,21 +4228,21 @@
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>BRSAN</t>
+          <t>GUBRF</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>DOJI</t>
+          <t>MORNING_STAR</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -4348,7 +4252,7 @@
         <v>6</v>
       </c>
       <c r="G34" t="n">
-        <v>2.611940298507465</v>
+        <v>3.76670716889429</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -4356,44 +4260,44 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2384</v>
+        <v>332</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>0.4991610738255033</v>
+        <v>0.6746987951807228</v>
       </c>
       <c r="K34" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.4516129032258064</v>
+        <v>0.75</v>
       </c>
       <c r="M34" t="n">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.6818181818181818</v>
+        <v>0.6875</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
       </c>
       <c r="P34" s="4" t="inlineStr"/>
       <c r="Q34" t="n">
-        <v>2382</v>
+        <v>332</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>0.6171284634760705</v>
+        <v>0.786144578313253</v>
       </c>
       <c r="S34" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>0.4838709677419355</v>
+        <v>1</v>
       </c>
       <c r="U34" t="n">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.6875</v>
       </c>
       <c r="W34" t="n">
         <v>0</v>
@@ -4402,21 +4306,21 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>BRSAN</t>
+          <t>GUBRF</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>DOJI</t>
+          <t>MORNING_STAR</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -4426,52 +4330,52 @@
         <v>2</v>
       </c>
       <c r="G35" t="n">
-        <v>-3.083700440528636</v>
+        <v>-7.224334600760452</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>[-4,-2)</t>
+          <t>[-8,-6)</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>137</v>
+        <v>111</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>0.489051094890511</v>
+        <v>0.7027027027027027</v>
       </c>
       <c r="K35" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
       </c>
       <c r="P35" s="4" t="inlineStr"/>
       <c r="Q35" t="n">
-        <v>137</v>
+        <v>111</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>0.656934306569343</v>
+        <v>0.7837837837837838</v>
       </c>
       <c r="S35" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U35" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8</v>
       </c>
       <c r="W35" t="n">
         <v>0</v>
@@ -4480,21 +4384,21 @@
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>BRSAN</t>
+          <t>GUBRF</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>DOJI</t>
+          <t>MORNING_STAR</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -4504,52 +4408,52 @@
         <v>4</v>
       </c>
       <c r="G36" t="n">
-        <v>-3.083700440528636</v>
+        <v>-7.224334600760452</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>[-4,0)</t>
+          <t>[-8,-4)</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>392</v>
+        <v>254</v>
       </c>
       <c r="J36" s="4" t="n">
-        <v>0.4642857142857143</v>
+        <v>0.6929133858267716</v>
       </c>
       <c r="K36" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L36" s="4" t="n">
-        <v>0.2857142857142857</v>
+        <v>1</v>
       </c>
       <c r="M36" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="N36" s="4" t="n">
-        <v>0.5</v>
+        <v>0.6363636363636364</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
       </c>
       <c r="P36" s="4" t="inlineStr"/>
       <c r="Q36" t="n">
-        <v>391</v>
+        <v>254</v>
       </c>
       <c r="R36" s="4" t="n">
-        <v>0.5907928388746803</v>
+        <v>0.7795275590551181</v>
       </c>
       <c r="S36" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T36" s="4" t="n">
-        <v>0.2857142857142857</v>
+        <v>1</v>
       </c>
       <c r="U36" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="V36" s="4" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.6363636363636364</v>
       </c>
       <c r="W36" t="n">
         <v>0</v>
@@ -4558,21 +4462,21 @@
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>BRSAN</t>
+          <t>GUBRF</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>DOJI</t>
+          <t>MORNING_STAR</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -4582,70 +4486,74 @@
         <v>6</v>
       </c>
       <c r="G37" t="n">
-        <v>-3.083700440528636</v>
+        <v>-7.224334600760452</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>[-6,0)</t>
+          <t>[-12,-6)</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>478</v>
+        <v>236</v>
       </c>
       <c r="J37" s="4" t="n">
-        <v>0.4853556485355648</v>
+        <v>0.6610169491525424</v>
       </c>
       <c r="K37" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="L37" s="4" t="n">
-        <v>0.4444444444444444</v>
+        <v>1</v>
       </c>
       <c r="M37" t="n">
         <v>9</v>
       </c>
       <c r="N37" s="4" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="P37" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="Q37" t="n">
-        <v>477</v>
+        <v>236</v>
       </c>
       <c r="R37" s="4" t="n">
-        <v>0.6058700209643606</v>
+        <v>0.7415254237288136</v>
       </c>
       <c r="S37" t="n">
+        <v>3</v>
+      </c>
+      <c r="T37" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
         <v>9</v>
       </c>
-      <c r="T37" s="4" t="n">
-        <v>0.4444444444444444</v>
-      </c>
-      <c r="U37" t="n">
-        <v>8</v>
-      </c>
       <c r="V37" s="4" t="n">
-        <v>0.75</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
-      </c>
-      <c r="X37" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="X37" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>BSOKE</t>
+          <t>OBAMS</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>BEARISH_ENGULFING</t>
+          <t>DOJI</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4660,52 +4568,52 @@
         <v>2</v>
       </c>
       <c r="G38" t="n">
-        <v>0.6010962564894085</v>
+        <v>-2.808990469686379</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>[0,2)</t>
+          <t>[-4,-2)</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1199</v>
+        <v>215</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>0.5312760633861552</v>
+        <v>0.5255813953488372</v>
       </c>
       <c r="K38" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="L38" s="4" t="n">
-        <v>0.36</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>39</v>
+        <v>4</v>
       </c>
       <c r="N38" s="4" t="n">
-        <v>0.7692307692307693</v>
+        <v>1</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
       </c>
       <c r="P38" s="4" t="inlineStr"/>
       <c r="Q38" t="n">
-        <v>1189</v>
+        <v>214</v>
       </c>
       <c r="R38" s="4" t="n">
-        <v>0.6593776282590412</v>
+        <v>0.6355140186915887</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T38" s="4" t="n">
-        <v>0.5600000000000001</v>
+        <v>1</v>
       </c>
       <c r="U38" t="n">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="V38" s="4" t="n">
-        <v>0.8157894736842105</v>
+        <v>1</v>
       </c>
       <c r="W38" t="n">
         <v>0</v>
@@ -4714,16 +4622,16 @@
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>BSOKE</t>
+          <t>OBAMS</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>BEARISH_ENGULFING</t>
+          <t>DOJI</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -4738,52 +4646,52 @@
         <v>4</v>
       </c>
       <c r="G39" t="n">
-        <v>0.6010962564894085</v>
+        <v>-2.808990469686379</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>[0,4)</t>
+          <t>[-4,0)</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1817</v>
+        <v>836</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>0.5465052283984591</v>
+        <v>0.5035885167464115</v>
       </c>
       <c r="K39" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="L39" s="4" t="n">
-        <v>0.34375</v>
+        <v>0.5</v>
       </c>
       <c r="M39" t="n">
-        <v>58</v>
+        <v>13</v>
       </c>
       <c r="N39" s="4" t="n">
-        <v>0.7413793103448276</v>
+        <v>0.8461538461538461</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
       </c>
       <c r="P39" s="4" t="inlineStr"/>
       <c r="Q39" t="n">
-        <v>1804</v>
+        <v>834</v>
       </c>
       <c r="R39" s="4" t="n">
-        <v>0.6657427937915743</v>
+        <v>0.6258992805755396</v>
       </c>
       <c r="S39" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="T39" s="4" t="n">
-        <v>0.5625</v>
+        <v>1</v>
       </c>
       <c r="U39" t="n">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="V39" s="4" t="n">
-        <v>0.8070175438596491</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="W39" t="n">
         <v>0</v>
@@ -4792,16 +4700,16 @@
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>BSOKE</t>
+          <t>OBAMS</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>BEARISH_ENGULFING</t>
+          <t>DOJI</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -4816,52 +4724,52 @@
         <v>6</v>
       </c>
       <c r="G40" t="n">
-        <v>0.6010962564894085</v>
+        <v>-2.808990469686379</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>[0,6)</t>
+          <t>[-6,0)</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2046</v>
+        <v>916</v>
       </c>
       <c r="J40" s="4" t="n">
-        <v>0.552297165200391</v>
+        <v>0.509825327510917</v>
       </c>
       <c r="K40" t="n">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="L40" s="4" t="n">
-        <v>0.3888888888888889</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="M40" t="n">
-        <v>68</v>
+        <v>15</v>
       </c>
       <c r="N40" s="4" t="n">
-        <v>0.7352941176470589</v>
+        <v>0.8</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
       </c>
       <c r="P40" s="4" t="inlineStr"/>
       <c r="Q40" t="n">
-        <v>2032</v>
+        <v>914</v>
       </c>
       <c r="R40" s="4" t="n">
-        <v>0.6692913385826772</v>
+        <v>0.6301969365426696</v>
       </c>
       <c r="S40" t="n">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="T40" s="4" t="n">
-        <v>0.5833333333333334</v>
+        <v>1</v>
       </c>
       <c r="U40" t="n">
-        <v>67</v>
+        <v>15</v>
       </c>
       <c r="V40" s="4" t="n">
-        <v>0.7910447761194029</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="W40" t="n">
         <v>0</v>
@@ -4870,16 +4778,16 @@
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>BSOKE</t>
+          <t>OBAMS</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>BEARISH_ENGULFING</t>
+          <t>DOJI</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -4894,7 +4802,7 @@
         <v>2</v>
       </c>
       <c r="G41" t="n">
-        <v>0.7662801649736428</v>
+        <v>0.5813994320832405</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -4902,66 +4810,62 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1049</v>
+        <v>657</v>
       </c>
       <c r="J41" s="4" t="n">
-        <v>0.553860819828408</v>
+        <v>0.487062404870624</v>
       </c>
       <c r="K41" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="L41" s="4" t="n">
-        <v>0.3888888888888889</v>
+        <v>0.5</v>
       </c>
       <c r="M41" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="N41" s="4" t="n">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="O41" t="n">
-        <v>1</v>
-      </c>
-      <c r="P41" s="4" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P41" s="4" t="inlineStr"/>
       <c r="Q41" t="n">
-        <v>1042</v>
+        <v>654</v>
       </c>
       <c r="R41" s="4" t="n">
-        <v>0.6525911708253359</v>
+        <v>0.599388379204893</v>
       </c>
       <c r="S41" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="T41" s="4" t="n">
-        <v>0.6111111111111112</v>
+        <v>0.5</v>
       </c>
       <c r="U41" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="V41" s="4" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="W41" t="n">
-        <v>1</v>
-      </c>
-      <c r="X41" s="4" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="X41" s="4" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>BSOKE</t>
+          <t>OBAMS</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>BEARISH_ENGULFING</t>
+          <t>DOJI</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -4976,7 +4880,7 @@
         <v>4</v>
       </c>
       <c r="G42" t="n">
-        <v>0.7662801649736428</v>
+        <v>0.5813994320832405</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -4984,66 +4888,62 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1916</v>
+        <v>1584</v>
       </c>
       <c r="J42" s="4" t="n">
-        <v>0.5443632567849687</v>
+        <v>0.4962121212121212</v>
       </c>
       <c r="K42" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="L42" s="4" t="n">
         <v>0.5</v>
       </c>
       <c r="M42" t="n">
-        <v>64</v>
+        <v>19</v>
       </c>
       <c r="N42" s="4" t="n">
-        <v>0.71875</v>
+        <v>0.5789473684210527</v>
       </c>
       <c r="O42" t="n">
-        <v>1</v>
-      </c>
-      <c r="P42" s="4" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P42" s="4" t="inlineStr"/>
       <c r="Q42" t="n">
-        <v>1902</v>
+        <v>1578</v>
       </c>
       <c r="R42" s="4" t="n">
-        <v>0.655099894847529</v>
+        <v>0.614702154626109</v>
       </c>
       <c r="S42" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="T42" s="4" t="n">
-        <v>0.65625</v>
+        <v>0.5</v>
       </c>
       <c r="U42" t="n">
-        <v>63</v>
+        <v>18</v>
       </c>
       <c r="V42" s="4" t="n">
-        <v>0.7936507936507936</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="W42" t="n">
-        <v>1</v>
-      </c>
-      <c r="X42" s="4" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="X42" s="4" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>BSOKE</t>
+          <t>OBAMS</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>BEARISH_ENGULFING</t>
+          <t>DOJI</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5058,7 +4958,7 @@
         <v>6</v>
       </c>
       <c r="G43" t="n">
-        <v>0.7662801649736428</v>
+        <v>0.5813994320832405</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -5066,66 +4966,62 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2521</v>
+        <v>2390</v>
       </c>
       <c r="J43" s="4" t="n">
-        <v>0.5450218167393891</v>
+        <v>0.5</v>
       </c>
       <c r="K43" t="n">
-        <v>39</v>
+        <v>3</v>
       </c>
       <c r="L43" s="4" t="n">
-        <v>0.4871794871794872</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="M43" t="n">
-        <v>75</v>
+        <v>33</v>
       </c>
       <c r="N43" s="4" t="n">
-        <v>0.7333333333333333</v>
+        <v>0.5757575757575758</v>
       </c>
       <c r="O43" t="n">
-        <v>1</v>
-      </c>
-      <c r="P43" s="4" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P43" s="4" t="inlineStr"/>
       <c r="Q43" t="n">
-        <v>2504</v>
+        <v>2383</v>
       </c>
       <c r="R43" s="4" t="n">
-        <v>0.6601437699680511</v>
+        <v>0.6164498531263114</v>
       </c>
       <c r="S43" t="n">
-        <v>39</v>
+        <v>3</v>
       </c>
       <c r="T43" s="4" t="n">
-        <v>0.6410256410256411</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="U43" t="n">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="V43" s="4" t="n">
-        <v>0.8082191780821918</v>
+        <v>0.75</v>
       </c>
       <c r="W43" t="n">
-        <v>1</v>
-      </c>
-      <c r="X43" s="4" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="X43" s="4" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="3" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>BSOKE</t>
+          <t>OBAMS</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>BEARISH_ENGULFING</t>
+          <t>DOJI</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5140,53 +5036,45 @@
         <v>2</v>
       </c>
       <c r="G44" t="n">
-        <v>-1.021508226671353</v>
+        <v>-10.97769939727128</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>[-2,0)</t>
+          <t>[-12,-10)</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>358</v>
+        <v>15</v>
       </c>
       <c r="J44" s="4" t="n">
-        <v>0.5810055865921788</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="K44" t="n">
-        <v>6</v>
-      </c>
-      <c r="L44" s="4" t="n">
-        <v>0.6666666666666666</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L44" s="4" t="inlineStr"/>
       <c r="M44" t="n">
-        <v>13</v>
-      </c>
-      <c r="N44" s="4" t="n">
-        <v>0.9230769230769231</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N44" s="4" t="inlineStr"/>
       <c r="O44" t="n">
         <v>0</v>
       </c>
       <c r="P44" s="4" t="inlineStr"/>
       <c r="Q44" t="n">
-        <v>358</v>
+        <v>15</v>
       </c>
       <c r="R44" s="4" t="n">
-        <v>0.6620111731843575</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="S44" t="n">
-        <v>6</v>
-      </c>
-      <c r="T44" s="4" t="n">
-        <v>0.8333333333333334</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="T44" s="4" t="inlineStr"/>
       <c r="U44" t="n">
-        <v>12</v>
-      </c>
-      <c r="V44" s="4" t="n">
-        <v>0.9166666666666666</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V44" s="4" t="inlineStr"/>
       <c r="W44" t="n">
         <v>0</v>
       </c>
@@ -5194,16 +5082,16 @@
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>BSOKE</t>
+          <t>OBAMS</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>BEARISH_ENGULFING</t>
+          <t>DOJI</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5218,52 +5106,48 @@
         <v>4</v>
       </c>
       <c r="G45" t="n">
-        <v>-1.021508226671353</v>
+        <v>-10.97769939727128</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>[-4,0)</t>
+          <t>[-12,-8)</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>590</v>
+        <v>33</v>
       </c>
       <c r="J45" s="4" t="n">
-        <v>0.5932203389830508</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="K45" t="n">
-        <v>11</v>
-      </c>
-      <c r="L45" s="4" t="n">
-        <v>0.5454545454545454</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L45" s="4" t="inlineStr"/>
       <c r="M45" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="N45" s="4" t="n">
-        <v>0.8181818181818182</v>
+        <v>1</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
       </c>
       <c r="P45" s="4" t="inlineStr"/>
       <c r="Q45" t="n">
-        <v>590</v>
+        <v>33</v>
       </c>
       <c r="R45" s="4" t="n">
-        <v>0.6711864406779661</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="S45" t="n">
-        <v>11</v>
-      </c>
-      <c r="T45" s="4" t="n">
-        <v>0.6363636363636364</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="T45" s="4" t="inlineStr"/>
       <c r="U45" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="V45" s="4" t="n">
-        <v>0.9047619047619048</v>
+        <v>1</v>
       </c>
       <c r="W45" t="n">
         <v>0</v>
@@ -5272,16 +5156,16 @@
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>BSOKE</t>
+          <t>OBAMS</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>BEARISH_ENGULFING</t>
+          <t>DOJI</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5296,52 +5180,48 @@
         <v>6</v>
       </c>
       <c r="G46" t="n">
-        <v>-1.021508226671353</v>
+        <v>-10.97769939727128</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>[-6,0)</t>
+          <t>[-12,-6)</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>714</v>
+        <v>93</v>
       </c>
       <c r="J46" s="4" t="n">
-        <v>0.6064425770308123</v>
+        <v>0.6021505376344086</v>
       </c>
       <c r="K46" t="n">
-        <v>15</v>
-      </c>
-      <c r="L46" s="4" t="n">
-        <v>0.6</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L46" s="4" t="inlineStr"/>
       <c r="M46" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="N46" s="4" t="n">
-        <v>0.8260869565217391</v>
+        <v>1</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
       </c>
       <c r="P46" s="4" t="inlineStr"/>
       <c r="Q46" t="n">
-        <v>714</v>
+        <v>93</v>
       </c>
       <c r="R46" s="4" t="n">
-        <v>0.6834733893557423</v>
+        <v>0.6881720430107527</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
-      </c>
-      <c r="T46" s="4" t="n">
-        <v>0.6666666666666666</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="T46" s="4" t="inlineStr"/>
       <c r="U46" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="V46" s="4" t="n">
-        <v>0.9090909090909091</v>
+        <v>1</v>
       </c>
       <c r="W46" t="n">
         <v>0</v>
@@ -5350,21 +5230,21 @@
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>DOAS</t>
+          <t>PGSUS</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>DOJI</t>
+          <t>HAMMER</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="E47" t="n">
@@ -5374,52 +5254,52 @@
         <v>2</v>
       </c>
       <c r="G47" t="n">
-        <v>0.5434782608695565</v>
+        <v>-2.504470497717692</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>[0,2)</t>
+          <t>[-4,-2)</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1058</v>
+        <v>657</v>
       </c>
       <c r="J47" s="4" t="n">
-        <v>0.4962192816635161</v>
+        <v>0.6590563165905632</v>
       </c>
       <c r="K47" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L47" s="4" t="n">
-        <v>0.5</v>
+        <v>0.7272727272727273</v>
       </c>
       <c r="M47" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N47" s="4" t="n">
-        <v>0.5789473684210527</v>
+        <v>0.7222222222222222</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
       </c>
       <c r="P47" s="4" t="inlineStr"/>
       <c r="Q47" t="n">
-        <v>1058</v>
+        <v>657</v>
       </c>
       <c r="R47" s="4" t="n">
-        <v>0.5954631379962193</v>
+        <v>0.7473363774733638</v>
       </c>
       <c r="S47" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T47" s="4" t="n">
-        <v>0.75</v>
+        <v>0.8181818181818182</v>
       </c>
       <c r="U47" t="n">
         <v>18</v>
       </c>
       <c r="V47" s="4" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.7222222222222222</v>
       </c>
       <c r="W47" t="n">
         <v>0</v>
@@ -5428,21 +5308,21 @@
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>DOAS</t>
+          <t>PGSUS</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>DOJI</t>
+          <t>HAMMER</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -5452,52 +5332,52 @@
         <v>4</v>
       </c>
       <c r="G48" t="n">
-        <v>0.5434782608695565</v>
+        <v>-2.504470497717692</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>[0,4)</t>
+          <t>[-4,0)</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1925</v>
+        <v>1423</v>
       </c>
       <c r="J48" s="4" t="n">
-        <v>0.5044155844155844</v>
+        <v>0.607167955024596</v>
       </c>
       <c r="K48" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L48" s="4" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.6521739130434783</v>
       </c>
       <c r="M48" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="N48" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6842105263157895</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
       </c>
       <c r="P48" s="4" t="inlineStr"/>
       <c r="Q48" t="n">
-        <v>1924</v>
+        <v>1423</v>
       </c>
       <c r="R48" s="4" t="n">
-        <v>0.6185031185031185</v>
+        <v>0.7118763176387913</v>
       </c>
       <c r="S48" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="T48" s="4" t="n">
-        <v>0.8095238095238095</v>
+        <v>0.7391304347826086</v>
       </c>
       <c r="U48" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="V48" s="4" t="n">
-        <v>0.85</v>
+        <v>0.7027027027027027</v>
       </c>
       <c r="W48" t="n">
         <v>0</v>
@@ -5506,21 +5386,21 @@
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>DOAS</t>
+          <t>PGSUS</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>DOJI</t>
+          <t>HAMMER</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -5530,75 +5410,79 @@
         <v>6</v>
       </c>
       <c r="G49" t="n">
-        <v>0.5434782608695565</v>
+        <v>-2.504470497717692</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>[0,6)</t>
+          <t>[-6,0)</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2503</v>
+        <v>1828</v>
       </c>
       <c r="J49" s="4" t="n">
-        <v>0.5213743507790651</v>
+        <v>0.6280087527352297</v>
       </c>
       <c r="K49" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L49" s="4" t="n">
-        <v>0.5925925925925926</v>
+        <v>0.6923076923076923</v>
       </c>
       <c r="M49" t="n">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="N49" s="4" t="n">
-        <v>0.6785714285714286</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
-      </c>
-      <c r="P49" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="P49" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="Q49" t="n">
-        <v>2501</v>
+        <v>1828</v>
       </c>
       <c r="R49" s="4" t="n">
-        <v>0.6297481007596961</v>
+        <v>0.7286652078774617</v>
       </c>
       <c r="S49" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="T49" s="4" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.7692307692307693</v>
       </c>
       <c r="U49" t="n">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="V49" s="4" t="n">
-        <v>0.8867924528301887</v>
+        <v>0.7045454545454546</v>
       </c>
       <c r="W49" t="n">
-        <v>0</v>
-      </c>
-      <c r="X49" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="X49" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>DOAS</t>
+          <t>PGSUS</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>DOJI</t>
+          <t>HAMMER</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="E50" t="n">
@@ -5608,7 +5492,7 @@
         <v>2</v>
       </c>
       <c r="G50" t="n">
-        <v>-0.5376344086021501</v>
+        <v>-1.148726702900293</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -5616,44 +5500,44 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>200</v>
+        <v>612</v>
       </c>
       <c r="J50" s="4" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5473856209150327</v>
       </c>
       <c r="K50" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L50" s="4" t="n">
-        <v>0</v>
+        <v>0.625</v>
       </c>
       <c r="M50" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="N50" s="4" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
       </c>
       <c r="P50" s="4" t="inlineStr"/>
       <c r="Q50" t="n">
-        <v>200</v>
+        <v>612</v>
       </c>
       <c r="R50" s="4" t="n">
-        <v>0.665</v>
+        <v>0.6699346405228758</v>
       </c>
       <c r="S50" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="T50" s="4" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="U50" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V50" s="4" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.6363636363636364</v>
       </c>
       <c r="W50" t="n">
         <v>0</v>
@@ -5662,21 +5546,21 @@
     </row>
     <row r="51">
       <c r="A51" s="3" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>DOAS</t>
+          <t>PGSUS</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>DOJI</t>
+          <t>HAMMER</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="E51" t="n">
@@ -5686,7 +5570,7 @@
         <v>4</v>
       </c>
       <c r="G51" t="n">
-        <v>-0.5376344086021501</v>
+        <v>-1.148726702900293</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -5694,44 +5578,44 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>268</v>
+        <v>1342</v>
       </c>
       <c r="J51" s="4" t="n">
-        <v>0.5708955223880597</v>
+        <v>0.5737704918032787</v>
       </c>
       <c r="K51" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="L51" s="4" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="M51" t="n">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="N51" s="4" t="n">
-        <v>0.75</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
       </c>
       <c r="P51" s="4" t="inlineStr"/>
       <c r="Q51" t="n">
-        <v>268</v>
+        <v>1342</v>
       </c>
       <c r="R51" s="4" t="n">
-        <v>0.667910447761194</v>
+        <v>0.6900149031296572</v>
       </c>
       <c r="S51" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="T51" s="4" t="n">
-        <v>1</v>
+        <v>0.8095238095238095</v>
       </c>
       <c r="U51" t="n">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="V51" s="4" t="n">
-        <v>0.875</v>
+        <v>0.6774193548387096</v>
       </c>
       <c r="W51" t="n">
         <v>0</v>
@@ -5740,21 +5624,21 @@
     </row>
     <row r="52">
       <c r="A52" s="3" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>DOAS</t>
+          <t>PGSUS</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>DOJI</t>
+          <t>HAMMER</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="E52" t="n">
@@ -5764,7 +5648,7 @@
         <v>6</v>
       </c>
       <c r="G52" t="n">
-        <v>-0.5376344086021501</v>
+        <v>-1.148726702900293</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -5772,67 +5656,71 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>315</v>
+        <v>1905</v>
       </c>
       <c r="J52" s="4" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.5994750656167979</v>
       </c>
       <c r="K52" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="L52" s="4" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.7241379310344828</v>
       </c>
       <c r="M52" t="n">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="N52" s="4" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.6</v>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
-      </c>
-      <c r="P52" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="P52" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="Q52" t="n">
-        <v>315</v>
+        <v>1905</v>
       </c>
       <c r="R52" s="4" t="n">
-        <v>0.6730158730158731</v>
+        <v>0.7081364829396325</v>
       </c>
       <c r="S52" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="T52" s="4" t="n">
-        <v>1</v>
+        <v>0.7586206896551724</v>
       </c>
       <c r="U52" t="n">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="V52" s="4" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.673469387755102</v>
       </c>
       <c r="W52" t="n">
-        <v>0</v>
-      </c>
-      <c r="X52" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="X52" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>DOAS</t>
+          <t>PGSUS</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>DOJI</t>
+          <t>HAMMER</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="E53" t="n">
@@ -5842,75 +5730,79 @@
         <v>2</v>
       </c>
       <c r="G53" t="n">
-        <v>-0.7510697115483023</v>
+        <v>-6.4645325254439</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>[-2,0)</t>
+          <t>[-8,-6)</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>255</v>
+        <v>338</v>
       </c>
       <c r="J53" s="4" t="n">
-        <v>0.4509803921568628</v>
+        <v>0.591715976331361</v>
       </c>
       <c r="K53" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="L53" s="4" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="M53" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="N53" s="4" t="n">
         <v>0.5</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
-      </c>
-      <c r="P53" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="P53" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="Q53" t="n">
-        <v>254</v>
+        <v>338</v>
       </c>
       <c r="R53" s="4" t="n">
-        <v>0.5551181102362205</v>
+        <v>0.7189349112426036</v>
       </c>
       <c r="S53" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="T53" s="4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="U53" t="n">
+        <v>8</v>
+      </c>
+      <c r="V53" s="4" t="n">
         <v>0.5</v>
       </c>
-      <c r="U53" t="n">
-        <v>4</v>
-      </c>
-      <c r="V53" s="4" t="n">
-        <v>0.75</v>
-      </c>
       <c r="W53" t="n">
-        <v>0</v>
-      </c>
-      <c r="X53" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="X53" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>DOAS</t>
+          <t>PGSUS</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>DOJI</t>
+          <t>HAMMER</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="E54" t="n">
@@ -5920,75 +5812,79 @@
         <v>4</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.7510697115483023</v>
+        <v>-6.4645325254439</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>[-4,0)</t>
+          <t>[-8,-4)</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>392</v>
+        <v>726</v>
       </c>
       <c r="J54" s="4" t="n">
-        <v>0.4642857142857143</v>
+        <v>0.6033057851239669</v>
       </c>
       <c r="K54" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="L54" s="4" t="n">
-        <v>0.5</v>
+        <v>0.8235294117647058</v>
       </c>
       <c r="M54" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="N54" s="4" t="n">
-        <v>0.5</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
-      </c>
-      <c r="P54" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="P54" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="Q54" t="n">
-        <v>391</v>
+        <v>726</v>
       </c>
       <c r="R54" s="4" t="n">
-        <v>0.5907928388746803</v>
+        <v>0.7107438016528925</v>
       </c>
       <c r="S54" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="T54" s="4" t="n">
-        <v>0.75</v>
+        <v>0.8235294117647058</v>
       </c>
       <c r="U54" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="V54" s="4" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.625</v>
       </c>
       <c r="W54" t="n">
-        <v>0</v>
-      </c>
-      <c r="X54" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="X54" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>DOAS</t>
+          <t>PGSUS</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>DOJI</t>
+          <t>HAMMER</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="E55" t="n">
@@ -5998,65 +5894,69 @@
         <v>6</v>
       </c>
       <c r="G55" t="n">
-        <v>-0.7510697115483023</v>
+        <v>-6.4645325254439</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>[-6,0)</t>
+          <t>[-12,-6)</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>478</v>
+        <v>777</v>
       </c>
       <c r="J55" s="4" t="n">
-        <v>0.4853556485355648</v>
+        <v>0.6782496782496783</v>
       </c>
       <c r="K55" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L55" s="4" t="n">
         <v>0.6666666666666666</v>
       </c>
       <c r="M55" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="N55" s="4" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="O55" t="n">
-        <v>0</v>
-      </c>
-      <c r="P55" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="P55" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="Q55" t="n">
-        <v>477</v>
+        <v>776</v>
       </c>
       <c r="R55" s="4" t="n">
-        <v>0.6058700209643606</v>
+        <v>0.7822164948453608</v>
       </c>
       <c r="S55" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="T55" s="4" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.75</v>
       </c>
       <c r="U55" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="V55" s="4" t="n">
-        <v>0.75</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="W55" t="n">
-        <v>0</v>
-      </c>
-      <c r="X55" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="X55" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>GUBRF</t>
+          <t>THYAO</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -6076,52 +5976,52 @@
         <v>2</v>
       </c>
       <c r="G56" t="n">
-        <v>-0.7259528130671544</v>
+        <v>-3.48484848484848</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>[-2,0)</t>
+          <t>[-4,-2)</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>766</v>
+        <v>657</v>
       </c>
       <c r="J56" s="4" t="n">
-        <v>0.5626631853785901</v>
+        <v>0.6590563165905632</v>
       </c>
       <c r="K56" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L56" s="4" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.6</v>
       </c>
       <c r="M56" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N56" s="4" t="n">
-        <v>0.631578947368421</v>
+        <v>0.7222222222222222</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
       </c>
       <c r="P56" s="4" t="inlineStr"/>
       <c r="Q56" t="n">
-        <v>766</v>
+        <v>657</v>
       </c>
       <c r="R56" s="4" t="n">
-        <v>0.6814621409921671</v>
+        <v>0.7473363774733638</v>
       </c>
       <c r="S56" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T56" s="4" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="U56" t="n">
         <v>18</v>
       </c>
       <c r="V56" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7222222222222222</v>
       </c>
       <c r="W56" t="n">
         <v>0</v>
@@ -6130,11 +6030,11 @@
     </row>
     <row r="57">
       <c r="A57" s="3" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>GUBRF</t>
+          <t>THYAO</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -6154,7 +6054,7 @@
         <v>4</v>
       </c>
       <c r="G57" t="n">
-        <v>-0.7259528130671544</v>
+        <v>-3.48484848484848</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -6168,16 +6068,16 @@
         <v>0.607167955024596</v>
       </c>
       <c r="K57" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L57" s="4" t="n">
-        <v>0.6428571428571429</v>
+        <v>0.5</v>
       </c>
       <c r="M57" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="N57" s="4" t="n">
-        <v>0.6756756756756757</v>
+        <v>0.6842105263157895</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -6190,16 +6090,16 @@
         <v>0.7118763176387913</v>
       </c>
       <c r="S57" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="T57" s="4" t="n">
-        <v>0.7857142857142857</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="U57" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="V57" s="4" t="n">
-        <v>0.6944444444444444</v>
+        <v>0.7027027027027027</v>
       </c>
       <c r="W57" t="n">
         <v>0</v>
@@ -6208,11 +6108,11 @@
     </row>
     <row r="58">
       <c r="A58" s="3" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>GUBRF</t>
+          <t>THYAO</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -6232,7 +6132,7 @@
         <v>6</v>
       </c>
       <c r="G58" t="n">
-        <v>-0.7259528130671544</v>
+        <v>-3.48484848484848</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -6246,16 +6146,16 @@
         <v>0.6280087527352297</v>
       </c>
       <c r="K58" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="L58" s="4" t="n">
-        <v>0.6190476190476191</v>
+        <v>0.6470588235294118</v>
       </c>
       <c r="M58" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="N58" s="4" t="n">
-        <v>0.6590909090909091</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -6268,16 +6168,16 @@
         <v>0.7286652078774617</v>
       </c>
       <c r="S58" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="T58" s="4" t="n">
-        <v>0.8095238095238095</v>
+        <v>0.7058823529411765</v>
       </c>
       <c r="U58" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="V58" s="4" t="n">
-        <v>0.6976744186046512</v>
+        <v>0.7045454545454546</v>
       </c>
       <c r="W58" t="n">
         <v>0</v>
@@ -6286,11 +6186,11 @@
     </row>
     <row r="59">
       <c r="A59" s="3" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>GUBRF</t>
+          <t>THYAO</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -6310,52 +6210,54 @@
         <v>2</v>
       </c>
       <c r="G59" t="n">
-        <v>-6.228571428571428</v>
+        <v>-4.497751124437777</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>[-8,-6)</t>
+          <t>[-6,-4)</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>303</v>
+        <v>563</v>
       </c>
       <c r="J59" s="4" t="n">
-        <v>0.6831683168316832</v>
+        <v>0.6607460035523979</v>
       </c>
       <c r="K59" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L59" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" t="n">
+        <v>19</v>
+      </c>
+      <c r="N59" s="4" t="n">
+        <v>0.5789473684210527</v>
+      </c>
+      <c r="O59" t="n">
+        <v>1</v>
+      </c>
+      <c r="P59" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>563</v>
+      </c>
+      <c r="R59" s="4" t="n">
+        <v>0.7513321492007105</v>
+      </c>
+      <c r="S59" t="n">
+        <v>1</v>
+      </c>
+      <c r="T59" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U59" t="n">
+        <v>18</v>
+      </c>
+      <c r="V59" s="4" t="n">
         <v>0.6666666666666666</v>
-      </c>
-      <c r="M59" t="n">
-        <v>14</v>
-      </c>
-      <c r="N59" s="4" t="n">
-        <v>0.5714285714285714</v>
-      </c>
-      <c r="O59" t="n">
-        <v>0</v>
-      </c>
-      <c r="P59" s="4" t="inlineStr"/>
-      <c r="Q59" t="n">
-        <v>302</v>
-      </c>
-      <c r="R59" s="4" t="n">
-        <v>0.7682119205298014</v>
-      </c>
-      <c r="S59" t="n">
-        <v>6</v>
-      </c>
-      <c r="T59" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="U59" t="n">
-        <v>14</v>
-      </c>
-      <c r="V59" s="4" t="n">
-        <v>0.5714285714285714</v>
       </c>
       <c r="W59" t="n">
         <v>0</v>
@@ -6364,11 +6266,11 @@
     </row>
     <row r="60">
       <c r="A60" s="3" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>GUBRF</t>
+          <t>THYAO</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -6388,7 +6290,7 @@
         <v>4</v>
       </c>
       <c r="G60" t="n">
-        <v>-6.228571428571428</v>
+        <v>-4.497751124437777</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -6402,22 +6304,22 @@
         <v>0.6685912240184757</v>
       </c>
       <c r="K60" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="L60" s="4" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="M60" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="N60" s="4" t="n">
-        <v>0.59375</v>
+        <v>0.5882352941176471</v>
       </c>
       <c r="O60" t="n">
         <v>1</v>
       </c>
       <c r="P60" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
         <v>865</v>
@@ -6426,10 +6328,10 @@
         <v>0.7572254335260116</v>
       </c>
       <c r="S60" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="T60" s="4" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="U60" t="n">
         <v>32</v>
@@ -6438,19 +6340,17 @@
         <v>0.625</v>
       </c>
       <c r="W60" t="n">
-        <v>1</v>
-      </c>
-      <c r="X60" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="X60" s="4" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="3" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>GUBRF</t>
+          <t>THYAO</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -6470,52 +6370,54 @@
         <v>6</v>
       </c>
       <c r="G61" t="n">
-        <v>-6.228571428571428</v>
+        <v>-4.497751124437777</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>[-12,-6)</t>
+          <t>[-6,0)</t>
         </is>
       </c>
       <c r="I61" t="n">
-        <v>581</v>
+        <v>1905</v>
       </c>
       <c r="J61" s="4" t="n">
-        <v>0.7366609294320138</v>
+        <v>0.5994750656167979</v>
       </c>
       <c r="K61" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="L61" s="4" t="n">
-        <v>0.8</v>
+        <v>0.7058823529411765</v>
       </c>
       <c r="M61" t="n">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="N61" s="4" t="n">
-        <v>0.6111111111111112</v>
+        <v>0.6</v>
       </c>
       <c r="O61" t="n">
-        <v>0</v>
-      </c>
-      <c r="P61" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="P61" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="Q61" t="n">
-        <v>580</v>
+        <v>1905</v>
       </c>
       <c r="R61" s="4" t="n">
-        <v>0.8068965517241379</v>
+        <v>0.7081364829396325</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="T61" s="4" t="n">
-        <v>1</v>
+        <v>0.7058823529411765</v>
       </c>
       <c r="U61" t="n">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="V61" s="4" t="n">
-        <v>0.6111111111111112</v>
+        <v>0.673469387755102</v>
       </c>
       <c r="W61" t="n">
         <v>0</v>
@@ -6524,11 +6426,11 @@
     </row>
     <row r="62">
       <c r="A62" s="3" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>GUBRF</t>
+          <t>THYAO</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -6548,69 +6450,65 @@
         <v>2</v>
       </c>
       <c r="G62" t="n">
-        <v>-10.0328947368421</v>
+        <v>-8.213256484149856</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>[-12,-10)</t>
+          <t>[-10,-8)</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>188</v>
+        <v>251</v>
       </c>
       <c r="J62" s="4" t="n">
-        <v>0.7553191489361702</v>
+        <v>0.7370517928286853</v>
       </c>
       <c r="K62" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L62" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N62" s="4" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="O62" t="n">
-        <v>1</v>
-      </c>
-      <c r="P62" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P62" s="4" t="inlineStr"/>
       <c r="Q62" t="n">
-        <v>187</v>
+        <v>251</v>
       </c>
       <c r="R62" s="4" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.8406374501992032</v>
       </c>
       <c r="S62" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T62" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U62" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V62" s="4" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="W62" t="n">
-        <v>1</v>
-      </c>
-      <c r="X62" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="X62" s="4" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="3" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>GUBRF</t>
+          <t>THYAO</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -6630,7 +6528,7 @@
         <v>4</v>
       </c>
       <c r="G63" t="n">
-        <v>-10.0328947368421</v>
+        <v>-8.213256484149856</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -6644,23 +6542,21 @@
         <v>0.744874715261959</v>
       </c>
       <c r="K63" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="L63" s="4" t="n">
-        <v>0.7777777777777778</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N63" s="4" t="n">
-        <v>0.5384615384615384</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="O63" t="n">
-        <v>1</v>
-      </c>
-      <c r="P63" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P63" s="4" t="inlineStr"/>
       <c r="Q63" t="n">
         <v>438</v>
       </c>
@@ -6668,31 +6564,29 @@
         <v>0.8310502283105022</v>
       </c>
       <c r="S63" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="T63" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U63" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="V63" s="4" t="n">
-        <v>0.5</v>
+        <v>0.5384615384615384</v>
       </c>
       <c r="W63" t="n">
-        <v>1</v>
-      </c>
-      <c r="X63" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="X63" s="4" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="3" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>GUBRF</t>
+          <t>THYAO</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -6712,7 +6606,7 @@
         <v>6</v>
       </c>
       <c r="G64" t="n">
-        <v>-10.0328947368421</v>
+        <v>-8.213256484149856</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -6726,23 +6620,21 @@
         <v>0.6782496782496783</v>
       </c>
       <c r="K64" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="L64" s="4" t="n">
-        <v>0.7333333333333333</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="M64" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N64" s="4" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="O64" t="n">
-        <v>1</v>
-      </c>
-      <c r="P64" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P64" s="4" t="inlineStr"/>
       <c r="Q64" t="n">
         <v>776</v>
       </c>
@@ -6750,31 +6642,29 @@
         <v>0.7822164948453608</v>
       </c>
       <c r="S64" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="T64" s="4" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="U64" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="V64" s="4" t="n">
-        <v>0.5</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="W64" t="n">
-        <v>1</v>
-      </c>
-      <c r="X64" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="X64" s="4" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="3" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>ODAS</t>
+          <t>TKFEN</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -6794,52 +6684,52 @@
         <v>2</v>
       </c>
       <c r="G65" t="n">
-        <v>-1.758494996787363</v>
+        <v>0.9090930431872923</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>[-2,0)</t>
+          <t>[0,2)</t>
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1219</v>
+        <v>1199</v>
       </c>
       <c r="J65" s="4" t="n">
-        <v>0.5520918785890074</v>
+        <v>0.5312760633861552</v>
       </c>
       <c r="K65" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="L65" s="4" t="n">
-        <v>0.6923076923076923</v>
+        <v>0.6842105263157895</v>
       </c>
       <c r="M65" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="N65" s="4" t="n">
-        <v>0.5428571428571428</v>
+        <v>0.75</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
       </c>
       <c r="P65" s="4" t="inlineStr"/>
       <c r="Q65" t="n">
-        <v>1215</v>
+        <v>1198</v>
       </c>
       <c r="R65" s="4" t="n">
-        <v>0.6436213991769547</v>
+        <v>0.656093489148581</v>
       </c>
       <c r="S65" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="T65" s="4" t="n">
-        <v>0.6923076923076923</v>
+        <v>0.7368421052631579</v>
       </c>
       <c r="U65" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="V65" s="4" t="n">
-        <v>0.6857142857142857</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="W65" t="n">
         <v>0</v>
@@ -6848,11 +6738,11 @@
     </row>
     <row r="66">
       <c r="A66" s="3" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>ODAS</t>
+          <t>TKFEN</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -6872,52 +6762,52 @@
         <v>4</v>
       </c>
       <c r="G66" t="n">
-        <v>-1.758494996787363</v>
+        <v>0.9090930431872923</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>[-4,0)</t>
+          <t>[0,4)</t>
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1947</v>
+        <v>1817</v>
       </c>
       <c r="J66" s="4" t="n">
-        <v>0.5824345146379045</v>
+        <v>0.5465052283984591</v>
       </c>
       <c r="K66" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="L66" s="4" t="n">
-        <v>0.6818181818181818</v>
+        <v>0.72</v>
       </c>
       <c r="M66" t="n">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="N66" s="4" t="n">
-        <v>0.7258064516129032</v>
+        <v>0.7446808510638298</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
       </c>
       <c r="P66" s="4" t="inlineStr"/>
       <c r="Q66" t="n">
-        <v>1941</v>
+        <v>1816</v>
       </c>
       <c r="R66" s="4" t="n">
-        <v>0.6738794435857806</v>
+        <v>0.6629955947136564</v>
       </c>
       <c r="S66" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="T66" s="4" t="n">
-        <v>0.6818181818181818</v>
+        <v>0.76</v>
       </c>
       <c r="U66" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="V66" s="4" t="n">
-        <v>0.8166666666666667</v>
+        <v>0.8</v>
       </c>
       <c r="W66" t="n">
         <v>0</v>
@@ -6926,11 +6816,11 @@
     </row>
     <row r="67">
       <c r="A67" s="3" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>ODAS</t>
+          <t>TKFEN</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -6950,69 +6840,65 @@
         <v>6</v>
       </c>
       <c r="G67" t="n">
-        <v>-1.758494996787363</v>
+        <v>0.9090930431872923</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>[-6,0)</t>
+          <t>[0,6)</t>
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2190</v>
+        <v>2046</v>
       </c>
       <c r="J67" s="4" t="n">
-        <v>0.5981735159817352</v>
+        <v>0.552297165200391</v>
       </c>
       <c r="K67" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="L67" s="4" t="n">
-        <v>0.7</v>
+        <v>0.7307692307692307</v>
       </c>
       <c r="M67" t="n">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="N67" s="4" t="n">
-        <v>0.726027397260274</v>
+        <v>0.7368421052631579</v>
       </c>
       <c r="O67" t="n">
-        <v>1</v>
-      </c>
-      <c r="P67" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P67" s="4" t="inlineStr"/>
       <c r="Q67" t="n">
-        <v>2184</v>
+        <v>2045</v>
       </c>
       <c r="R67" s="4" t="n">
-        <v>0.6872710622710623</v>
+        <v>0.6665036674816626</v>
       </c>
       <c r="S67" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="T67" s="4" t="n">
-        <v>0.7</v>
+        <v>0.7692307692307693</v>
       </c>
       <c r="U67" t="n">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="V67" s="4" t="n">
-        <v>0.8450704225352113</v>
+        <v>0.7818181818181819</v>
       </c>
       <c r="W67" t="n">
-        <v>1</v>
-      </c>
-      <c r="X67" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="X67" s="4" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="3" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>ODAS</t>
+          <t>TKFEN</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -7032,7 +6918,7 @@
         <v>2</v>
       </c>
       <c r="G68" t="n">
-        <v>1.08564720147204</v>
+        <v>1.763046506485244</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -7046,38 +6932,38 @@
         <v>0.553860819828408</v>
       </c>
       <c r="K68" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="L68" s="4" t="n">
-        <v>0.76</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="M68" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="N68" s="4" t="n">
-        <v>0.75</v>
+        <v>0.7586206896551724</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
       </c>
       <c r="P68" s="4" t="inlineStr"/>
       <c r="Q68" t="n">
-        <v>1042</v>
+        <v>1049</v>
       </c>
       <c r="R68" s="4" t="n">
-        <v>0.6525911708253359</v>
+        <v>0.6491897044804575</v>
       </c>
       <c r="S68" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="T68" s="4" t="n">
-        <v>0.76</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="U68" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="V68" s="4" t="n">
-        <v>0.8</v>
+        <v>0.8148148148148148</v>
       </c>
       <c r="W68" t="n">
         <v>0</v>
@@ -7086,11 +6972,11 @@
     </row>
     <row r="69">
       <c r="A69" s="3" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>ODAS</t>
+          <t>TKFEN</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -7110,7 +6996,7 @@
         <v>4</v>
       </c>
       <c r="G69" t="n">
-        <v>1.08564720147204</v>
+        <v>1.763046506485244</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -7118,61 +7004,57 @@
         </is>
       </c>
       <c r="I69" t="n">
+        <v>1918</v>
+      </c>
+      <c r="J69" s="4" t="n">
+        <v>0.5443169968717414</v>
+      </c>
+      <c r="K69" t="n">
+        <v>19</v>
+      </c>
+      <c r="L69" s="4" t="n">
+        <v>0.5789473684210527</v>
+      </c>
+      <c r="M69" t="n">
+        <v>54</v>
+      </c>
+      <c r="N69" s="4" t="n">
+        <v>0.7037037037037037</v>
+      </c>
+      <c r="O69" t="n">
+        <v>0</v>
+      </c>
+      <c r="P69" s="4" t="inlineStr"/>
+      <c r="Q69" t="n">
         <v>1916</v>
       </c>
-      <c r="J69" s="4" t="n">
-        <v>0.5443632567849687</v>
-      </c>
-      <c r="K69" t="n">
-        <v>33</v>
-      </c>
-      <c r="L69" s="4" t="n">
-        <v>0.7272727272727273</v>
-      </c>
-      <c r="M69" t="n">
-        <v>64</v>
-      </c>
-      <c r="N69" s="4" t="n">
-        <v>0.71875</v>
-      </c>
-      <c r="O69" t="n">
-        <v>1</v>
-      </c>
-      <c r="P69" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q69" t="n">
-        <v>1902</v>
-      </c>
       <c r="R69" s="4" t="n">
-        <v>0.655099894847529</v>
+        <v>0.651356993736952</v>
       </c>
       <c r="S69" t="n">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="T69" s="4" t="n">
-        <v>0.7575757575757576</v>
+        <v>0.631578947368421</v>
       </c>
       <c r="U69" t="n">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="V69" s="4" t="n">
-        <v>0.7936507936507936</v>
+        <v>0.7884615384615384</v>
       </c>
       <c r="W69" t="n">
-        <v>1</v>
-      </c>
-      <c r="X69" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="X69" s="4" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="3" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>ODAS</t>
+          <t>TKFEN</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -7192,7 +7074,7 @@
         <v>6</v>
       </c>
       <c r="G70" t="n">
-        <v>1.08564720147204</v>
+        <v>1.763046506485244</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -7200,61 +7082,57 @@
         </is>
       </c>
       <c r="I70" t="n">
+        <v>2523</v>
+      </c>
+      <c r="J70" s="4" t="n">
+        <v>0.5449861276258422</v>
+      </c>
+      <c r="K70" t="n">
+        <v>28</v>
+      </c>
+      <c r="L70" s="4" t="n">
+        <v>0.6071428571428571</v>
+      </c>
+      <c r="M70" t="n">
+        <v>64</v>
+      </c>
+      <c r="N70" s="4" t="n">
+        <v>0.734375</v>
+      </c>
+      <c r="O70" t="n">
+        <v>0</v>
+      </c>
+      <c r="P70" s="4" t="inlineStr"/>
+      <c r="Q70" t="n">
         <v>2521</v>
       </c>
-      <c r="J70" s="4" t="n">
-        <v>0.5450218167393891</v>
-      </c>
-      <c r="K70" t="n">
-        <v>44</v>
-      </c>
-      <c r="L70" s="4" t="n">
-        <v>0.7045454545454546</v>
-      </c>
-      <c r="M70" t="n">
-        <v>75</v>
-      </c>
-      <c r="N70" s="4" t="n">
-        <v>0.7333333333333333</v>
-      </c>
-      <c r="O70" t="n">
-        <v>1</v>
-      </c>
-      <c r="P70" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q70" t="n">
-        <v>2504</v>
-      </c>
       <c r="R70" s="4" t="n">
-        <v>0.6601437699680511</v>
+        <v>0.6568821896072987</v>
       </c>
       <c r="S70" t="n">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="T70" s="4" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.6785714285714286</v>
       </c>
       <c r="U70" t="n">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="V70" s="4" t="n">
-        <v>0.8082191780821918</v>
+        <v>0.8064516129032258</v>
       </c>
       <c r="W70" t="n">
-        <v>1</v>
-      </c>
-      <c r="X70" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="X70" s="4" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="3" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>ODAS</t>
+          <t>TKFEN</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -7274,18 +7152,18 @@
         <v>2</v>
       </c>
       <c r="G71" t="n">
-        <v>3.456786664007372</v>
+        <v>7.286247622124775</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>[2,4)</t>
+          <t>[6,8)</t>
         </is>
       </c>
       <c r="I71" t="n">
-        <v>644</v>
+        <v>473</v>
       </c>
       <c r="J71" s="4" t="n">
-        <v>0.531055900621118</v>
+        <v>0.5539112050739958</v>
       </c>
       <c r="K71" t="n">
         <v>5</v>
@@ -7294,20 +7172,20 @@
         <v>0.6</v>
       </c>
       <c r="M71" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="N71" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7692307692307693</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
       </c>
       <c r="P71" s="4" t="inlineStr"/>
       <c r="Q71" t="n">
-        <v>641</v>
+        <v>473</v>
       </c>
       <c r="R71" s="4" t="n">
-        <v>0.6708268330733229</v>
+        <v>0.6638477801268499</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -7316,10 +7194,10 @@
         <v>0.6</v>
       </c>
       <c r="U71" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="V71" s="4" t="n">
-        <v>0.6923076923076923</v>
+        <v>0.8461538461538461</v>
       </c>
       <c r="W71" t="n">
         <v>0</v>
@@ -7328,11 +7206,11 @@
     </row>
     <row r="72">
       <c r="A72" s="3" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>ODAS</t>
+          <t>TKFEN</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -7352,52 +7230,52 @@
         <v>4</v>
       </c>
       <c r="G72" t="n">
-        <v>3.456786664007372</v>
+        <v>7.286247622124775</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>[0,4)</t>
+          <t>[4,8)</t>
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1186</v>
+        <v>1119</v>
       </c>
       <c r="J72" s="4" t="n">
-        <v>0.5354131534569984</v>
+        <v>0.5781948168007149</v>
       </c>
       <c r="K72" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="L72" s="4" t="n">
-        <v>0.4545454545454545</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="M72" t="n">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="N72" s="4" t="n">
-        <v>0.6744186046511628</v>
+        <v>0.625</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
       </c>
       <c r="P72" s="4" t="inlineStr"/>
       <c r="Q72" t="n">
-        <v>1181</v>
+        <v>1118</v>
       </c>
       <c r="R72" s="4" t="n">
-        <v>0.6663844199830652</v>
+        <v>0.6833631484794276</v>
       </c>
       <c r="S72" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="T72" s="4" t="n">
-        <v>0.6363636363636364</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="U72" t="n">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="V72" s="4" t="n">
-        <v>0.7317073170731707</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="W72" t="n">
         <v>0</v>
@@ -7406,11 +7284,11 @@
     </row>
     <row r="73">
       <c r="A73" s="3" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>ODAS</t>
+          <t>TKFEN</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -7430,1488 +7308,60 @@
         <v>6</v>
       </c>
       <c r="G73" t="n">
-        <v>3.456786664007372</v>
+        <v>7.286247622124775</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>[0,6)</t>
+          <t>[6,12)</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1832</v>
+        <v>1138</v>
       </c>
       <c r="J73" s="4" t="n">
-        <v>0.5567685589519651</v>
+        <v>0.5606326889279437</v>
       </c>
       <c r="K73" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="L73" s="4" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.7058823529411765</v>
       </c>
       <c r="M73" t="n">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="N73" s="4" t="n">
-        <v>0.6363636363636364</v>
+        <v>0.75</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
       </c>
       <c r="P73" s="4" t="inlineStr"/>
       <c r="Q73" t="n">
-        <v>1823</v>
+        <v>1138</v>
       </c>
       <c r="R73" s="4" t="n">
-        <v>0.6785518376302797</v>
+        <v>0.6511423550087874</v>
       </c>
       <c r="S73" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="T73" s="4" t="n">
-        <v>0.64</v>
+        <v>0.7647058823529411</v>
       </c>
       <c r="U73" t="n">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="V73" s="4" t="n">
-        <v>0.6981132075471698</v>
+        <v>0.84375</v>
       </c>
       <c r="W73" t="n">
         <v>0</v>
       </c>
       <c r="X73" s="4" t="inlineStr"/>
     </row>
-    <row r="74">
-      <c r="A74" s="3" t="n">
-        <v>46223</v>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>THYAO</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>HAMMER</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="E74" t="n">
-        <v>3</v>
-      </c>
-      <c r="F74" t="n">
-        <v>2</v>
-      </c>
-      <c r="G74" t="n">
-        <v>0.6134969325153339</v>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>[0,2)</t>
-        </is>
-      </c>
-      <c r="I74" t="n">
-        <v>513</v>
-      </c>
-      <c r="J74" s="4" t="n">
-        <v>0.580896686159844</v>
-      </c>
-      <c r="K74" t="n">
-        <v>6</v>
-      </c>
-      <c r="L74" s="4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M74" t="n">
-        <v>11</v>
-      </c>
-      <c r="N74" s="4" t="n">
-        <v>0.2727272727272727</v>
-      </c>
-      <c r="O74" t="n">
-        <v>0</v>
-      </c>
-      <c r="P74" s="4" t="inlineStr"/>
-      <c r="Q74" t="n">
-        <v>512</v>
-      </c>
-      <c r="R74" s="4" t="n">
-        <v>0.6875</v>
-      </c>
-      <c r="S74" t="n">
-        <v>6</v>
-      </c>
-      <c r="T74" s="4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="U74" t="n">
-        <v>11</v>
-      </c>
-      <c r="V74" s="4" t="n">
-        <v>0.3636363636363636</v>
-      </c>
-      <c r="W74" t="n">
-        <v>0</v>
-      </c>
-      <c r="X74" s="4" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="3" t="n">
-        <v>46223</v>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>THYAO</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>HAMMER</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="E75" t="n">
-        <v>3</v>
-      </c>
-      <c r="F75" t="n">
-        <v>4</v>
-      </c>
-      <c r="G75" t="n">
-        <v>0.6134969325153339</v>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>[0,4)</t>
-        </is>
-      </c>
-      <c r="I75" t="n">
-        <v>684</v>
-      </c>
-      <c r="J75" s="4" t="n">
-        <v>0.5847953216374269</v>
-      </c>
-      <c r="K75" t="n">
-        <v>6</v>
-      </c>
-      <c r="L75" s="4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M75" t="n">
-        <v>17</v>
-      </c>
-      <c r="N75" s="4" t="n">
-        <v>0.4117647058823529</v>
-      </c>
-      <c r="O75" t="n">
-        <v>0</v>
-      </c>
-      <c r="P75" s="4" t="inlineStr"/>
-      <c r="Q75" t="n">
-        <v>683</v>
-      </c>
-      <c r="R75" s="4" t="n">
-        <v>0.6925329428989752</v>
-      </c>
-      <c r="S75" t="n">
-        <v>6</v>
-      </c>
-      <c r="T75" s="4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="U75" t="n">
-        <v>17</v>
-      </c>
-      <c r="V75" s="4" t="n">
-        <v>0.4705882352941176</v>
-      </c>
-      <c r="W75" t="n">
-        <v>0</v>
-      </c>
-      <c r="X75" s="4" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="3" t="n">
-        <v>46223</v>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>THYAO</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>HAMMER</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="E76" t="n">
-        <v>3</v>
-      </c>
-      <c r="F76" t="n">
-        <v>6</v>
-      </c>
-      <c r="G76" t="n">
-        <v>0.6134969325153339</v>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>[0,6)</t>
-        </is>
-      </c>
-      <c r="I76" t="n">
-        <v>747</v>
-      </c>
-      <c r="J76" s="4" t="n">
-        <v>0.5997322623828648</v>
-      </c>
-      <c r="K76" t="n">
-        <v>6</v>
-      </c>
-      <c r="L76" s="4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M76" t="n">
-        <v>18</v>
-      </c>
-      <c r="N76" s="4" t="n">
-        <v>0.4444444444444444</v>
-      </c>
-      <c r="O76" t="n">
-        <v>0</v>
-      </c>
-      <c r="P76" s="4" t="inlineStr"/>
-      <c r="Q76" t="n">
-        <v>746</v>
-      </c>
-      <c r="R76" s="4" t="n">
-        <v>0.7010723860589813</v>
-      </c>
-      <c r="S76" t="n">
-        <v>6</v>
-      </c>
-      <c r="T76" s="4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="U76" t="n">
-        <v>18</v>
-      </c>
-      <c r="V76" s="4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="W76" t="n">
-        <v>0</v>
-      </c>
-      <c r="X76" s="4" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="3" t="n">
-        <v>46223</v>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>THYAO</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>HAMMER</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="E77" t="n">
-        <v>5</v>
-      </c>
-      <c r="F77" t="n">
-        <v>2</v>
-      </c>
-      <c r="G77" t="n">
-        <v>-4.789550072568938</v>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>[-6,-4)</t>
-        </is>
-      </c>
-      <c r="I77" t="n">
-        <v>563</v>
-      </c>
-      <c r="J77" s="4" t="n">
-        <v>0.6607460035523979</v>
-      </c>
-      <c r="K77" t="n">
-        <v>1</v>
-      </c>
-      <c r="L77" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M77" t="n">
-        <v>18</v>
-      </c>
-      <c r="N77" s="4" t="n">
-        <v>0.6111111111111112</v>
-      </c>
-      <c r="O77" t="n">
-        <v>0</v>
-      </c>
-      <c r="P77" s="4" t="inlineStr"/>
-      <c r="Q77" t="n">
-        <v>563</v>
-      </c>
-      <c r="R77" s="4" t="n">
-        <v>0.7513321492007105</v>
-      </c>
-      <c r="S77" t="n">
-        <v>1</v>
-      </c>
-      <c r="T77" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U77" t="n">
-        <v>18</v>
-      </c>
-      <c r="V77" s="4" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="W77" t="n">
-        <v>0</v>
-      </c>
-      <c r="X77" s="4" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="3" t="n">
-        <v>46223</v>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>THYAO</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>HAMMER</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="E78" t="n">
-        <v>5</v>
-      </c>
-      <c r="F78" t="n">
-        <v>4</v>
-      </c>
-      <c r="G78" t="n">
-        <v>-4.789550072568938</v>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>[-8,-4)</t>
-        </is>
-      </c>
-      <c r="I78" t="n">
-        <v>866</v>
-      </c>
-      <c r="J78" s="4" t="n">
-        <v>0.6685912240184757</v>
-      </c>
-      <c r="K78" t="n">
-        <v>6</v>
-      </c>
-      <c r="L78" s="4" t="n">
-        <v>0.1666666666666667</v>
-      </c>
-      <c r="M78" t="n">
-        <v>32</v>
-      </c>
-      <c r="N78" s="4" t="n">
-        <v>0.59375</v>
-      </c>
-      <c r="O78" t="n">
-        <v>0</v>
-      </c>
-      <c r="P78" s="4" t="inlineStr"/>
-      <c r="Q78" t="n">
-        <v>865</v>
-      </c>
-      <c r="R78" s="4" t="n">
-        <v>0.7572254335260116</v>
-      </c>
-      <c r="S78" t="n">
-        <v>6</v>
-      </c>
-      <c r="T78" s="4" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="U78" t="n">
-        <v>32</v>
-      </c>
-      <c r="V78" s="4" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="W78" t="n">
-        <v>0</v>
-      </c>
-      <c r="X78" s="4" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="3" t="n">
-        <v>46223</v>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>THYAO</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>HAMMER</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="E79" t="n">
-        <v>5</v>
-      </c>
-      <c r="F79" t="n">
-        <v>6</v>
-      </c>
-      <c r="G79" t="n">
-        <v>-4.789550072568938</v>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>[-6,0)</t>
-        </is>
-      </c>
-      <c r="I79" t="n">
-        <v>1905</v>
-      </c>
-      <c r="J79" s="4" t="n">
-        <v>0.5994750656167979</v>
-      </c>
-      <c r="K79" t="n">
-        <v>17</v>
-      </c>
-      <c r="L79" s="4" t="n">
-        <v>0.7058823529411765</v>
-      </c>
-      <c r="M79" t="n">
-        <v>49</v>
-      </c>
-      <c r="N79" s="4" t="n">
-        <v>0.6122448979591837</v>
-      </c>
-      <c r="O79" t="n">
-        <v>0</v>
-      </c>
-      <c r="P79" s="4" t="inlineStr"/>
-      <c r="Q79" t="n">
-        <v>1905</v>
-      </c>
-      <c r="R79" s="4" t="n">
-        <v>0.7081364829396325</v>
-      </c>
-      <c r="S79" t="n">
-        <v>17</v>
-      </c>
-      <c r="T79" s="4" t="n">
-        <v>0.7058823529411765</v>
-      </c>
-      <c r="U79" t="n">
-        <v>48</v>
-      </c>
-      <c r="V79" s="4" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="W79" t="n">
-        <v>0</v>
-      </c>
-      <c r="X79" s="4" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="3" t="n">
-        <v>46223</v>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>THYAO</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>HAMMER</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="E80" t="n">
-        <v>10</v>
-      </c>
-      <c r="F80" t="n">
-        <v>2</v>
-      </c>
-      <c r="G80" t="n">
-        <v>-1.796407185628746</v>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>[-2,0)</t>
-        </is>
-      </c>
-      <c r="I80" t="n">
-        <v>374</v>
-      </c>
-      <c r="J80" s="4" t="n">
-        <v>0.553475935828877</v>
-      </c>
-      <c r="K80" t="n">
-        <v>1</v>
-      </c>
-      <c r="L80" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M80" t="n">
-        <v>3</v>
-      </c>
-      <c r="N80" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O80" t="n">
-        <v>0</v>
-      </c>
-      <c r="P80" s="4" t="inlineStr"/>
-      <c r="Q80" t="n">
-        <v>374</v>
-      </c>
-      <c r="R80" s="4" t="n">
-        <v>0.6631016042780749</v>
-      </c>
-      <c r="S80" t="n">
-        <v>1</v>
-      </c>
-      <c r="T80" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="U80" t="n">
-        <v>3</v>
-      </c>
-      <c r="V80" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="W80" t="n">
-        <v>0</v>
-      </c>
-      <c r="X80" s="4" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="3" t="n">
-        <v>46223</v>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>THYAO</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>HAMMER</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="E81" t="n">
-        <v>10</v>
-      </c>
-      <c r="F81" t="n">
-        <v>4</v>
-      </c>
-      <c r="G81" t="n">
-        <v>-1.796407185628746</v>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>[-4,0)</t>
-        </is>
-      </c>
-      <c r="I81" t="n">
-        <v>821</v>
-      </c>
-      <c r="J81" s="4" t="n">
-        <v>0.5639464068209501</v>
-      </c>
-      <c r="K81" t="n">
-        <v>4</v>
-      </c>
-      <c r="L81" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M81" t="n">
-        <v>17</v>
-      </c>
-      <c r="N81" s="4" t="n">
-        <v>0.6470588235294118</v>
-      </c>
-      <c r="O81" t="n">
-        <v>0</v>
-      </c>
-      <c r="P81" s="4" t="inlineStr"/>
-      <c r="Q81" t="n">
-        <v>821</v>
-      </c>
-      <c r="R81" s="4" t="n">
-        <v>0.6699147381242387</v>
-      </c>
-      <c r="S81" t="n">
-        <v>4</v>
-      </c>
-      <c r="T81" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="U81" t="n">
-        <v>17</v>
-      </c>
-      <c r="V81" s="4" t="n">
-        <v>0.6470588235294118</v>
-      </c>
-      <c r="W81" t="n">
-        <v>0</v>
-      </c>
-      <c r="X81" s="4" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="3" t="n">
-        <v>46223</v>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>THYAO</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>HAMMER</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="E82" t="n">
-        <v>10</v>
-      </c>
-      <c r="F82" t="n">
-        <v>6</v>
-      </c>
-      <c r="G82" t="n">
-        <v>-1.796407185628746</v>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>[-6,0)</t>
-        </is>
-      </c>
-      <c r="I82" t="n">
-        <v>1209</v>
-      </c>
-      <c r="J82" s="4" t="n">
-        <v>0.5798180314309347</v>
-      </c>
-      <c r="K82" t="n">
-        <v>8</v>
-      </c>
-      <c r="L82" s="4" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="M82" t="n">
-        <v>33</v>
-      </c>
-      <c r="N82" s="4" t="n">
-        <v>0.6363636363636364</v>
-      </c>
-      <c r="O82" t="n">
-        <v>0</v>
-      </c>
-      <c r="P82" s="4" t="inlineStr"/>
-      <c r="Q82" t="n">
-        <v>1209</v>
-      </c>
-      <c r="R82" s="4" t="n">
-        <v>0.6807278742762614</v>
-      </c>
-      <c r="S82" t="n">
-        <v>8</v>
-      </c>
-      <c r="T82" s="4" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="U82" t="n">
-        <v>33</v>
-      </c>
-      <c r="V82" s="4" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="W82" t="n">
-        <v>0</v>
-      </c>
-      <c r="X82" s="4" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="3" t="n">
-        <v>46223</v>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>VESTL</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>SHOOTING_STAR</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>SHORT</t>
-        </is>
-      </c>
-      <c r="E83" t="n">
-        <v>3</v>
-      </c>
-      <c r="F83" t="n">
-        <v>2</v>
-      </c>
-      <c r="G83" t="n">
-        <v>-3.379420265651756</v>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>[-4,-2)</t>
-        </is>
-      </c>
-      <c r="I83" t="n">
-        <v>347</v>
-      </c>
-      <c r="J83" s="4" t="n">
-        <v>0.5244956772334294</v>
-      </c>
-      <c r="K83" t="n">
-        <v>5</v>
-      </c>
-      <c r="L83" s="4" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="M83" t="n">
-        <v>9</v>
-      </c>
-      <c r="N83" s="4" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="O83" t="n">
-        <v>1</v>
-      </c>
-      <c r="P83" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q83" t="n">
-        <v>346</v>
-      </c>
-      <c r="R83" s="4" t="n">
-        <v>0.6213872832369942</v>
-      </c>
-      <c r="S83" t="n">
-        <v>5</v>
-      </c>
-      <c r="T83" s="4" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="U83" t="n">
-        <v>9</v>
-      </c>
-      <c r="V83" s="4" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="W83" t="n">
-        <v>1</v>
-      </c>
-      <c r="X83" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="3" t="n">
-        <v>46223</v>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>VESTL</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>SHOOTING_STAR</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>SHORT</t>
-        </is>
-      </c>
-      <c r="E84" t="n">
-        <v>3</v>
-      </c>
-      <c r="F84" t="n">
-        <v>4</v>
-      </c>
-      <c r="G84" t="n">
-        <v>-3.379420265651756</v>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>[-4,0)</t>
-        </is>
-      </c>
-      <c r="I84" t="n">
-        <v>1196</v>
-      </c>
-      <c r="J84" s="4" t="n">
-        <v>0.4966555183946488</v>
-      </c>
-      <c r="K84" t="n">
-        <v>14</v>
-      </c>
-      <c r="L84" s="4" t="n">
-        <v>0.5714285714285714</v>
-      </c>
-      <c r="M84" t="n">
-        <v>26</v>
-      </c>
-      <c r="N84" s="4" t="n">
-        <v>0.6153846153846154</v>
-      </c>
-      <c r="O84" t="n">
-        <v>1</v>
-      </c>
-      <c r="P84" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q84" t="n">
-        <v>1195</v>
-      </c>
-      <c r="R84" s="4" t="n">
-        <v>0.6033472803347281</v>
-      </c>
-      <c r="S84" t="n">
-        <v>14</v>
-      </c>
-      <c r="T84" s="4" t="n">
-        <v>0.6428571428571429</v>
-      </c>
-      <c r="U84" t="n">
-        <v>26</v>
-      </c>
-      <c r="V84" s="4" t="n">
-        <v>0.6538461538461539</v>
-      </c>
-      <c r="W84" t="n">
-        <v>1</v>
-      </c>
-      <c r="X84" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="3" t="n">
-        <v>46223</v>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>VESTL</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>SHOOTING_STAR</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>SHORT</t>
-        </is>
-      </c>
-      <c r="E85" t="n">
-        <v>3</v>
-      </c>
-      <c r="F85" t="n">
-        <v>6</v>
-      </c>
-      <c r="G85" t="n">
-        <v>-3.379420265651756</v>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>[-6,0)</t>
-        </is>
-      </c>
-      <c r="I85" t="n">
-        <v>1327</v>
-      </c>
-      <c r="J85" s="4" t="n">
-        <v>0.5026375282592314</v>
-      </c>
-      <c r="K85" t="n">
-        <v>19</v>
-      </c>
-      <c r="L85" s="4" t="n">
-        <v>0.4736842105263158</v>
-      </c>
-      <c r="M85" t="n">
-        <v>30</v>
-      </c>
-      <c r="N85" s="4" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="O85" t="n">
-        <v>1</v>
-      </c>
-      <c r="P85" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q85" t="n">
-        <v>1326</v>
-      </c>
-      <c r="R85" s="4" t="n">
-        <v>0.6063348416289592</v>
-      </c>
-      <c r="S85" t="n">
-        <v>19</v>
-      </c>
-      <c r="T85" s="4" t="n">
-        <v>0.5263157894736842</v>
-      </c>
-      <c r="U85" t="n">
-        <v>30</v>
-      </c>
-      <c r="V85" s="4" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="W85" t="n">
-        <v>1</v>
-      </c>
-      <c r="X85" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="3" t="n">
-        <v>46223</v>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>VESTL</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>SHOOTING_STAR</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>SHORT</t>
-        </is>
-      </c>
-      <c r="E86" t="n">
-        <v>5</v>
-      </c>
-      <c r="F86" t="n">
-        <v>2</v>
-      </c>
-      <c r="G86" t="n">
-        <v>-4.769115159891335</v>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>[-6,-4)</t>
-        </is>
-      </c>
-      <c r="I86" t="n">
-        <v>63</v>
-      </c>
-      <c r="J86" s="4" t="n">
-        <v>0.6031746031746031</v>
-      </c>
-      <c r="K86" t="n">
-        <v>0</v>
-      </c>
-      <c r="L86" s="4" t="inlineStr"/>
-      <c r="M86" t="n">
-        <v>5</v>
-      </c>
-      <c r="N86" s="4" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="O86" t="n">
-        <v>1</v>
-      </c>
-      <c r="P86" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q86" t="n">
-        <v>63</v>
-      </c>
-      <c r="R86" s="4" t="n">
-        <v>0.746031746031746</v>
-      </c>
-      <c r="S86" t="n">
-        <v>0</v>
-      </c>
-      <c r="T86" s="4" t="inlineStr"/>
-      <c r="U86" t="n">
-        <v>5</v>
-      </c>
-      <c r="V86" s="4" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="W86" t="n">
-        <v>1</v>
-      </c>
-      <c r="X86" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="3" t="n">
-        <v>46223</v>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>VESTL</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>SHOOTING_STAR</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>SHORT</t>
-        </is>
-      </c>
-      <c r="E87" t="n">
-        <v>5</v>
-      </c>
-      <c r="F87" t="n">
-        <v>4</v>
-      </c>
-      <c r="G87" t="n">
-        <v>-4.769115159891335</v>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>[-8,-4)</t>
-        </is>
-      </c>
-      <c r="I87" t="n">
-        <v>90</v>
-      </c>
-      <c r="J87" s="4" t="n">
-        <v>0.6111111111111112</v>
-      </c>
-      <c r="K87" t="n">
-        <v>0</v>
-      </c>
-      <c r="L87" s="4" t="inlineStr"/>
-      <c r="M87" t="n">
-        <v>5</v>
-      </c>
-      <c r="N87" s="4" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="O87" t="n">
-        <v>1</v>
-      </c>
-      <c r="P87" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q87" t="n">
-        <v>90</v>
-      </c>
-      <c r="R87" s="4" t="n">
-        <v>0.7555555555555555</v>
-      </c>
-      <c r="S87" t="n">
-        <v>0</v>
-      </c>
-      <c r="T87" s="4" t="inlineStr"/>
-      <c r="U87" t="n">
-        <v>5</v>
-      </c>
-      <c r="V87" s="4" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="W87" t="n">
-        <v>1</v>
-      </c>
-      <c r="X87" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="3" t="n">
-        <v>46223</v>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>VESTL</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>SHOOTING_STAR</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>SHORT</t>
-        </is>
-      </c>
-      <c r="E88" t="n">
-        <v>5</v>
-      </c>
-      <c r="F88" t="n">
-        <v>6</v>
-      </c>
-      <c r="G88" t="n">
-        <v>-4.769115159891335</v>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>[-6,0)</t>
-        </is>
-      </c>
-      <c r="I88" t="n">
-        <v>520</v>
-      </c>
-      <c r="J88" s="4" t="n">
-        <v>0.5461538461538461</v>
-      </c>
-      <c r="K88" t="n">
-        <v>5</v>
-      </c>
-      <c r="L88" s="4" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="M88" t="n">
-        <v>17</v>
-      </c>
-      <c r="N88" s="4" t="n">
-        <v>0.8235294117647058</v>
-      </c>
-      <c r="O88" t="n">
-        <v>1</v>
-      </c>
-      <c r="P88" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q88" t="n">
-        <v>520</v>
-      </c>
-      <c r="R88" s="4" t="n">
-        <v>0.6480769230769231</v>
-      </c>
-      <c r="S88" t="n">
-        <v>5</v>
-      </c>
-      <c r="T88" s="4" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="U88" t="n">
-        <v>17</v>
-      </c>
-      <c r="V88" s="4" t="n">
-        <v>0.8823529411764706</v>
-      </c>
-      <c r="W88" t="n">
-        <v>1</v>
-      </c>
-      <c r="X88" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="3" t="n">
-        <v>46223</v>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>VESTL</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>SHOOTING_STAR</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>SHORT</t>
-        </is>
-      </c>
-      <c r="E89" t="n">
-        <v>10</v>
-      </c>
-      <c r="F89" t="n">
-        <v>2</v>
-      </c>
-      <c r="G89" t="n">
-        <v>0.9630809405433149</v>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>[0,2)</t>
-        </is>
-      </c>
-      <c r="I89" t="n">
-        <v>580</v>
-      </c>
-      <c r="J89" s="4" t="n">
-        <v>0.4706896551724138</v>
-      </c>
-      <c r="K89" t="n">
-        <v>13</v>
-      </c>
-      <c r="L89" s="4" t="n">
-        <v>0.5384615384615384</v>
-      </c>
-      <c r="M89" t="n">
-        <v>15</v>
-      </c>
-      <c r="N89" s="4" t="n">
-        <v>0.4666666666666667</v>
-      </c>
-      <c r="O89" t="n">
-        <v>0</v>
-      </c>
-      <c r="P89" s="4" t="inlineStr"/>
-      <c r="Q89" t="n">
-        <v>579</v>
-      </c>
-      <c r="R89" s="4" t="n">
-        <v>0.5941278065630398</v>
-      </c>
-      <c r="S89" t="n">
-        <v>13</v>
-      </c>
-      <c r="T89" s="4" t="n">
-        <v>0.6153846153846154</v>
-      </c>
-      <c r="U89" t="n">
-        <v>13</v>
-      </c>
-      <c r="V89" s="4" t="n">
-        <v>0.7692307692307693</v>
-      </c>
-      <c r="W89" t="n">
-        <v>0</v>
-      </c>
-      <c r="X89" s="4" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="3" t="n">
-        <v>46223</v>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>VESTL</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>SHOOTING_STAR</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>SHORT</t>
-        </is>
-      </c>
-      <c r="E90" t="n">
-        <v>10</v>
-      </c>
-      <c r="F90" t="n">
-        <v>4</v>
-      </c>
-      <c r="G90" t="n">
-        <v>0.9630809405433149</v>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>[0,4)</t>
-        </is>
-      </c>
-      <c r="I90" t="n">
-        <v>1323</v>
-      </c>
-      <c r="J90" s="4" t="n">
-        <v>0.4822373393801965</v>
-      </c>
-      <c r="K90" t="n">
-        <v>28</v>
-      </c>
-      <c r="L90" s="4" t="n">
-        <v>0.6071428571428571</v>
-      </c>
-      <c r="M90" t="n">
-        <v>27</v>
-      </c>
-      <c r="N90" s="4" t="n">
-        <v>0.5555555555555556</v>
-      </c>
-      <c r="O90" t="n">
-        <v>1</v>
-      </c>
-      <c r="P90" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q90" t="n">
-        <v>1322</v>
-      </c>
-      <c r="R90" s="4" t="n">
-        <v>0.6013615733736762</v>
-      </c>
-      <c r="S90" t="n">
-        <v>28</v>
-      </c>
-      <c r="T90" s="4" t="n">
-        <v>0.7142857142857143</v>
-      </c>
-      <c r="U90" t="n">
-        <v>25</v>
-      </c>
-      <c r="V90" s="4" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="W90" t="n">
-        <v>1</v>
-      </c>
-      <c r="X90" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="3" t="n">
-        <v>46223</v>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>VESTL</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>SHOOTING_STAR</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>SHORT</t>
-        </is>
-      </c>
-      <c r="E91" t="n">
-        <v>10</v>
-      </c>
-      <c r="F91" t="n">
-        <v>6</v>
-      </c>
-      <c r="G91" t="n">
-        <v>0.9630809405433149</v>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>[0,6)</t>
-        </is>
-      </c>
-      <c r="I91" t="n">
-        <v>2108</v>
-      </c>
-      <c r="J91" s="4" t="n">
-        <v>0.4943074003795067</v>
-      </c>
-      <c r="K91" t="n">
-        <v>43</v>
-      </c>
-      <c r="L91" s="4" t="n">
-        <v>0.6046511627906976</v>
-      </c>
-      <c r="M91" t="n">
-        <v>46</v>
-      </c>
-      <c r="N91" s="4" t="n">
-        <v>0.6086956521739131</v>
-      </c>
-      <c r="O91" t="n">
-        <v>1</v>
-      </c>
-      <c r="P91" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q91" t="n">
-        <v>2106</v>
-      </c>
-      <c r="R91" s="4" t="n">
-        <v>0.6168091168091168</v>
-      </c>
-      <c r="S91" t="n">
-        <v>43</v>
-      </c>
-      <c r="T91" s="4" t="n">
-        <v>0.7209302325581395</v>
-      </c>
-      <c r="U91" t="n">
-        <v>44</v>
-      </c>
-      <c r="V91" s="4" t="n">
-        <v>0.7954545454545454</v>
-      </c>
-      <c r="W91" t="n">
-        <v>1</v>
-      </c>
-      <c r="X91" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:X91"/>
+  <autoFilter ref="A1:X73"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/pattern_report.xlsx
+++ b/pattern_report.xlsx
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>46231.78125834816</v>
+        <v>46231.97980701069</v>
       </c>
     </row>
     <row r="4">

--- a/pattern_report.xlsx
+++ b/pattern_report.xlsx
@@ -476,7 +476,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>V3</t>
+          <t>V4</t>
         </is>
       </c>
     </row>
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>46232.56231249999</v>
+        <v>46232.63286596074</v>
       </c>
     </row>
     <row r="4">

--- a/pattern_report.xlsx
+++ b/pattern_report.xlsx
@@ -9,14 +9,16 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OZET" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BUGUN_SINYALLER" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BUGUN_DEVAM_ANALIZI" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BUGUN_BENZER_HAREKET" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SISTEM_100G_OZET" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BUGUN_DEVAM_ANALIZI" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BUGUN_BENZER_HAREKET" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'OZET'!$A$1:$B$30</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'BUGUN_SINYALLER'!$A$1:$AA$33</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'BUGUN_DEVAM_ANALIZI'!$A$1:$AE$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'BUGUN_BENZER_HAREKET'!$A$1:$Y$127</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'BUGUN_SINYALLER'!$A$1:$AB$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'SISTEM_100G_OZET'!$A$1:$J$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'BUGUN_DEVAM_ANALIZI'!$A$1:$AE$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'BUGUN_BENZER_HAREKET'!$A$1:$Y$127</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -476,7 +478,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>V5</t>
+          <t>V7</t>
         </is>
       </c>
     </row>
@@ -487,7 +489,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>46232.73274214468</v>
+        <v>46232.80124854209</v>
       </c>
     </row>
     <row r="4">
@@ -788,7 +790,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA33"/>
+  <dimension ref="A1:AB33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -799,25 +801,26 @@
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="23" customWidth="1" min="9" max="9"/>
+    <col width="55" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
-    <col width="24" customWidth="1" min="11" max="11"/>
-    <col width="42" customWidth="1" min="12" max="12"/>
-    <col width="47" customWidth="1" min="13" max="13"/>
-    <col width="38" customWidth="1" min="14" max="14"/>
-    <col width="43" customWidth="1" min="15" max="15"/>
-    <col width="40" customWidth="1" min="16" max="16"/>
-    <col width="45" customWidth="1" min="17" max="17"/>
-    <col width="36" customWidth="1" min="18" max="18"/>
-    <col width="41" customWidth="1" min="19" max="19"/>
-    <col width="42" customWidth="1" min="20" max="20"/>
-    <col width="47" customWidth="1" min="21" max="21"/>
-    <col width="38" customWidth="1" min="22" max="22"/>
-    <col width="43" customWidth="1" min="23" max="23"/>
-    <col width="40" customWidth="1" min="24" max="24"/>
-    <col width="45" customWidth="1" min="25" max="25"/>
-    <col width="36" customWidth="1" min="26" max="26"/>
-    <col width="41" customWidth="1" min="27" max="27"/>
+    <col width="23" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="42" customWidth="1" min="13" max="13"/>
+    <col width="47" customWidth="1" min="14" max="14"/>
+    <col width="38" customWidth="1" min="15" max="15"/>
+    <col width="43" customWidth="1" min="16" max="16"/>
+    <col width="40" customWidth="1" min="17" max="17"/>
+    <col width="45" customWidth="1" min="18" max="18"/>
+    <col width="36" customWidth="1" min="19" max="19"/>
+    <col width="41" customWidth="1" min="20" max="20"/>
+    <col width="42" customWidth="1" min="21" max="21"/>
+    <col width="47" customWidth="1" min="22" max="22"/>
+    <col width="38" customWidth="1" min="23" max="23"/>
+    <col width="43" customWidth="1" min="24" max="24"/>
+    <col width="40" customWidth="1" min="25" max="25"/>
+    <col width="45" customWidth="1" min="26" max="26"/>
+    <col width="36" customWidth="1" min="27" max="27"/>
+    <col width="41" customWidth="1" min="28" max="28"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -863,95 +866,100 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>Son_100G_Uyan_Sistemler</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>Son_3_Gun_Hareket_Pct</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Son_5_Gun_Hareket_Pct</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Son_10_Gun_Hareket_Pct</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>TRAIN_10Y_Tum_Senetler_Ayni_Pattern_1G_N</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>TRAIN_10Y_Tum_Senetler_Ayni_Pattern_1G_Basari</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>TRAIN_10Y_Bu_Hisse_Ayni_Pattern_1G_N</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>TRAIN_10Y_Bu_Hisse_Ayni_Pattern_1G_Basari</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>TEST_3M_Tum_Senetler_Ayni_Pattern_1G_N</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>TEST_3M_Tum_Senetler_Ayni_Pattern_1G_Basari</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>TEST_3M_Bu_Hisse_Ayni_Pattern_1G_N</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>TEST_3M_Bu_Hisse_Ayni_Pattern_1G_Basari</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>TRAIN_10Y_Tum_Senetler_Ayni_Pattern_2G_N</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>TRAIN_10Y_Tum_Senetler_Ayni_Pattern_2G_Basari</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>TRAIN_10Y_Bu_Hisse_Ayni_Pattern_2G_N</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>TRAIN_10Y_Bu_Hisse_Ayni_Pattern_2G_Basari</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>TEST_3M_Tum_Senetler_Ayni_Pattern_2G_N</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>TEST_3M_Tum_Senetler_Ayni_Pattern_2G_Basari</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>TEST_3M_Bu_Hisse_Ayni_Pattern_2G_N</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>TEST_3M_Bu_Hisse_Ayni_Pattern_2G_Basari</t>
         </is>
@@ -992,61 +1000,66 @@
       <c r="H2" t="n">
         <v>21.26000023</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>E - %71.9 (n=1366); F - %70.9 (n=1142)</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
         <v>0.3777144420636702</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>-0.2814233624409579</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>-0.4681665596637852</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>5978</v>
       </c>
-      <c r="M2" s="4" t="n">
+      <c r="N2" s="4" t="n">
         <v>0.545332887253262</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>64</v>
       </c>
-      <c r="O2" s="4" t="n">
+      <c r="P2" s="4" t="n">
         <v>0.515625</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>143</v>
       </c>
-      <c r="Q2" s="4" t="n">
+      <c r="R2" s="4" t="n">
         <v>0.6783216783216783</v>
       </c>
-      <c r="R2" t="n">
+      <c r="S2" t="n">
         <v>2</v>
       </c>
-      <c r="S2" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="T2" t="n">
+      <c r="T2" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
         <v>5976</v>
       </c>
-      <c r="U2" s="4" t="n">
+      <c r="V2" s="4" t="n">
         <v>0.6549531459170014</v>
       </c>
-      <c r="V2" t="n">
+      <c r="W2" t="n">
         <v>64</v>
       </c>
-      <c r="W2" s="4" t="n">
+      <c r="X2" s="4" t="n">
         <v>0.609375</v>
       </c>
-      <c r="X2" t="n">
+      <c r="Y2" t="n">
         <v>139</v>
       </c>
-      <c r="Y2" s="4" t="n">
+      <c r="Z2" s="4" t="n">
         <v>0.7841726618705036</v>
       </c>
-      <c r="Z2" t="n">
+      <c r="AA2" t="n">
         <v>2</v>
       </c>
-      <c r="AA2" s="4" t="n">
+      <c r="AB2" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1085,61 +1098,62 @@
       <c r="H3" t="n">
         <v>125.69999695</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="n">
         <v>-0.2380976587301631</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>-0.1588598709844624</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>-2.482542359530704</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>5057</v>
       </c>
-      <c r="M3" s="4" t="n">
+      <c r="N3" s="4" t="n">
         <v>0.5896776745105794</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>59</v>
       </c>
-      <c r="O3" s="4" t="n">
+      <c r="P3" s="4" t="n">
         <v>0.4576271186440678</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>149</v>
       </c>
-      <c r="Q3" s="4" t="n">
+      <c r="R3" s="4" t="n">
         <v>0.738255033557047</v>
       </c>
-      <c r="R3" t="n">
-        <v>1</v>
-      </c>
-      <c r="S3" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="T3" t="n">
+      <c r="S3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="n">
         <v>5056</v>
       </c>
-      <c r="U3" s="4" t="n">
+      <c r="V3" s="4" t="n">
         <v>0.6867088607594937</v>
       </c>
-      <c r="V3" t="n">
+      <c r="W3" t="n">
         <v>59</v>
       </c>
-      <c r="W3" s="4" t="n">
+      <c r="X3" s="4" t="n">
         <v>0.6271186440677966</v>
       </c>
-      <c r="X3" t="n">
+      <c r="Y3" t="n">
         <v>149</v>
       </c>
-      <c r="Y3" s="4" t="n">
+      <c r="Z3" s="4" t="n">
         <v>0.8053691275167785</v>
       </c>
-      <c r="Z3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA3" s="4" t="n">
+      <c r="AA3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB3" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1178,59 +1192,64 @@
       <c r="H4" t="n">
         <v>6.71000004</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>G - %80.0 (n=205)</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
         <v>-0.5925920000000029</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>-0.8862620410229338</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>-4.00571872980191</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>3031</v>
       </c>
-      <c r="M4" s="4" t="n">
+      <c r="N4" s="4" t="n">
         <v>0.6423622566809634</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>5</v>
       </c>
-      <c r="O4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="P4" t="n">
+      <c r="P4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q4" t="n">
         <v>81</v>
       </c>
-      <c r="Q4" s="4" t="n">
+      <c r="R4" s="4" t="n">
         <v>0.6049382716049383</v>
       </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" s="4" t="inlineStr"/>
-      <c r="T4" t="n">
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" s="4" t="inlineStr"/>
+      <c r="U4" t="n">
         <v>3029</v>
       </c>
-      <c r="U4" s="4" t="n">
+      <c r="V4" s="4" t="n">
         <v>0.7388577088147904</v>
       </c>
-      <c r="V4" t="n">
+      <c r="W4" t="n">
         <v>5</v>
       </c>
-      <c r="W4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="X4" t="n">
+      <c r="X4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y4" t="n">
         <v>79</v>
       </c>
-      <c r="Y4" s="4" t="n">
+      <c r="Z4" s="4" t="n">
         <v>0.6708860759493671</v>
       </c>
-      <c r="Z4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA4" s="4" t="inlineStr"/>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1267,61 +1286,66 @@
       <c r="H5" t="n">
         <v>150.19999695</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>E - %71.9 (n=1366); F - %70.9 (n=1142); G - %71.1 (n=515)</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
         <v>0.1333313000000169</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>2.665751072245115</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>5.923831960030435</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>4260</v>
       </c>
-      <c r="M5" s="4" t="n">
+      <c r="N5" s="4" t="n">
         <v>0.5483568075117371</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>54</v>
       </c>
-      <c r="O5" s="4" t="n">
+      <c r="P5" s="4" t="n">
         <v>0.5740740740740741</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>80</v>
       </c>
-      <c r="Q5" s="4" t="n">
+      <c r="R5" s="4" t="n">
         <v>0.6</v>
       </c>
-      <c r="R5" t="n">
+      <c r="S5" t="n">
         <v>3</v>
       </c>
-      <c r="S5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="T5" t="n">
+      <c r="T5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
         <v>4259</v>
       </c>
-      <c r="U5" s="4" t="n">
+      <c r="V5" s="4" t="n">
         <v>0.6525005869922517</v>
       </c>
-      <c r="V5" t="n">
+      <c r="W5" t="n">
         <v>54</v>
       </c>
-      <c r="W5" s="4" t="n">
+      <c r="X5" s="4" t="n">
         <v>0.6296296296296297</v>
       </c>
-      <c r="X5" t="n">
+      <c r="Y5" t="n">
         <v>78</v>
       </c>
-      <c r="Y5" s="4" t="n">
+      <c r="Z5" s="4" t="n">
         <v>0.717948717948718</v>
       </c>
-      <c r="Z5" t="n">
+      <c r="AA5" t="n">
         <v>3</v>
       </c>
-      <c r="AA5" s="4" t="n">
+      <c r="AB5" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1360,61 +1384,66 @@
       <c r="H6" t="n">
         <v>566</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>E - %71.9 (n=1366); F - %70.9 (n=1142)</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
         <v>1.524663677130045</v>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>0.3546099290780091</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>6.89329556185081</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>5978</v>
       </c>
-      <c r="M6" s="4" t="n">
+      <c r="N6" s="4" t="n">
         <v>0.545332887253262</v>
       </c>
-      <c r="N6" t="n">
+      <c r="O6" t="n">
         <v>99</v>
       </c>
-      <c r="O6" s="4" t="n">
+      <c r="P6" s="4" t="n">
         <v>0.5959595959595959</v>
       </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="n">
         <v>143</v>
       </c>
-      <c r="Q6" s="4" t="n">
+      <c r="R6" s="4" t="n">
         <v>0.6783216783216783</v>
       </c>
-      <c r="R6" t="n">
-        <v>1</v>
-      </c>
-      <c r="S6" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="T6" t="n">
+      <c r="S6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
         <v>5976</v>
       </c>
-      <c r="U6" s="4" t="n">
+      <c r="V6" s="4" t="n">
         <v>0.6549531459170014</v>
       </c>
-      <c r="V6" t="n">
+      <c r="W6" t="n">
         <v>99</v>
       </c>
-      <c r="W6" s="4" t="n">
+      <c r="X6" s="4" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="X6" t="n">
+      <c r="Y6" t="n">
         <v>139</v>
       </c>
-      <c r="Y6" s="4" t="n">
+      <c r="Z6" s="4" t="n">
         <v>0.7841726618705036</v>
       </c>
-      <c r="Z6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA6" s="4" t="inlineStr"/>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1451,61 +1480,62 @@
       <c r="H7" t="n">
         <v>34.04000092</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="n">
         <v>-2.631573753462479</v>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>-3.678549022303856</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>-5.966850261469459</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>2416</v>
       </c>
-      <c r="M7" s="4" t="n">
+      <c r="N7" s="4" t="n">
         <v>0.6572847682119205</v>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>33</v>
       </c>
-      <c r="O7" s="4" t="n">
+      <c r="P7" s="4" t="n">
         <v>0.5757575757575758</v>
       </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="n">
         <v>63</v>
       </c>
-      <c r="Q7" s="4" t="n">
+      <c r="R7" s="4" t="n">
         <v>0.6507936507936508</v>
       </c>
-      <c r="R7" t="n">
+      <c r="S7" t="n">
         <v>2</v>
       </c>
-      <c r="S7" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="T7" t="n">
+      <c r="T7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
         <v>2416</v>
       </c>
-      <c r="U7" s="4" t="n">
+      <c r="V7" s="4" t="n">
         <v>0.7533112582781457</v>
       </c>
-      <c r="V7" t="n">
+      <c r="W7" t="n">
         <v>33</v>
       </c>
-      <c r="W7" s="4" t="n">
+      <c r="X7" s="4" t="n">
         <v>0.7575757575757576</v>
       </c>
-      <c r="X7" t="n">
+      <c r="Y7" t="n">
         <v>62</v>
       </c>
-      <c r="Y7" s="4" t="n">
+      <c r="Z7" s="4" t="n">
         <v>0.6935483870967742</v>
       </c>
-      <c r="Z7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA7" s="4" t="n">
+      <c r="AA7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB7" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1544,61 +1574,62 @@
       <c r="H8" t="n">
         <v>47.34000015</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="n">
         <v>-5.60319300951374</v>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>-6.535046949681689</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>1.806451935483877</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>3031</v>
       </c>
-      <c r="M8" s="4" t="n">
+      <c r="N8" s="4" t="n">
         <v>0.6423622566809634</v>
       </c>
-      <c r="N8" t="n">
+      <c r="O8" t="n">
         <v>49</v>
       </c>
-      <c r="O8" s="4" t="n">
+      <c r="P8" s="4" t="n">
         <v>0.5510204081632653</v>
       </c>
-      <c r="P8" t="n">
+      <c r="Q8" t="n">
         <v>81</v>
       </c>
-      <c r="Q8" s="4" t="n">
+      <c r="R8" s="4" t="n">
         <v>0.6049382716049383</v>
       </c>
-      <c r="R8" t="n">
-        <v>1</v>
-      </c>
-      <c r="S8" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="T8" t="n">
+      <c r="S8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
         <v>3029</v>
       </c>
-      <c r="U8" s="4" t="n">
+      <c r="V8" s="4" t="n">
         <v>0.7388577088147904</v>
       </c>
-      <c r="V8" t="n">
+      <c r="W8" t="n">
         <v>49</v>
       </c>
-      <c r="W8" s="4" t="n">
+      <c r="X8" s="4" t="n">
         <v>0.6530612244897959</v>
       </c>
-      <c r="X8" t="n">
+      <c r="Y8" t="n">
         <v>79</v>
       </c>
-      <c r="Y8" s="4" t="n">
+      <c r="Z8" s="4" t="n">
         <v>0.6708860759493671</v>
       </c>
-      <c r="Z8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA8" s="4" t="inlineStr"/>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1635,61 +1666,62 @@
       <c r="H9" t="n">
         <v>38</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="n">
         <v>-3.651112271856582</v>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>-5.472638603004842</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>-0.5235621885364639</v>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
         <v>3031</v>
       </c>
-      <c r="M9" s="4" t="n">
+      <c r="N9" s="4" t="n">
         <v>0.6423622566809634</v>
       </c>
-      <c r="N9" t="n">
+      <c r="O9" t="n">
         <v>8</v>
       </c>
-      <c r="O9" s="4" t="n">
+      <c r="P9" s="4" t="n">
         <v>0.625</v>
       </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
         <v>81</v>
       </c>
-      <c r="Q9" s="4" t="n">
+      <c r="R9" s="4" t="n">
         <v>0.6049382716049383</v>
       </c>
-      <c r="R9" t="n">
+      <c r="S9" t="n">
         <v>2</v>
       </c>
-      <c r="S9" s="4" t="n">
+      <c r="T9" s="4" t="n">
         <v>0.5</v>
       </c>
-      <c r="T9" t="n">
+      <c r="U9" t="n">
         <v>3029</v>
       </c>
-      <c r="U9" s="4" t="n">
+      <c r="V9" s="4" t="n">
         <v>0.7388577088147904</v>
       </c>
-      <c r="V9" t="n">
+      <c r="W9" t="n">
         <v>8</v>
       </c>
-      <c r="W9" s="4" t="n">
+      <c r="X9" s="4" t="n">
         <v>0.875</v>
       </c>
-      <c r="X9" t="n">
+      <c r="Y9" t="n">
         <v>79</v>
       </c>
-      <c r="Y9" s="4" t="n">
+      <c r="Z9" s="4" t="n">
         <v>0.6708860759493671</v>
       </c>
-      <c r="Z9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA9" s="4" t="n">
+      <c r="AA9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB9" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1728,61 +1760,66 @@
       <c r="H10" t="n">
         <v>127.40000153</v>
       </c>
-      <c r="I10" t="n">
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>F - %70.9 (n=1142)</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
         <v>1.920001224000001</v>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>2.576493283883297</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>0.5524898159833702</v>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>4260</v>
       </c>
-      <c r="M10" s="4" t="n">
+      <c r="N10" s="4" t="n">
         <v>0.5483568075117371</v>
       </c>
-      <c r="N10" t="n">
+      <c r="O10" t="n">
         <v>39</v>
       </c>
-      <c r="O10" s="4" t="n">
+      <c r="P10" s="4" t="n">
         <v>0.5384615384615384</v>
       </c>
-      <c r="P10" t="n">
+      <c r="Q10" t="n">
         <v>80</v>
       </c>
-      <c r="Q10" s="4" t="n">
+      <c r="R10" s="4" t="n">
         <v>0.6</v>
       </c>
-      <c r="R10" t="n">
-        <v>1</v>
-      </c>
-      <c r="S10" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="T10" t="n">
+      <c r="S10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
         <v>4259</v>
       </c>
-      <c r="U10" s="4" t="n">
+      <c r="V10" s="4" t="n">
         <v>0.6525005869922517</v>
       </c>
-      <c r="V10" t="n">
+      <c r="W10" t="n">
         <v>39</v>
       </c>
-      <c r="W10" s="4" t="n">
+      <c r="X10" s="4" t="n">
         <v>0.6410256410256411</v>
       </c>
-      <c r="X10" t="n">
+      <c r="Y10" t="n">
         <v>78</v>
       </c>
-      <c r="Y10" s="4" t="n">
+      <c r="Z10" s="4" t="n">
         <v>0.717948717948718</v>
       </c>
-      <c r="Z10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA10" s="4" t="inlineStr"/>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1819,61 +1856,66 @@
       <c r="H11" t="n">
         <v>68.15000153</v>
       </c>
-      <c r="I11" t="n">
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>G - %71.1 (n=515)</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
         <v>-6.898901134448754</v>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>12.64463062809917</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>-3.470250698434618</v>
       </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
         <v>5978</v>
       </c>
-      <c r="M11" s="4" t="n">
+      <c r="N11" s="4" t="n">
         <v>0.545332887253262</v>
       </c>
-      <c r="N11" t="n">
+      <c r="O11" t="n">
         <v>86</v>
       </c>
-      <c r="O11" s="4" t="n">
+      <c r="P11" s="4" t="n">
         <v>0.6162790697674418</v>
       </c>
-      <c r="P11" t="n">
+      <c r="Q11" t="n">
         <v>143</v>
       </c>
-      <c r="Q11" s="4" t="n">
+      <c r="R11" s="4" t="n">
         <v>0.6783216783216783</v>
       </c>
-      <c r="R11" t="n">
+      <c r="S11" t="n">
         <v>7</v>
       </c>
-      <c r="S11" s="4" t="n">
+      <c r="T11" s="4" t="n">
         <v>0.7142857142857143</v>
       </c>
-      <c r="T11" t="n">
+      <c r="U11" t="n">
         <v>5976</v>
       </c>
-      <c r="U11" s="4" t="n">
+      <c r="V11" s="4" t="n">
         <v>0.6549531459170014</v>
       </c>
-      <c r="V11" t="n">
+      <c r="W11" t="n">
         <v>86</v>
       </c>
-      <c r="W11" s="4" t="n">
+      <c r="X11" s="4" t="n">
         <v>0.6976744186046512</v>
       </c>
-      <c r="X11" t="n">
+      <c r="Y11" t="n">
         <v>139</v>
       </c>
-      <c r="Y11" s="4" t="n">
+      <c r="Z11" s="4" t="n">
         <v>0.7841726618705036</v>
       </c>
-      <c r="Z11" t="n">
+      <c r="AA11" t="n">
         <v>6</v>
       </c>
-      <c r="AA11" s="4" t="n">
+      <c r="AB11" s="4" t="n">
         <v>0.8333333333333334</v>
       </c>
     </row>
@@ -1912,61 +1954,62 @@
       <c r="H12" t="n">
         <v>634</v>
       </c>
-      <c r="I12" t="n">
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="n">
         <v>0.5551149881046769</v>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>-0.3144654088050314</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>1.27795527156549</v>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
         <v>2020</v>
       </c>
-      <c r="M12" s="4" t="n">
+      <c r="N12" s="4" t="n">
         <v>0.6866336633663367</v>
       </c>
-      <c r="N12" t="n">
+      <c r="O12" t="n">
         <v>21</v>
       </c>
-      <c r="O12" s="4" t="n">
+      <c r="P12" s="4" t="n">
         <v>0.7142857142857143</v>
       </c>
-      <c r="P12" t="n">
+      <c r="Q12" t="n">
         <v>98</v>
       </c>
-      <c r="Q12" s="4" t="n">
+      <c r="R12" s="4" t="n">
         <v>0.6326530612244898</v>
       </c>
-      <c r="R12" t="n">
-        <v>1</v>
-      </c>
-      <c r="S12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
+      <c r="S12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
         <v>2016</v>
       </c>
-      <c r="U12" s="4" t="n">
+      <c r="V12" s="4" t="n">
         <v>0.7633928571428571</v>
       </c>
-      <c r="V12" t="n">
+      <c r="W12" t="n">
         <v>21</v>
       </c>
-      <c r="W12" s="4" t="n">
+      <c r="X12" s="4" t="n">
         <v>0.7619047619047619</v>
       </c>
-      <c r="X12" t="n">
+      <c r="Y12" t="n">
         <v>97</v>
       </c>
-      <c r="Y12" s="4" t="n">
+      <c r="Z12" s="4" t="n">
         <v>0.711340206185567</v>
       </c>
-      <c r="Z12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA12" s="4" t="inlineStr"/>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2003,61 +2046,66 @@
       <c r="H13" t="n">
         <v>8.60999966</v>
       </c>
-      <c r="I13" t="n">
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>E - %71.9 (n=1366); G - %71.1 (n=515)</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
         <v>-5.79869431383413</v>
       </c>
-      <c r="J13" t="n">
+      <c r="K13" t="n">
         <v>1.175081401848566</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>3.985506530928351</v>
       </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
         <v>4260</v>
       </c>
-      <c r="M13" s="4" t="n">
+      <c r="N13" s="4" t="n">
         <v>0.5483568075117371</v>
       </c>
-      <c r="N13" t="n">
+      <c r="O13" t="n">
         <v>64</v>
       </c>
-      <c r="O13" s="4" t="n">
+      <c r="P13" s="4" t="n">
         <v>0.625</v>
       </c>
-      <c r="P13" t="n">
+      <c r="Q13" t="n">
         <v>80</v>
       </c>
-      <c r="Q13" s="4" t="n">
+      <c r="R13" s="4" t="n">
         <v>0.6</v>
       </c>
-      <c r="R13" t="n">
-        <v>1</v>
-      </c>
-      <c r="S13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
         <v>4259</v>
       </c>
-      <c r="U13" s="4" t="n">
+      <c r="V13" s="4" t="n">
         <v>0.6525005869922517</v>
       </c>
-      <c r="V13" t="n">
+      <c r="W13" t="n">
         <v>64</v>
       </c>
-      <c r="W13" s="4" t="n">
+      <c r="X13" s="4" t="n">
         <v>0.6875</v>
       </c>
-      <c r="X13" t="n">
+      <c r="Y13" t="n">
         <v>78</v>
       </c>
-      <c r="Y13" s="4" t="n">
+      <c r="Z13" s="4" t="n">
         <v>0.717948717948718</v>
       </c>
-      <c r="Z13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA13" s="4" t="inlineStr"/>
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2094,61 +2142,66 @@
       <c r="H14" t="n">
         <v>8.60999966</v>
       </c>
-      <c r="I14" t="n">
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>E - %71.9 (n=1366); G - %71.1 (n=515)</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
         <v>-5.79869431383413</v>
       </c>
-      <c r="J14" t="n">
+      <c r="K14" t="n">
         <v>1.175081401848566</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>3.985506530928351</v>
       </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
         <v>5978</v>
       </c>
-      <c r="M14" s="4" t="n">
+      <c r="N14" s="4" t="n">
         <v>0.545332887253262</v>
       </c>
-      <c r="N14" t="n">
+      <c r="O14" t="n">
         <v>80</v>
       </c>
-      <c r="O14" s="4" t="n">
+      <c r="P14" s="4" t="n">
         <v>0.5375</v>
       </c>
-      <c r="P14" t="n">
+      <c r="Q14" t="n">
         <v>143</v>
       </c>
-      <c r="Q14" s="4" t="n">
+      <c r="R14" s="4" t="n">
         <v>0.6783216783216783</v>
       </c>
-      <c r="R14" t="n">
-        <v>1</v>
-      </c>
-      <c r="S14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" t="n">
+      <c r="S14" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
         <v>5976</v>
       </c>
-      <c r="U14" s="4" t="n">
+      <c r="V14" s="4" t="n">
         <v>0.6549531459170014</v>
       </c>
-      <c r="V14" t="n">
+      <c r="W14" t="n">
         <v>80</v>
       </c>
-      <c r="W14" s="4" t="n">
+      <c r="X14" s="4" t="n">
         <v>0.575</v>
       </c>
-      <c r="X14" t="n">
+      <c r="Y14" t="n">
         <v>139</v>
       </c>
-      <c r="Y14" s="4" t="n">
+      <c r="Z14" s="4" t="n">
         <v>0.7841726618705036</v>
       </c>
-      <c r="Z14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA14" s="4" t="inlineStr"/>
+      <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2185,61 +2238,66 @@
       <c r="H15" t="n">
         <v>3.63000011</v>
       </c>
-      <c r="I15" t="n">
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>H - %74.8 (n=326)</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
         <v>-6.683804198359788</v>
       </c>
-      <c r="J15" t="n">
+      <c r="K15" t="n">
         <v>-2.156332321764609</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>2.253525665542622</v>
       </c>
-      <c r="L15" t="n">
+      <c r="M15" t="n">
         <v>5978</v>
       </c>
-      <c r="M15" s="4" t="n">
+      <c r="N15" s="4" t="n">
         <v>0.545332887253262</v>
       </c>
-      <c r="N15" t="n">
+      <c r="O15" t="n">
         <v>54</v>
       </c>
-      <c r="O15" s="4" t="n">
+      <c r="P15" s="4" t="n">
         <v>0.462962962962963</v>
       </c>
-      <c r="P15" t="n">
+      <c r="Q15" t="n">
         <v>143</v>
       </c>
-      <c r="Q15" s="4" t="n">
+      <c r="R15" s="4" t="n">
         <v>0.6783216783216783</v>
       </c>
-      <c r="R15" t="n">
+      <c r="S15" t="n">
         <v>3</v>
       </c>
-      <c r="S15" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="T15" t="n">
+      <c r="T15" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
         <v>5976</v>
       </c>
-      <c r="U15" s="4" t="n">
+      <c r="V15" s="4" t="n">
         <v>0.6549531459170014</v>
       </c>
-      <c r="V15" t="n">
+      <c r="W15" t="n">
         <v>54</v>
       </c>
-      <c r="W15" s="4" t="n">
+      <c r="X15" s="4" t="n">
         <v>0.5740740740740741</v>
       </c>
-      <c r="X15" t="n">
+      <c r="Y15" t="n">
         <v>139</v>
       </c>
-      <c r="Y15" s="4" t="n">
+      <c r="Z15" s="4" t="n">
         <v>0.7841726618705036</v>
       </c>
-      <c r="Z15" t="n">
+      <c r="AA15" t="n">
         <v>2</v>
       </c>
-      <c r="AA15" s="4" t="n">
+      <c r="AB15" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2278,61 +2336,66 @@
       <c r="H16" t="n">
         <v>360.5</v>
       </c>
-      <c r="I16" t="n">
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>A - %74.1 (n=844); G - %71.1 (n=515)</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
         <v>-2.567567567567564</v>
       </c>
-      <c r="J16" t="n">
+      <c r="K16" t="n">
         <v>1.692524682651619</v>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
         <v>-2.567567567567564</v>
       </c>
-      <c r="L16" t="n">
+      <c r="M16" t="n">
         <v>5057</v>
       </c>
-      <c r="M16" s="4" t="n">
+      <c r="N16" s="4" t="n">
         <v>0.5896776745105794</v>
       </c>
-      <c r="N16" t="n">
+      <c r="O16" t="n">
         <v>73</v>
       </c>
-      <c r="O16" s="4" t="n">
+      <c r="P16" s="4" t="n">
         <v>0.5068493150684932</v>
       </c>
-      <c r="P16" t="n">
+      <c r="Q16" t="n">
         <v>149</v>
       </c>
-      <c r="Q16" s="4" t="n">
+      <c r="R16" s="4" t="n">
         <v>0.738255033557047</v>
       </c>
-      <c r="R16" t="n">
+      <c r="S16" t="n">
         <v>3</v>
       </c>
-      <c r="S16" s="4" t="n">
+      <c r="T16" s="4" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="T16" t="n">
+      <c r="U16" t="n">
         <v>5056</v>
       </c>
-      <c r="U16" s="4" t="n">
+      <c r="V16" s="4" t="n">
         <v>0.6867088607594937</v>
       </c>
-      <c r="V16" t="n">
+      <c r="W16" t="n">
         <v>73</v>
       </c>
-      <c r="W16" s="4" t="n">
+      <c r="X16" s="4" t="n">
         <v>0.589041095890411</v>
       </c>
-      <c r="X16" t="n">
+      <c r="Y16" t="n">
         <v>149</v>
       </c>
-      <c r="Y16" s="4" t="n">
+      <c r="Z16" s="4" t="n">
         <v>0.8053691275167785</v>
       </c>
-      <c r="Z16" t="n">
+      <c r="AA16" t="n">
         <v>3</v>
       </c>
-      <c r="AA16" s="4" t="n">
+      <c r="AB16" s="4" t="n">
         <v>0.6666666666666666</v>
       </c>
     </row>
@@ -2371,61 +2434,66 @@
       <c r="H17" t="n">
         <v>98.19999695</v>
       </c>
-      <c r="I17" t="n">
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>A - %74.1 (n=844); E - %71.9 (n=1366); G - %71.1 (n=515)</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
         <v>-1.405624037656683</v>
       </c>
-      <c r="J17" t="n">
+      <c r="K17" t="n">
         <v>2.29166348958334</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>7.381082804945893</v>
       </c>
-      <c r="L17" t="n">
+      <c r="M17" t="n">
         <v>5057</v>
       </c>
-      <c r="M17" s="4" t="n">
+      <c r="N17" s="4" t="n">
         <v>0.5896776745105794</v>
       </c>
-      <c r="N17" t="n">
+      <c r="O17" t="n">
         <v>23</v>
       </c>
-      <c r="O17" s="4" t="n">
+      <c r="P17" s="4" t="n">
         <v>0.6086956521739131</v>
       </c>
-      <c r="P17" t="n">
+      <c r="Q17" t="n">
         <v>149</v>
       </c>
-      <c r="Q17" s="4" t="n">
+      <c r="R17" s="4" t="n">
         <v>0.738255033557047</v>
       </c>
-      <c r="R17" t="n">
+      <c r="S17" t="n">
         <v>3</v>
       </c>
-      <c r="S17" s="4" t="n">
+      <c r="T17" s="4" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="T17" t="n">
+      <c r="U17" t="n">
         <v>5056</v>
       </c>
-      <c r="U17" s="4" t="n">
+      <c r="V17" s="4" t="n">
         <v>0.6867088607594937</v>
       </c>
-      <c r="V17" t="n">
+      <c r="W17" t="n">
         <v>23</v>
       </c>
-      <c r="W17" s="4" t="n">
+      <c r="X17" s="4" t="n">
         <v>0.7391304347826086</v>
       </c>
-      <c r="X17" t="n">
+      <c r="Y17" t="n">
         <v>149</v>
       </c>
-      <c r="Y17" s="4" t="n">
+      <c r="Z17" s="4" t="n">
         <v>0.8053691275167785</v>
       </c>
-      <c r="Z17" t="n">
+      <c r="AA17" t="n">
         <v>3</v>
       </c>
-      <c r="AA17" s="4" t="n">
+      <c r="AB17" s="4" t="n">
         <v>0.6666666666666666</v>
       </c>
     </row>
@@ -2464,61 +2532,66 @@
       <c r="H18" t="n">
         <v>155.8999939</v>
       </c>
-      <c r="I18" t="n">
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>A - %80.9 (n=256); H - %80.2 (n=197); I - %82.7 (n=231); J - %80.5 (n=370)</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
         <v>-10.9142892</v>
       </c>
-      <c r="J18" t="n">
+      <c r="K18" t="n">
         <v>-13.67663973738925</v>
       </c>
-      <c r="K18" t="n">
+      <c r="L18" t="n">
         <v>-17.94737163157895</v>
       </c>
-      <c r="L18" t="n">
+      <c r="M18" t="n">
         <v>2416</v>
       </c>
-      <c r="M18" s="4" t="n">
+      <c r="N18" s="4" t="n">
         <v>0.6572847682119205</v>
       </c>
-      <c r="N18" t="n">
+      <c r="O18" t="n">
         <v>4</v>
       </c>
-      <c r="O18" s="4" t="n">
+      <c r="P18" s="4" t="n">
         <v>0.75</v>
       </c>
-      <c r="P18" t="n">
+      <c r="Q18" t="n">
         <v>63</v>
       </c>
-      <c r="Q18" s="4" t="n">
+      <c r="R18" s="4" t="n">
         <v>0.6507936507936508</v>
       </c>
-      <c r="R18" t="n">
-        <v>1</v>
-      </c>
-      <c r="S18" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="T18" t="n">
+      <c r="S18" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
         <v>2416</v>
       </c>
-      <c r="U18" s="4" t="n">
+      <c r="V18" s="4" t="n">
         <v>0.7533112582781457</v>
       </c>
-      <c r="V18" t="n">
+      <c r="W18" t="n">
         <v>4</v>
       </c>
-      <c r="W18" s="4" t="n">
+      <c r="X18" s="4" t="n">
         <v>0.75</v>
       </c>
-      <c r="X18" t="n">
+      <c r="Y18" t="n">
         <v>62</v>
       </c>
-      <c r="Y18" s="4" t="n">
+      <c r="Z18" s="4" t="n">
         <v>0.6935483870967742</v>
       </c>
-      <c r="Z18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA18" s="4" t="n">
+      <c r="AA18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB18" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2557,61 +2630,66 @@
       <c r="H19" t="n">
         <v>155.8999939</v>
       </c>
-      <c r="I19" t="n">
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>A - %80.9 (n=256); H - %80.2 (n=197); I - %82.7 (n=231); J - %80.5 (n=370)</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
         <v>-10.9142892</v>
       </c>
-      <c r="J19" t="n">
+      <c r="K19" t="n">
         <v>-13.67663973738925</v>
       </c>
-      <c r="K19" t="n">
+      <c r="L19" t="n">
         <v>-17.94737163157895</v>
       </c>
-      <c r="L19" t="n">
+      <c r="M19" t="n">
         <v>3031</v>
       </c>
-      <c r="M19" s="4" t="n">
+      <c r="N19" s="4" t="n">
         <v>0.6423622566809634</v>
       </c>
-      <c r="N19" t="n">
+      <c r="O19" t="n">
         <v>10</v>
       </c>
-      <c r="O19" s="4" t="n">
+      <c r="P19" s="4" t="n">
         <v>0.7</v>
       </c>
-      <c r="P19" t="n">
+      <c r="Q19" t="n">
         <v>81</v>
       </c>
-      <c r="Q19" s="4" t="n">
+      <c r="R19" s="4" t="n">
         <v>0.6049382716049383</v>
       </c>
-      <c r="R19" t="n">
+      <c r="S19" t="n">
         <v>3</v>
       </c>
-      <c r="S19" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="T19" t="n">
+      <c r="T19" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
         <v>3029</v>
       </c>
-      <c r="U19" s="4" t="n">
+      <c r="V19" s="4" t="n">
         <v>0.7388577088147904</v>
       </c>
-      <c r="V19" t="n">
+      <c r="W19" t="n">
         <v>10</v>
       </c>
-      <c r="W19" s="4" t="n">
+      <c r="X19" s="4" t="n">
         <v>0.8</v>
       </c>
-      <c r="X19" t="n">
+      <c r="Y19" t="n">
         <v>79</v>
       </c>
-      <c r="Y19" s="4" t="n">
+      <c r="Z19" s="4" t="n">
         <v>0.6708860759493671</v>
       </c>
-      <c r="Z19" t="n">
+      <c r="AA19" t="n">
         <v>3</v>
       </c>
-      <c r="AA19" s="4" t="n">
+      <c r="AB19" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2650,61 +2728,66 @@
       <c r="H20" t="n">
         <v>20.34000015</v>
       </c>
-      <c r="I20" t="n">
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>A - %74.1 (n=844)</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
         <v>-4.507038142035147</v>
       </c>
-      <c r="J20" t="n">
+      <c r="K20" t="n">
         <v>0.3948663331283742</v>
       </c>
-      <c r="K20" t="n">
+      <c r="L20" t="n">
         <v>0.6930662610529437</v>
       </c>
-      <c r="L20" t="n">
+      <c r="M20" t="n">
         <v>5057</v>
       </c>
-      <c r="M20" s="4" t="n">
+      <c r="N20" s="4" t="n">
         <v>0.5896776745105794</v>
       </c>
-      <c r="N20" t="n">
+      <c r="O20" t="n">
         <v>55</v>
       </c>
-      <c r="O20" s="4" t="n">
+      <c r="P20" s="4" t="n">
         <v>0.5636363636363636</v>
       </c>
-      <c r="P20" t="n">
+      <c r="Q20" t="n">
         <v>149</v>
       </c>
-      <c r="Q20" s="4" t="n">
+      <c r="R20" s="4" t="n">
         <v>0.738255033557047</v>
       </c>
-      <c r="R20" t="n">
+      <c r="S20" t="n">
         <v>2</v>
       </c>
-      <c r="S20" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="T20" t="n">
+      <c r="T20" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
         <v>5056</v>
       </c>
-      <c r="U20" s="4" t="n">
+      <c r="V20" s="4" t="n">
         <v>0.6867088607594937</v>
       </c>
-      <c r="V20" t="n">
+      <c r="W20" t="n">
         <v>55</v>
       </c>
-      <c r="W20" s="4" t="n">
+      <c r="X20" s="4" t="n">
         <v>0.6909090909090909</v>
       </c>
-      <c r="X20" t="n">
+      <c r="Y20" t="n">
         <v>149</v>
       </c>
-      <c r="Y20" s="4" t="n">
+      <c r="Z20" s="4" t="n">
         <v>0.8053691275167785</v>
       </c>
-      <c r="Z20" t="n">
+      <c r="AA20" t="n">
         <v>2</v>
       </c>
-      <c r="AA20" s="4" t="n">
+      <c r="AB20" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2743,61 +2826,66 @@
       <c r="H21" t="n">
         <v>3.71000004</v>
       </c>
-      <c r="I21" t="n">
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>A - %74.1 (n=844); E - %71.9 (n=1366); H - %74.8 (n=326)</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
         <v>-7.249998999999995</v>
       </c>
-      <c r="J21" t="n">
+      <c r="K21" t="n">
         <v>9.763311220720649</v>
       </c>
-      <c r="K21" t="n">
+      <c r="L21" t="n">
         <v>6.609195939027623</v>
       </c>
-      <c r="L21" t="n">
+      <c r="M21" t="n">
         <v>5057</v>
       </c>
-      <c r="M21" s="4" t="n">
+      <c r="N21" s="4" t="n">
         <v>0.5896776745105794</v>
       </c>
-      <c r="N21" t="n">
+      <c r="O21" t="n">
         <v>37</v>
       </c>
-      <c r="O21" s="4" t="n">
+      <c r="P21" s="4" t="n">
         <v>0.5675675675675675</v>
       </c>
-      <c r="P21" t="n">
+      <c r="Q21" t="n">
         <v>149</v>
       </c>
-      <c r="Q21" s="4" t="n">
+      <c r="R21" s="4" t="n">
         <v>0.738255033557047</v>
       </c>
-      <c r="R21" t="n">
+      <c r="S21" t="n">
         <v>3</v>
       </c>
-      <c r="S21" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="T21" t="n">
+      <c r="T21" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
         <v>5056</v>
       </c>
-      <c r="U21" s="4" t="n">
+      <c r="V21" s="4" t="n">
         <v>0.6867088607594937</v>
       </c>
-      <c r="V21" t="n">
+      <c r="W21" t="n">
         <v>37</v>
       </c>
-      <c r="W21" s="4" t="n">
+      <c r="X21" s="4" t="n">
         <v>0.6216216216216216</v>
       </c>
-      <c r="X21" t="n">
+      <c r="Y21" t="n">
         <v>149</v>
       </c>
-      <c r="Y21" s="4" t="n">
+      <c r="Z21" s="4" t="n">
         <v>0.8053691275167785</v>
       </c>
-      <c r="Z21" t="n">
+      <c r="AA21" t="n">
         <v>3</v>
       </c>
-      <c r="AA21" s="4" t="n">
+      <c r="AB21" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2836,61 +2924,66 @@
       <c r="H22" t="n">
         <v>2.56999993</v>
       </c>
-      <c r="I22" t="n">
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>A - %74.1 (n=844); E - %71.9 (n=1366); G - %71.1 (n=515)</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
         <v>-2.651521490472675</v>
       </c>
-      <c r="J22" t="n">
+      <c r="K22" t="n">
         <v>1.181101199702383</v>
       </c>
-      <c r="K22" t="n">
+      <c r="L22" t="n">
         <v>6.198340704187077</v>
       </c>
-      <c r="L22" t="n">
+      <c r="M22" t="n">
         <v>5057</v>
       </c>
-      <c r="M22" s="4" t="n">
+      <c r="N22" s="4" t="n">
         <v>0.5896776745105794</v>
       </c>
-      <c r="N22" t="n">
+      <c r="O22" t="n">
         <v>75</v>
       </c>
-      <c r="O22" s="4" t="n">
+      <c r="P22" s="4" t="n">
         <v>0.5866666666666667</v>
       </c>
-      <c r="P22" t="n">
+      <c r="Q22" t="n">
         <v>149</v>
       </c>
-      <c r="Q22" s="4" t="n">
+      <c r="R22" s="4" t="n">
         <v>0.738255033557047</v>
       </c>
-      <c r="R22" t="n">
-        <v>1</v>
-      </c>
-      <c r="S22" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="T22" t="n">
+      <c r="S22" t="n">
+        <v>1</v>
+      </c>
+      <c r="T22" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
         <v>5056</v>
       </c>
-      <c r="U22" s="4" t="n">
+      <c r="V22" s="4" t="n">
         <v>0.6867088607594937</v>
       </c>
-      <c r="V22" t="n">
+      <c r="W22" t="n">
         <v>75</v>
       </c>
-      <c r="W22" s="4" t="n">
+      <c r="X22" s="4" t="n">
         <v>0.7466666666666667</v>
       </c>
-      <c r="X22" t="n">
+      <c r="Y22" t="n">
         <v>149</v>
       </c>
-      <c r="Y22" s="4" t="n">
+      <c r="Z22" s="4" t="n">
         <v>0.8053691275167785</v>
       </c>
-      <c r="Z22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA22" s="4" t="n">
+      <c r="AA22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB22" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2929,61 +3022,66 @@
       <c r="H23" t="n">
         <v>7.30000019</v>
       </c>
-      <c r="I23" t="n">
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>A - %74.1 (n=844); E - %71.9 (n=1366); F - %70.9 (n=1142); L - %71.4 (n=1089)</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
         <v>3.693185106211283</v>
       </c>
-      <c r="J23" t="n">
+      <c r="K23" t="n">
         <v>7.352940971020772</v>
       </c>
-      <c r="K23" t="n">
+      <c r="L23" t="n">
         <v>4.584529643024271</v>
       </c>
-      <c r="L23" t="n">
+      <c r="M23" t="n">
         <v>1384</v>
       </c>
-      <c r="M23" s="4" t="n">
+      <c r="N23" s="4" t="n">
         <v>0.5578034682080925</v>
       </c>
-      <c r="N23" t="n">
+      <c r="O23" t="n">
         <v>7</v>
       </c>
-      <c r="O23" s="4" t="n">
+      <c r="P23" s="4" t="n">
         <v>0.4285714285714285</v>
       </c>
-      <c r="P23" t="n">
+      <c r="Q23" t="n">
         <v>25</v>
       </c>
-      <c r="Q23" s="4" t="n">
+      <c r="R23" s="4" t="n">
         <v>0.64</v>
       </c>
-      <c r="R23" t="n">
-        <v>1</v>
-      </c>
-      <c r="S23" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="T23" t="n">
+      <c r="S23" t="n">
+        <v>1</v>
+      </c>
+      <c r="T23" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
         <v>1383</v>
       </c>
-      <c r="U23" s="4" t="n">
+      <c r="V23" s="4" t="n">
         <v>0.6681127982646421</v>
       </c>
-      <c r="V23" t="n">
+      <c r="W23" t="n">
         <v>7</v>
       </c>
-      <c r="W23" s="4" t="n">
+      <c r="X23" s="4" t="n">
         <v>0.4285714285714285</v>
       </c>
-      <c r="X23" t="n">
+      <c r="Y23" t="n">
         <v>25</v>
       </c>
-      <c r="Y23" s="4" t="n">
+      <c r="Z23" s="4" t="n">
         <v>0.68</v>
       </c>
-      <c r="Z23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA23" s="4" t="n">
+      <c r="AA23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB23" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3022,61 +3120,66 @@
       <c r="H24" t="n">
         <v>105.59999847</v>
       </c>
-      <c r="I24" t="n">
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>E - %71.9 (n=1366); G - %71.1 (n=515)</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
         <v>-3.649635087444725</v>
       </c>
-      <c r="J24" t="n">
+      <c r="K24" t="n">
         <v>0.9560229585345636</v>
       </c>
-      <c r="K24" t="n">
+      <c r="L24" t="n">
         <v>6.720567685676926</v>
       </c>
-      <c r="L24" t="n">
+      <c r="M24" t="n">
         <v>5978</v>
       </c>
-      <c r="M24" s="4" t="n">
+      <c r="N24" s="4" t="n">
         <v>0.545332887253262</v>
       </c>
-      <c r="N24" t="n">
+      <c r="O24" t="n">
         <v>83</v>
       </c>
-      <c r="O24" s="4" t="n">
+      <c r="P24" s="4" t="n">
         <v>0.5301204819277109</v>
       </c>
-      <c r="P24" t="n">
+      <c r="Q24" t="n">
         <v>143</v>
       </c>
-      <c r="Q24" s="4" t="n">
+      <c r="R24" s="4" t="n">
         <v>0.6783216783216783</v>
       </c>
-      <c r="R24" t="n">
+      <c r="S24" t="n">
         <v>2</v>
       </c>
-      <c r="S24" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="T24" t="n">
+      <c r="T24" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
         <v>5976</v>
       </c>
-      <c r="U24" s="4" t="n">
+      <c r="V24" s="4" t="n">
         <v>0.6549531459170014</v>
       </c>
-      <c r="V24" t="n">
+      <c r="W24" t="n">
         <v>83</v>
       </c>
-      <c r="W24" s="4" t="n">
+      <c r="X24" s="4" t="n">
         <v>0.6024096385542169</v>
       </c>
-      <c r="X24" t="n">
+      <c r="Y24" t="n">
         <v>139</v>
       </c>
-      <c r="Y24" s="4" t="n">
+      <c r="Z24" s="4" t="n">
         <v>0.7841726618705036</v>
       </c>
-      <c r="Z24" t="n">
+      <c r="AA24" t="n">
         <v>2</v>
       </c>
-      <c r="AA24" s="4" t="n">
+      <c r="AB24" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3115,61 +3218,62 @@
       <c r="H25" t="n">
         <v>34.75999832</v>
       </c>
-      <c r="I25" t="n">
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="n">
         <v>-1.641204944929808</v>
       </c>
-      <c r="J25" t="n">
+      <c r="K25" t="n">
         <v>-6.65951462975336</v>
       </c>
-      <c r="K25" t="n">
+      <c r="L25" t="n">
         <v>1.282047301790046</v>
       </c>
-      <c r="L25" t="n">
+      <c r="M25" t="n">
         <v>3031</v>
       </c>
-      <c r="M25" s="4" t="n">
+      <c r="N25" s="4" t="n">
         <v>0.6423622566809634</v>
       </c>
-      <c r="N25" t="n">
+      <c r="O25" t="n">
         <v>39</v>
       </c>
-      <c r="O25" s="4" t="n">
+      <c r="P25" s="4" t="n">
         <v>0.5384615384615384</v>
       </c>
-      <c r="P25" t="n">
+      <c r="Q25" t="n">
         <v>81</v>
       </c>
-      <c r="Q25" s="4" t="n">
+      <c r="R25" s="4" t="n">
         <v>0.6049382716049383</v>
       </c>
-      <c r="R25" t="n">
-        <v>1</v>
-      </c>
-      <c r="S25" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" t="n">
+      <c r="S25" t="n">
+        <v>1</v>
+      </c>
+      <c r="T25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
         <v>3029</v>
       </c>
-      <c r="U25" s="4" t="n">
+      <c r="V25" s="4" t="n">
         <v>0.7388577088147904</v>
       </c>
-      <c r="V25" t="n">
+      <c r="W25" t="n">
         <v>39</v>
       </c>
-      <c r="W25" s="4" t="n">
+      <c r="X25" s="4" t="n">
         <v>0.6410256410256411</v>
       </c>
-      <c r="X25" t="n">
+      <c r="Y25" t="n">
         <v>79</v>
       </c>
-      <c r="Y25" s="4" t="n">
+      <c r="Z25" s="4" t="n">
         <v>0.6708860759493671</v>
       </c>
-      <c r="Z25" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA25" s="4" t="n">
+      <c r="AA25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB25" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3208,61 +3312,66 @@
       <c r="H26" t="n">
         <v>9.210000040000001</v>
       </c>
-      <c r="I26" t="n">
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>E - %71.9 (n=1366); F - %70.9 (n=1142); G - %71.1 (n=515)</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
         <v>1.543554077012343</v>
       </c>
-      <c r="J26" t="n">
+      <c r="K26" t="n">
         <v>-0.3246724106790722</v>
       </c>
-      <c r="K26" t="n">
+      <c r="L26" t="n">
         <v>2.561252915164425</v>
       </c>
-      <c r="L26" t="n">
+      <c r="M26" t="n">
         <v>5057</v>
       </c>
-      <c r="M26" s="4" t="n">
+      <c r="N26" s="4" t="n">
         <v>0.5896776745105794</v>
       </c>
-      <c r="N26" t="n">
+      <c r="O26" t="n">
         <v>28</v>
       </c>
-      <c r="O26" s="4" t="n">
+      <c r="P26" s="4" t="n">
         <v>0.8214285714285714</v>
       </c>
-      <c r="P26" t="n">
+      <c r="Q26" t="n">
         <v>149</v>
       </c>
-      <c r="Q26" s="4" t="n">
+      <c r="R26" s="4" t="n">
         <v>0.738255033557047</v>
       </c>
-      <c r="R26" t="n">
+      <c r="S26" t="n">
         <v>3</v>
       </c>
-      <c r="S26" s="4" t="n">
+      <c r="T26" s="4" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="T26" t="n">
+      <c r="U26" t="n">
         <v>5056</v>
       </c>
-      <c r="U26" s="4" t="n">
+      <c r="V26" s="4" t="n">
         <v>0.6867088607594937</v>
       </c>
-      <c r="V26" t="n">
+      <c r="W26" t="n">
         <v>28</v>
       </c>
-      <c r="W26" s="4" t="n">
+      <c r="X26" s="4" t="n">
         <v>0.8214285714285714</v>
       </c>
-      <c r="X26" t="n">
+      <c r="Y26" t="n">
         <v>149</v>
       </c>
-      <c r="Y26" s="4" t="n">
+      <c r="Z26" s="4" t="n">
         <v>0.8053691275167785</v>
       </c>
-      <c r="Z26" t="n">
+      <c r="AA26" t="n">
         <v>3</v>
       </c>
-      <c r="AA26" s="4" t="n">
+      <c r="AB26" s="4" t="n">
         <v>0.6666666666666666</v>
       </c>
     </row>
@@ -3301,61 +3410,66 @@
       <c r="H27" t="n">
         <v>36.29999924</v>
       </c>
-      <c r="I27" t="n">
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>E - %78.2 (n=193); G - %80.0 (n=205)</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
         <v>-0.76545264076604</v>
       </c>
-      <c r="J27" t="n">
+      <c r="K27" t="n">
         <v>-0.8196700615873076</v>
       </c>
-      <c r="K27" t="n">
+      <c r="L27" t="n">
         <v>4.852687353910312</v>
       </c>
-      <c r="L27" t="n">
+      <c r="M27" t="n">
         <v>3031</v>
       </c>
-      <c r="M27" s="4" t="n">
+      <c r="N27" s="4" t="n">
         <v>0.6423622566809634</v>
       </c>
-      <c r="N27" t="n">
+      <c r="O27" t="n">
         <v>54</v>
       </c>
-      <c r="O27" s="4" t="n">
+      <c r="P27" s="4" t="n">
         <v>0.5</v>
       </c>
-      <c r="P27" t="n">
+      <c r="Q27" t="n">
         <v>81</v>
       </c>
-      <c r="Q27" s="4" t="n">
+      <c r="R27" s="4" t="n">
         <v>0.6049382716049383</v>
       </c>
-      <c r="R27" t="n">
+      <c r="S27" t="n">
         <v>3</v>
       </c>
-      <c r="S27" s="4" t="n">
+      <c r="T27" s="4" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="T27" t="n">
+      <c r="U27" t="n">
         <v>3029</v>
       </c>
-      <c r="U27" s="4" t="n">
+      <c r="V27" s="4" t="n">
         <v>0.7388577088147904</v>
       </c>
-      <c r="V27" t="n">
+      <c r="W27" t="n">
         <v>54</v>
       </c>
-      <c r="W27" s="4" t="n">
+      <c r="X27" s="4" t="n">
         <v>0.6296296296296297</v>
       </c>
-      <c r="X27" t="n">
+      <c r="Y27" t="n">
         <v>79</v>
       </c>
-      <c r="Y27" s="4" t="n">
+      <c r="Z27" s="4" t="n">
         <v>0.6708860759493671</v>
       </c>
-      <c r="Z27" t="n">
+      <c r="AA27" t="n">
         <v>3</v>
       </c>
-      <c r="AA27" s="4" t="n">
+      <c r="AB27" s="4" t="n">
         <v>0.6666666666666666</v>
       </c>
     </row>
@@ -3394,61 +3508,66 @@
       <c r="H28" t="n">
         <v>70.75</v>
       </c>
-      <c r="I28" t="n">
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>F - %70.9 (n=1142)</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
         <v>16.94214876033058</v>
       </c>
-      <c r="J28" t="n">
+      <c r="K28" t="n">
         <v>4.044117647058831</v>
       </c>
-      <c r="K28" t="n">
+      <c r="L28" t="n">
         <v>-2.815938137519081</v>
       </c>
-      <c r="L28" t="n">
+      <c r="M28" t="n">
         <v>4260</v>
       </c>
-      <c r="M28" s="4" t="n">
+      <c r="N28" s="4" t="n">
         <v>0.5483568075117371</v>
       </c>
-      <c r="N28" t="n">
+      <c r="O28" t="n">
         <v>67</v>
       </c>
-      <c r="O28" s="4" t="n">
+      <c r="P28" s="4" t="n">
         <v>0.5970149253731343</v>
       </c>
-      <c r="P28" t="n">
+      <c r="Q28" t="n">
         <v>80</v>
       </c>
-      <c r="Q28" s="4" t="n">
+      <c r="R28" s="4" t="n">
         <v>0.6</v>
       </c>
-      <c r="R28" t="n">
+      <c r="S28" t="n">
         <v>3</v>
       </c>
-      <c r="S28" s="4" t="n">
+      <c r="T28" s="4" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="T28" t="n">
+      <c r="U28" t="n">
         <v>4259</v>
       </c>
-      <c r="U28" s="4" t="n">
+      <c r="V28" s="4" t="n">
         <v>0.6525005869922517</v>
       </c>
-      <c r="V28" t="n">
+      <c r="W28" t="n">
         <v>67</v>
       </c>
-      <c r="W28" s="4" t="n">
+      <c r="X28" s="4" t="n">
         <v>0.6716417910447762</v>
       </c>
-      <c r="X28" t="n">
+      <c r="Y28" t="n">
         <v>78</v>
       </c>
-      <c r="Y28" s="4" t="n">
+      <c r="Z28" s="4" t="n">
         <v>0.717948717948718</v>
       </c>
-      <c r="Z28" t="n">
+      <c r="AA28" t="n">
         <v>3</v>
       </c>
-      <c r="AA28" s="4" t="n">
+      <c r="AB28" s="4" t="n">
         <v>0.6666666666666666</v>
       </c>
     </row>
@@ -3487,61 +3606,66 @@
       <c r="H29" t="n">
         <v>70.75</v>
       </c>
-      <c r="I29" t="n">
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>F - %70.9 (n=1142)</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
         <v>16.94214876033058</v>
       </c>
-      <c r="J29" t="n">
+      <c r="K29" t="n">
         <v>4.044117647058831</v>
       </c>
-      <c r="K29" t="n">
+      <c r="L29" t="n">
         <v>-2.815938137519081</v>
       </c>
-      <c r="L29" t="n">
+      <c r="M29" t="n">
         <v>5978</v>
       </c>
-      <c r="M29" s="4" t="n">
+      <c r="N29" s="4" t="n">
         <v>0.545332887253262</v>
       </c>
-      <c r="N29" t="n">
+      <c r="O29" t="n">
         <v>86</v>
       </c>
-      <c r="O29" s="4" t="n">
+      <c r="P29" s="4" t="n">
         <v>0.6162790697674418</v>
       </c>
-      <c r="P29" t="n">
+      <c r="Q29" t="n">
         <v>143</v>
       </c>
-      <c r="Q29" s="4" t="n">
+      <c r="R29" s="4" t="n">
         <v>0.6783216783216783</v>
       </c>
-      <c r="R29" t="n">
+      <c r="S29" t="n">
         <v>7</v>
       </c>
-      <c r="S29" s="4" t="n">
+      <c r="T29" s="4" t="n">
         <v>0.7142857142857143</v>
       </c>
-      <c r="T29" t="n">
+      <c r="U29" t="n">
         <v>5976</v>
       </c>
-      <c r="U29" s="4" t="n">
+      <c r="V29" s="4" t="n">
         <v>0.6549531459170014</v>
       </c>
-      <c r="V29" t="n">
+      <c r="W29" t="n">
         <v>86</v>
       </c>
-      <c r="W29" s="4" t="n">
+      <c r="X29" s="4" t="n">
         <v>0.6976744186046512</v>
       </c>
-      <c r="X29" t="n">
+      <c r="Y29" t="n">
         <v>139</v>
       </c>
-      <c r="Y29" s="4" t="n">
+      <c r="Z29" s="4" t="n">
         <v>0.7841726618705036</v>
       </c>
-      <c r="Z29" t="n">
+      <c r="AA29" t="n">
         <v>6</v>
       </c>
-      <c r="AA29" s="4" t="n">
+      <c r="AB29" s="4" t="n">
         <v>0.8333333333333334</v>
       </c>
     </row>
@@ -3580,61 +3704,66 @@
       <c r="H30" t="n">
         <v>40.5</v>
       </c>
-      <c r="I30" t="n">
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>E - %71.9 (n=1366); F - %70.9 (n=1142)</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
         <v>2.272731224173707</v>
       </c>
-      <c r="J30" t="n">
+      <c r="K30" t="n">
         <v>4.220276284756341</v>
       </c>
-      <c r="K30" t="n">
+      <c r="L30" t="n">
         <v>19.61015732539291</v>
       </c>
-      <c r="L30" t="n">
+      <c r="M30" t="n">
         <v>5057</v>
       </c>
-      <c r="M30" s="4" t="n">
+      <c r="N30" s="4" t="n">
         <v>0.5896776745105794</v>
       </c>
-      <c r="N30" t="n">
+      <c r="O30" t="n">
         <v>37</v>
       </c>
-      <c r="O30" s="4" t="n">
+      <c r="P30" s="4" t="n">
         <v>0.7027027027027027</v>
       </c>
-      <c r="P30" t="n">
+      <c r="Q30" t="n">
         <v>149</v>
       </c>
-      <c r="Q30" s="4" t="n">
+      <c r="R30" s="4" t="n">
         <v>0.738255033557047</v>
       </c>
-      <c r="R30" t="n">
+      <c r="S30" t="n">
         <v>2</v>
       </c>
-      <c r="S30" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="T30" t="n">
+      <c r="T30" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
         <v>5056</v>
       </c>
-      <c r="U30" s="4" t="n">
+      <c r="V30" s="4" t="n">
         <v>0.6867088607594937</v>
       </c>
-      <c r="V30" t="n">
+      <c r="W30" t="n">
         <v>37</v>
       </c>
-      <c r="W30" s="4" t="n">
+      <c r="X30" s="4" t="n">
         <v>0.8918918918918919</v>
       </c>
-      <c r="X30" t="n">
+      <c r="Y30" t="n">
         <v>149</v>
       </c>
-      <c r="Y30" s="4" t="n">
+      <c r="Z30" s="4" t="n">
         <v>0.8053691275167785</v>
       </c>
-      <c r="Z30" t="n">
+      <c r="AA30" t="n">
         <v>2</v>
       </c>
-      <c r="AA30" s="4" t="n">
+      <c r="AB30" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3673,61 +3802,66 @@
       <c r="H31" t="n">
         <v>8.52000046</v>
       </c>
-      <c r="I31" t="n">
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>E - %71.9 (n=1366); F - %70.9 (n=1142)</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
         <v>0.1175115126877069</v>
       </c>
-      <c r="J31" t="n">
+      <c r="K31" t="n">
         <v>0.5903209965305134</v>
       </c>
-      <c r="K31" t="n">
+      <c r="L31" t="n">
         <v>2.898559635581055</v>
       </c>
-      <c r="L31" t="n">
+      <c r="M31" t="n">
         <v>5057</v>
       </c>
-      <c r="M31" s="4" t="n">
+      <c r="N31" s="4" t="n">
         <v>0.5896776745105794</v>
       </c>
-      <c r="N31" t="n">
+      <c r="O31" t="n">
         <v>66</v>
       </c>
-      <c r="O31" s="4" t="n">
+      <c r="P31" s="4" t="n">
         <v>0.6818181818181818</v>
       </c>
-      <c r="P31" t="n">
+      <c r="Q31" t="n">
         <v>149</v>
       </c>
-      <c r="Q31" s="4" t="n">
+      <c r="R31" s="4" t="n">
         <v>0.738255033557047</v>
       </c>
-      <c r="R31" t="n">
+      <c r="S31" t="n">
         <v>4</v>
       </c>
-      <c r="S31" s="4" t="n">
+      <c r="T31" s="4" t="n">
         <v>0.5</v>
       </c>
-      <c r="T31" t="n">
+      <c r="U31" t="n">
         <v>5056</v>
       </c>
-      <c r="U31" s="4" t="n">
+      <c r="V31" s="4" t="n">
         <v>0.6867088607594937</v>
       </c>
-      <c r="V31" t="n">
+      <c r="W31" t="n">
         <v>66</v>
       </c>
-      <c r="W31" s="4" t="n">
+      <c r="X31" s="4" t="n">
         <v>0.7272727272727273</v>
       </c>
-      <c r="X31" t="n">
+      <c r="Y31" t="n">
         <v>149</v>
       </c>
-      <c r="Y31" s="4" t="n">
+      <c r="Z31" s="4" t="n">
         <v>0.8053691275167785</v>
       </c>
-      <c r="Z31" t="n">
+      <c r="AA31" t="n">
         <v>4</v>
       </c>
-      <c r="AA31" s="4" t="n">
+      <c r="AB31" s="4" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -3766,61 +3900,66 @@
       <c r="H32" t="n">
         <v>3.74000001</v>
       </c>
-      <c r="I32" t="n">
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>E - %71.9 (n=1366); F - %70.9 (n=1142)</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
         <v>14.02439159168651</v>
       </c>
-      <c r="J32" t="n">
+      <c r="K32" t="n">
         <v>13.67781323620443</v>
       </c>
-      <c r="K32" t="n">
+      <c r="L32" t="n">
         <v>17.98106989322221</v>
       </c>
-      <c r="L32" t="n">
+      <c r="M32" t="n">
         <v>1384</v>
       </c>
-      <c r="M32" s="4" t="n">
+      <c r="N32" s="4" t="n">
         <v>0.5578034682080925</v>
       </c>
-      <c r="N32" t="n">
+      <c r="O32" t="n">
         <v>9</v>
       </c>
-      <c r="O32" s="4" t="n">
+      <c r="P32" s="4" t="n">
         <v>0.8888888888888888</v>
       </c>
-      <c r="P32" t="n">
+      <c r="Q32" t="n">
         <v>25</v>
       </c>
-      <c r="Q32" s="4" t="n">
+      <c r="R32" s="4" t="n">
         <v>0.64</v>
       </c>
-      <c r="R32" t="n">
-        <v>1</v>
-      </c>
-      <c r="S32" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="T32" t="n">
+      <c r="S32" t="n">
+        <v>1</v>
+      </c>
+      <c r="T32" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
         <v>1383</v>
       </c>
-      <c r="U32" s="4" t="n">
+      <c r="V32" s="4" t="n">
         <v>0.6681127982646421</v>
       </c>
-      <c r="V32" t="n">
+      <c r="W32" t="n">
         <v>9</v>
       </c>
-      <c r="W32" s="4" t="n">
+      <c r="X32" s="4" t="n">
         <v>0.8888888888888888</v>
       </c>
-      <c r="X32" t="n">
+      <c r="Y32" t="n">
         <v>25</v>
       </c>
-      <c r="Y32" s="4" t="n">
+      <c r="Z32" s="4" t="n">
         <v>0.68</v>
       </c>
-      <c r="Z32" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA32" s="4" t="n">
+      <c r="AA32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB32" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3859,71 +3998,1115 @@
       <c r="H33" t="n">
         <v>100.30000305</v>
       </c>
-      <c r="I33" t="n">
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>E - %71.9 (n=1366); F - %70.9 (n=1142)</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
         <v>11.50639961194573</v>
       </c>
-      <c r="J33" t="n">
+      <c r="K33" t="n">
         <v>9.140371469153784</v>
       </c>
-      <c r="K33" t="n">
+      <c r="L33" t="n">
         <v>3.991711997664305</v>
       </c>
-      <c r="L33" t="n">
+      <c r="M33" t="n">
         <v>1384</v>
       </c>
-      <c r="M33" s="4" t="n">
+      <c r="N33" s="4" t="n">
         <v>0.5578034682080925</v>
       </c>
-      <c r="N33" t="n">
+      <c r="O33" t="n">
         <v>25</v>
       </c>
-      <c r="O33" s="4" t="n">
+      <c r="P33" s="4" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="P33" t="n">
+      <c r="Q33" t="n">
         <v>25</v>
       </c>
-      <c r="Q33" s="4" t="n">
+      <c r="R33" s="4" t="n">
         <v>0.64</v>
       </c>
-      <c r="R33" t="n">
-        <v>1</v>
-      </c>
-      <c r="S33" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="T33" t="n">
+      <c r="S33" t="n">
+        <v>1</v>
+      </c>
+      <c r="T33" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
         <v>1383</v>
       </c>
-      <c r="U33" s="4" t="n">
+      <c r="V33" s="4" t="n">
         <v>0.6681127982646421</v>
       </c>
-      <c r="V33" t="n">
+      <c r="W33" t="n">
         <v>25</v>
       </c>
-      <c r="W33" s="4" t="n">
+      <c r="X33" s="4" t="n">
         <v>0.6</v>
       </c>
-      <c r="X33" t="n">
+      <c r="Y33" t="n">
         <v>25</v>
       </c>
-      <c r="Y33" s="4" t="n">
+      <c r="Z33" s="4" t="n">
         <v>0.68</v>
       </c>
-      <c r="Z33" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA33" s="4" t="n">
+      <c r="AA33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB33" s="4" t="n">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AA33"/>
+  <autoFilter ref="A1:AB33"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="25" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Sistem</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Yon</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Kosul</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Pencere_Islem_Gunu</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Pencere_Baslangic</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Pencere_Bitis</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Orneklem_N</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Hedefi_Goren_N</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Basari_Orani</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Hedef</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>XU_10g &gt;= -5 AND EW_1g &lt;= 0</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>200</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>45944</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>46232</v>
+      </c>
+      <c r="G2" t="n">
+        <v>256</v>
+      </c>
+      <c r="H2" t="n">
+        <v>207</v>
+      </c>
+      <c r="I2" s="4" t="n">
+        <v>0.80859375</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>2 işlem günü içinde +%1</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>SHORT</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>XU_10g &gt;= -5 AND EW_1g &lt;= 0</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>200</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>45944</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>46232</v>
+      </c>
+      <c r="G3" t="n">
+        <v>844</v>
+      </c>
+      <c r="H3" t="n">
+        <v>625</v>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>0.740521327014218</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>2 işlem günü içinde -%1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>XU_10g &gt;= -3 AND H_gun_araligi_pct &gt;= 4</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>200</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>45944</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>46232</v>
+      </c>
+      <c r="G4" t="n">
+        <v>226</v>
+      </c>
+      <c r="H4" t="n">
+        <v>177</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>0.7831858407079646</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>2 işlem günü içinde +%1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>SHORT</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>XU_10g &gt;= -3 AND H_gun_araligi_pct &gt;= 4</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>200</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>45944</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>46232</v>
+      </c>
+      <c r="G5" t="n">
+        <v>684</v>
+      </c>
+      <c r="H5" t="n">
+        <v>515</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>0.7529239766081871</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>2 işlem günü içinde -%1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>XU_10g &gt;= -3 AND XU_gun_ici_poz &lt;= 0.75</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>200</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>45944</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>46232</v>
+      </c>
+      <c r="G6" t="n">
+        <v>355</v>
+      </c>
+      <c r="H6" t="n">
+        <v>270</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>0.7605633802816901</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>2 işlem günü içinde +%1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>SHORT</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>XU_10g &gt;= -3 AND XU_gun_ici_poz &lt;= 0.75</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>200</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>45944</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>46232</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1306</v>
+      </c>
+      <c r="H7" t="n">
+        <v>950</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>0.7274119448698315</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>2 işlem günü içinde -%1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>XU_3g &gt;= -1 AND REL_10g &lt;= -5</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>200</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>45944</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>46232</v>
+      </c>
+      <c r="G8" t="n">
+        <v>296</v>
+      </c>
+      <c r="H8" t="n">
+        <v>233</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>0.7871621621621622</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>2 işlem günü içinde +%1</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>SHORT</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>XU_3g &gt;= -1 AND REL_10g &lt;= -5</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>200</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>45944</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>46232</v>
+      </c>
+      <c r="G9" t="n">
+        <v>214</v>
+      </c>
+      <c r="H9" t="n">
+        <v>167</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>0.780373831775701</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>2 işlem günü içinde -%1</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>H_ma20_uzaklik &gt;= 0</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>200</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>45944</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>46232</v>
+      </c>
+      <c r="G10" t="n">
+        <v>193</v>
+      </c>
+      <c r="H10" t="n">
+        <v>151</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>0.7823834196891192</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>2 işlem günü içinde +%1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>SHORT</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>H_ma20_uzaklik &gt;= 0</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>200</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>45944</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>46232</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1366</v>
+      </c>
+      <c r="H11" t="n">
+        <v>982</v>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>0.7188872620790629</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>2 işlem günü içinde -%1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Onceki_3_Gun_Getiri_Pct &gt;= 0 AND H_gun_ici_poz &lt;= 0.8</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>200</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>45944</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>46232</v>
+      </c>
+      <c r="G12" t="n">
+        <v>164</v>
+      </c>
+      <c r="H12" t="n">
+        <v>130</v>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>0.7926829268292683</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>2 işlem günü içinde +%1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>SHORT</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Onceki_3_Gun_Getiri_Pct &gt;= 0 AND H_gun_ici_poz &lt;= 0.8</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>200</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>45944</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>46232</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1142</v>
+      </c>
+      <c r="H13" t="n">
+        <v>810</v>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>0.7092819614711033</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>2 işlem günü içinde -%1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Onceki_5_Gun_Getiri_Pct &gt;= -3 AND Hacim_Orani_20 &lt;= 0.8</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>200</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>45944</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>46232</v>
+      </c>
+      <c r="G14" t="n">
+        <v>205</v>
+      </c>
+      <c r="H14" t="n">
+        <v>164</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>2 işlem günü içinde +%1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>SHORT</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Onceki_5_Gun_Getiri_Pct &gt;= -3 AND Hacim_Orani_20 &lt;= 0.8</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>200</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>45944</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>46232</v>
+      </c>
+      <c r="G15" t="n">
+        <v>515</v>
+      </c>
+      <c r="H15" t="n">
+        <v>366</v>
+      </c>
+      <c r="I15" s="4" t="n">
+        <v>0.7106796116504854</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>2 işlem günü içinde -%1</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>REL_2g &lt;= -1 AND REL_3g &lt;= -2</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>200</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>45944</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>46232</v>
+      </c>
+      <c r="G16" t="n">
+        <v>197</v>
+      </c>
+      <c r="H16" t="n">
+        <v>158</v>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>0.8020304568527918</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>2 işlem günü içinde +%1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>SHORT</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>REL_2g &lt;= -1 AND REL_3g &lt;= -2</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>200</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>45944</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>46232</v>
+      </c>
+      <c r="G17" t="n">
+        <v>326</v>
+      </c>
+      <c r="H17" t="n">
+        <v>244</v>
+      </c>
+      <c r="I17" s="4" t="n">
+        <v>0.7484662576687117</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>2 işlem günü içinde -%1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>REL_10g &lt;= -8</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>200</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>45944</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>46232</v>
+      </c>
+      <c r="G18" t="n">
+        <v>231</v>
+      </c>
+      <c r="H18" t="n">
+        <v>191</v>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>0.8268398268398268</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>2 işlem günü içinde +%1</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>SHORT</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>REL_10g &lt;= -8</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>200</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>45944</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>46232</v>
+      </c>
+      <c r="G19" t="n">
+        <v>79</v>
+      </c>
+      <c r="H19" t="n">
+        <v>67</v>
+      </c>
+      <c r="I19" s="4" t="n">
+        <v>0.8481012658227848</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>2 işlem günü içinde -%1</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>REL_10g &lt;= -3 AND Onceki_10_Gun_Getiri_Pct &lt;= -5</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>200</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>45944</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>46232</v>
+      </c>
+      <c r="G20" t="n">
+        <v>370</v>
+      </c>
+      <c r="H20" t="n">
+        <v>298</v>
+      </c>
+      <c r="I20" s="4" t="n">
+        <v>0.8054054054054054</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>2 işlem günü içinde +%1</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>SHORT</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>REL_10g &lt;= -3 AND Onceki_10_Gun_Getiri_Pct &lt;= -5</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>200</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>45944</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>46232</v>
+      </c>
+      <c r="G21" t="n">
+        <v>56</v>
+      </c>
+      <c r="H21" t="n">
+        <v>45</v>
+      </c>
+      <c r="I21" s="4" t="n">
+        <v>0.8035714285714286</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>2 işlem günü içinde -%1</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>XU_1g &lt;= 1.5 AND XU_10g &gt;= -3</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>200</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>45944</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>46232</v>
+      </c>
+      <c r="G22" t="n">
+        <v>517</v>
+      </c>
+      <c r="H22" t="n">
+        <v>383</v>
+      </c>
+      <c r="I22" s="4" t="n">
+        <v>0.7408123791102514</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>2 işlem günü içinde +%1</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>SHORT</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>XU_1g &lt;= 1.5 AND XU_10g &gt;= -3</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>200</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>45944</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>46232</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1365</v>
+      </c>
+      <c r="H23" t="n">
+        <v>973</v>
+      </c>
+      <c r="I23" s="4" t="n">
+        <v>0.7128205128205128</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>2 işlem günü içinde -%1</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>XU_10g &gt;= -5 AND Onceki_3_Gun_Getiri_Pct &gt;= 0</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>200</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>45944</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>46232</v>
+      </c>
+      <c r="G24" t="n">
+        <v>347</v>
+      </c>
+      <c r="H24" t="n">
+        <v>263</v>
+      </c>
+      <c r="I24" s="4" t="n">
+        <v>0.7579250720461095</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>2 işlem günü içinde +%1</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>SHORT</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>XU_10g &gt;= -5 AND Onceki_3_Gun_Getiri_Pct &gt;= 0</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>200</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>45944</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>46232</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1089</v>
+      </c>
+      <c r="H25" t="n">
+        <v>778</v>
+      </c>
+      <c r="I25" s="4" t="n">
+        <v>0.7144168962350781</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>2 işlem günü içinde -%1</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:J25"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5556,7 +6739,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/pattern_report.xlsx
+++ b/pattern_report.xlsx
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>46246.81595442959</v>
+        <v>46246.85278774316</v>
       </c>
     </row>
     <row r="4">
